--- a/tests/eindhoven-500/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaal_laag.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaal_laag.xlsx
@@ -406,7 +406,7 @@
         <v>9199</v>
       </c>
       <c r="C2">
-        <v>11645</v>
+        <v>11975</v>
       </c>
       <c r="D2">
         <v>4276</v>
@@ -418,7 +418,7 @@
         <v>10213</v>
       </c>
       <c r="G2">
-        <v>13739</v>
+        <v>13743</v>
       </c>
       <c r="H2">
         <v>16164</v>
@@ -432,7 +432,7 @@
         <v>8766</v>
       </c>
       <c r="C3">
-        <v>12533</v>
+        <v>12892</v>
       </c>
       <c r="D3">
         <v>5189</v>
@@ -444,7 +444,7 @@
         <v>9996</v>
       </c>
       <c r="G3">
-        <v>15011</v>
+        <v>15017</v>
       </c>
       <c r="H3">
         <v>16822</v>
@@ -458,7 +458,7 @@
         <v>7055</v>
       </c>
       <c r="C4">
-        <v>11009</v>
+        <v>11073</v>
       </c>
       <c r="D4">
         <v>3011</v>
@@ -470,7 +470,7 @@
         <v>7689</v>
       </c>
       <c r="G4">
-        <v>12407</v>
+        <v>12411</v>
       </c>
       <c r="H4">
         <v>14153</v>
@@ -484,7 +484,7 @@
         <v>7055</v>
       </c>
       <c r="C5">
-        <v>11009</v>
+        <v>11073</v>
       </c>
       <c r="D5">
         <v>3011</v>
@@ -496,7 +496,7 @@
         <v>7689</v>
       </c>
       <c r="G5">
-        <v>12407</v>
+        <v>12411</v>
       </c>
       <c r="H5">
         <v>14153</v>
@@ -510,7 +510,7 @@
         <v>7055</v>
       </c>
       <c r="C6">
-        <v>11009</v>
+        <v>11073</v>
       </c>
       <c r="D6">
         <v>3011</v>
@@ -522,7 +522,7 @@
         <v>7689</v>
       </c>
       <c r="G6">
-        <v>12407</v>
+        <v>12411</v>
       </c>
       <c r="H6">
         <v>14153</v>
@@ -536,7 +536,7 @@
         <v>9277</v>
       </c>
       <c r="C7">
-        <v>9270</v>
+        <v>9793</v>
       </c>
       <c r="D7">
         <v>5546</v>
@@ -548,7 +548,7 @@
         <v>10468</v>
       </c>
       <c r="G7">
-        <v>12059</v>
+        <v>12099</v>
       </c>
       <c r="H7">
         <v>14463</v>
@@ -562,7 +562,7 @@
         <v>9277</v>
       </c>
       <c r="C8">
-        <v>9270</v>
+        <v>9793</v>
       </c>
       <c r="D8">
         <v>5546</v>
@@ -574,7 +574,7 @@
         <v>10468</v>
       </c>
       <c r="G8">
-        <v>12059</v>
+        <v>12099</v>
       </c>
       <c r="H8">
         <v>14463</v>
@@ -588,7 +588,7 @@
         <v>9343</v>
       </c>
       <c r="C9">
-        <v>6221</v>
+        <v>7012</v>
       </c>
       <c r="D9">
         <v>6128</v>
@@ -600,7 +600,7 @@
         <v>10774</v>
       </c>
       <c r="G9">
-        <v>9789</v>
+        <v>9860</v>
       </c>
       <c r="H9">
         <v>12724</v>
@@ -614,7 +614,7 @@
         <v>9277</v>
       </c>
       <c r="C10">
-        <v>9270</v>
+        <v>9793</v>
       </c>
       <c r="D10">
         <v>5546</v>
@@ -626,7 +626,7 @@
         <v>10468</v>
       </c>
       <c r="G10">
-        <v>12059</v>
+        <v>12099</v>
       </c>
       <c r="H10">
         <v>14463</v>
@@ -640,7 +640,7 @@
         <v>9277</v>
       </c>
       <c r="C11">
-        <v>9270</v>
+        <v>9793</v>
       </c>
       <c r="D11">
         <v>5546</v>
@@ -652,7 +652,7 @@
         <v>10468</v>
       </c>
       <c r="G11">
-        <v>12059</v>
+        <v>12099</v>
       </c>
       <c r="H11">
         <v>14463</v>
@@ -666,7 +666,7 @@
         <v>7045</v>
       </c>
       <c r="C12">
-        <v>10039</v>
+        <v>10118</v>
       </c>
       <c r="D12">
         <v>3721</v>
@@ -678,7 +678,7 @@
         <v>8027</v>
       </c>
       <c r="G12">
-        <v>11817</v>
+        <v>11822</v>
       </c>
       <c r="H12">
         <v>13484</v>
@@ -692,7 +692,7 @@
         <v>8766</v>
       </c>
       <c r="C13">
-        <v>12533</v>
+        <v>12892</v>
       </c>
       <c r="D13">
         <v>5189</v>
@@ -704,7 +704,7 @@
         <v>9996</v>
       </c>
       <c r="G13">
-        <v>15011</v>
+        <v>15017</v>
       </c>
       <c r="H13">
         <v>16822</v>
@@ -718,7 +718,7 @@
         <v>7045</v>
       </c>
       <c r="C14">
-        <v>10039</v>
+        <v>10118</v>
       </c>
       <c r="D14">
         <v>3721</v>
@@ -730,7 +730,7 @@
         <v>8027</v>
       </c>
       <c r="G14">
-        <v>11817</v>
+        <v>11822</v>
       </c>
       <c r="H14">
         <v>13484</v>
@@ -744,7 +744,7 @@
         <v>9277</v>
       </c>
       <c r="C15">
-        <v>9270</v>
+        <v>9793</v>
       </c>
       <c r="D15">
         <v>5546</v>
@@ -756,7 +756,7 @@
         <v>10468</v>
       </c>
       <c r="G15">
-        <v>12059</v>
+        <v>12099</v>
       </c>
       <c r="H15">
         <v>14463</v>
@@ -770,7 +770,7 @@
         <v>9766</v>
       </c>
       <c r="C16">
-        <v>8644</v>
+        <v>9111</v>
       </c>
       <c r="D16">
         <v>4518</v>
@@ -782,7 +782,7 @@
         <v>10729</v>
       </c>
       <c r="G16">
-        <v>10987</v>
+        <v>11017</v>
       </c>
       <c r="H16">
         <v>14193</v>
@@ -796,7 +796,7 @@
         <v>7045</v>
       </c>
       <c r="C17">
-        <v>10039</v>
+        <v>10118</v>
       </c>
       <c r="D17">
         <v>3721</v>
@@ -808,7 +808,7 @@
         <v>8027</v>
       </c>
       <c r="G17">
-        <v>11817</v>
+        <v>11822</v>
       </c>
       <c r="H17">
         <v>13484</v>
@@ -822,7 +822,7 @@
         <v>8766</v>
       </c>
       <c r="C18">
-        <v>12533</v>
+        <v>12892</v>
       </c>
       <c r="D18">
         <v>5189</v>
@@ -834,7 +834,7 @@
         <v>9996</v>
       </c>
       <c r="G18">
-        <v>15011</v>
+        <v>15017</v>
       </c>
       <c r="H18">
         <v>16822</v>
@@ -848,7 +848,7 @@
         <v>9766</v>
       </c>
       <c r="C19">
-        <v>8644</v>
+        <v>9111</v>
       </c>
       <c r="D19">
         <v>4518</v>
@@ -860,7 +860,7 @@
         <v>10729</v>
       </c>
       <c r="G19">
-        <v>10987</v>
+        <v>11017</v>
       </c>
       <c r="H19">
         <v>14193</v>
@@ -874,7 +874,7 @@
         <v>9766</v>
       </c>
       <c r="C20">
-        <v>8644</v>
+        <v>9111</v>
       </c>
       <c r="D20">
         <v>4518</v>
@@ -886,7 +886,7 @@
         <v>10729</v>
       </c>
       <c r="G20">
-        <v>10987</v>
+        <v>11017</v>
       </c>
       <c r="H20">
         <v>14193</v>
@@ -900,7 +900,7 @@
         <v>9766</v>
       </c>
       <c r="C21">
-        <v>8644</v>
+        <v>9111</v>
       </c>
       <c r="D21">
         <v>4518</v>
@@ -912,7 +912,7 @@
         <v>10729</v>
       </c>
       <c r="G21">
-        <v>10987</v>
+        <v>11017</v>
       </c>
       <c r="H21">
         <v>14193</v>
@@ -926,7 +926,7 @@
         <v>11990</v>
       </c>
       <c r="C22">
-        <v>17256</v>
+        <v>17417</v>
       </c>
       <c r="D22">
         <v>1348</v>
@@ -938,7 +938,7 @@
         <v>12179</v>
       </c>
       <c r="G22">
-        <v>17819</v>
+        <v>17901</v>
       </c>
       <c r="H22">
         <v>21902</v>
@@ -952,7 +952,7 @@
         <v>9199</v>
       </c>
       <c r="C23">
-        <v>11645</v>
+        <v>11975</v>
       </c>
       <c r="D23">
         <v>4276</v>
@@ -964,7 +964,7 @@
         <v>10213</v>
       </c>
       <c r="G23">
-        <v>13739</v>
+        <v>13743</v>
       </c>
       <c r="H23">
         <v>16164</v>
@@ -978,7 +978,7 @@
         <v>5488</v>
       </c>
       <c r="C24">
-        <v>8649</v>
+        <v>8691</v>
       </c>
       <c r="D24">
         <v>2300</v>
@@ -990,7 +990,7 @@
         <v>5949</v>
       </c>
       <c r="G24">
-        <v>9659</v>
+        <v>9660</v>
       </c>
       <c r="H24">
         <v>11168</v>
@@ -1004,7 +1004,7 @@
         <v>5488</v>
       </c>
       <c r="C25">
-        <v>8649</v>
+        <v>8691</v>
       </c>
       <c r="D25">
         <v>2300</v>
@@ -1016,7 +1016,7 @@
         <v>5949</v>
       </c>
       <c r="G25">
-        <v>9659</v>
+        <v>9660</v>
       </c>
       <c r="H25">
         <v>11168</v>
@@ -1030,7 +1030,7 @@
         <v>5488</v>
       </c>
       <c r="C26">
-        <v>8649</v>
+        <v>8691</v>
       </c>
       <c r="D26">
         <v>2300</v>
@@ -1042,7 +1042,7 @@
         <v>5949</v>
       </c>
       <c r="G26">
-        <v>9659</v>
+        <v>9660</v>
       </c>
       <c r="H26">
         <v>11168</v>
@@ -1056,7 +1056,7 @@
         <v>11020</v>
       </c>
       <c r="C27">
-        <v>12067</v>
+        <v>12157</v>
       </c>
       <c r="D27">
         <v>2718</v>
@@ -1068,7 +1068,7 @@
         <v>11362</v>
       </c>
       <c r="G27">
-        <v>13244</v>
+        <v>13250</v>
       </c>
       <c r="H27">
         <v>16453</v>
@@ -1082,7 +1082,7 @@
         <v>11020</v>
       </c>
       <c r="C28">
-        <v>12067</v>
+        <v>12157</v>
       </c>
       <c r="D28">
         <v>2718</v>
@@ -1094,7 +1094,7 @@
         <v>11362</v>
       </c>
       <c r="G28">
-        <v>13244</v>
+        <v>13250</v>
       </c>
       <c r="H28">
         <v>16453</v>
@@ -1108,7 +1108,7 @@
         <v>11020</v>
       </c>
       <c r="C29">
-        <v>12067</v>
+        <v>12157</v>
       </c>
       <c r="D29">
         <v>2718</v>
@@ -1120,7 +1120,7 @@
         <v>11362</v>
       </c>
       <c r="G29">
-        <v>13244</v>
+        <v>13250</v>
       </c>
       <c r="H29">
         <v>16453</v>
@@ -1134,7 +1134,7 @@
         <v>23637</v>
       </c>
       <c r="C30">
-        <v>13625</v>
+        <v>15054</v>
       </c>
       <c r="D30">
         <v>15605</v>
@@ -1146,7 +1146,7 @@
         <v>26369</v>
       </c>
       <c r="G30">
-        <v>22681</v>
+        <v>22827</v>
       </c>
       <c r="H30">
         <v>29583</v>
@@ -1160,7 +1160,7 @@
         <v>23637</v>
       </c>
       <c r="C31">
-        <v>13625</v>
+        <v>15054</v>
       </c>
       <c r="D31">
         <v>15605</v>
@@ -1172,7 +1172,7 @@
         <v>26369</v>
       </c>
       <c r="G31">
-        <v>22681</v>
+        <v>22827</v>
       </c>
       <c r="H31">
         <v>29583</v>
@@ -1186,7 +1186,7 @@
         <v>23538</v>
       </c>
       <c r="C32">
-        <v>19956</v>
+        <v>20827</v>
       </c>
       <c r="D32">
         <v>13910</v>
@@ -1198,7 +1198,7 @@
         <v>25659</v>
       </c>
       <c r="G32">
-        <v>26831</v>
+        <v>26902</v>
       </c>
       <c r="H32">
         <v>32563</v>
@@ -1212,7 +1212,7 @@
         <v>23637</v>
       </c>
       <c r="C33">
-        <v>13625</v>
+        <v>15054</v>
       </c>
       <c r="D33">
         <v>15605</v>
@@ -1224,7 +1224,7 @@
         <v>26369</v>
       </c>
       <c r="G33">
-        <v>22681</v>
+        <v>22827</v>
       </c>
       <c r="H33">
         <v>29583</v>
@@ -1238,22 +1238,22 @@
         <v>27808</v>
       </c>
       <c r="C34">
-        <v>30348</v>
+        <v>30888</v>
       </c>
       <c r="D34">
         <v>11665</v>
       </c>
       <c r="E34">
-        <v>40380</v>
+        <v>40391</v>
       </c>
       <c r="F34">
         <v>28738</v>
       </c>
       <c r="G34">
-        <v>35315</v>
+        <v>35352</v>
       </c>
       <c r="H34">
-        <v>41012</v>
+        <v>41022</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1264,7 +1264,7 @@
         <v>29026</v>
       </c>
       <c r="C35">
-        <v>28300</v>
+        <v>29020</v>
       </c>
       <c r="D35">
         <v>13441</v>
@@ -1276,7 +1276,7 @@
         <v>30367</v>
       </c>
       <c r="G35">
-        <v>34223</v>
+        <v>34246</v>
       </c>
       <c r="H35">
         <v>40379</v>
@@ -1290,7 +1290,7 @@
         <v>20150</v>
       </c>
       <c r="C36">
-        <v>15339</v>
+        <v>15743</v>
       </c>
       <c r="D36">
         <v>12412</v>
@@ -1302,7 +1302,7 @@
         <v>22566</v>
       </c>
       <c r="G36">
-        <v>22028</v>
+        <v>22064</v>
       </c>
       <c r="H36">
         <v>27552</v>
@@ -1316,7 +1316,7 @@
         <v>25241</v>
       </c>
       <c r="C37">
-        <v>13103</v>
+        <v>14354</v>
       </c>
       <c r="D37">
         <v>16495</v>
@@ -1328,7 +1328,7 @@
         <v>27702</v>
       </c>
       <c r="G37">
-        <v>22800</v>
+        <v>22837</v>
       </c>
       <c r="H37">
         <v>30313</v>
@@ -1342,7 +1342,7 @@
         <v>25241</v>
       </c>
       <c r="C38">
-        <v>13103</v>
+        <v>14354</v>
       </c>
       <c r="D38">
         <v>16495</v>
@@ -1354,7 +1354,7 @@
         <v>27702</v>
       </c>
       <c r="G38">
-        <v>22800</v>
+        <v>22837</v>
       </c>
       <c r="H38">
         <v>30313</v>
@@ -1368,22 +1368,22 @@
         <v>28952</v>
       </c>
       <c r="C39">
-        <v>22002</v>
+        <v>23111</v>
       </c>
       <c r="D39">
         <v>15470</v>
       </c>
       <c r="E39">
-        <v>35501</v>
+        <v>35524</v>
       </c>
       <c r="F39">
         <v>30410</v>
       </c>
       <c r="G39">
-        <v>29311</v>
+        <v>29423</v>
       </c>
       <c r="H39">
-        <v>36595</v>
+        <v>36613</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1394,7 +1394,7 @@
         <v>29054</v>
       </c>
       <c r="C40">
-        <v>30702</v>
+        <v>31303</v>
       </c>
       <c r="D40">
         <v>10944</v>
@@ -1406,7 +1406,7 @@
         <v>29891</v>
       </c>
       <c r="G40">
-        <v>35309</v>
+        <v>35329</v>
       </c>
       <c r="H40">
         <v>41723</v>
@@ -1420,7 +1420,7 @@
         <v>29026</v>
       </c>
       <c r="C41">
-        <v>28300</v>
+        <v>29020</v>
       </c>
       <c r="D41">
         <v>13441</v>
@@ -1432,7 +1432,7 @@
         <v>30367</v>
       </c>
       <c r="G41">
-        <v>34223</v>
+        <v>34246</v>
       </c>
       <c r="H41">
         <v>40379</v>
@@ -1446,7 +1446,7 @@
         <v>22721</v>
       </c>
       <c r="C42">
-        <v>17537</v>
+        <v>17850</v>
       </c>
       <c r="D42">
         <v>13845</v>
@@ -1458,7 +1458,7 @@
         <v>24701</v>
       </c>
       <c r="G42">
-        <v>24410</v>
+        <v>24415</v>
       </c>
       <c r="H42">
         <v>30245</v>
@@ -1472,7 +1472,7 @@
         <v>21533</v>
       </c>
       <c r="C43">
-        <v>23514</v>
+        <v>23629</v>
       </c>
       <c r="D43">
         <v>12671</v>
@@ -1484,7 +1484,7 @@
         <v>23673</v>
       </c>
       <c r="G43">
-        <v>29492</v>
+        <v>29494</v>
       </c>
       <c r="H43">
         <v>33759</v>
@@ -1498,7 +1498,7 @@
         <v>18097</v>
       </c>
       <c r="C44">
-        <v>25669</v>
+        <v>25847</v>
       </c>
       <c r="D44">
         <v>7020</v>
@@ -1510,7 +1510,7 @@
         <v>19161</v>
       </c>
       <c r="G44">
-        <v>28867</v>
+        <v>28879</v>
       </c>
       <c r="H44">
         <v>33316</v>
@@ -1524,7 +1524,7 @@
         <v>20353</v>
       </c>
       <c r="C45">
-        <v>15219</v>
+        <v>15539</v>
       </c>
       <c r="D45">
         <v>11414</v>
@@ -1536,7 +1536,7 @@
         <v>22417</v>
       </c>
       <c r="G45">
-        <v>21139</v>
+        <v>21149</v>
       </c>
       <c r="H45">
         <v>27176</v>
@@ -1550,7 +1550,7 @@
         <v>25146</v>
       </c>
       <c r="C46">
-        <v>19371</v>
+        <v>20102</v>
       </c>
       <c r="D46">
         <v>14747</v>
@@ -1562,7 +1562,7 @@
         <v>27049</v>
       </c>
       <c r="G46">
-        <v>26699</v>
+        <v>26726</v>
       </c>
       <c r="H46">
         <v>33007</v>
@@ -1576,7 +1576,7 @@
         <v>19099</v>
       </c>
       <c r="C47">
-        <v>23045</v>
+        <v>23218</v>
       </c>
       <c r="D47">
         <v>8994</v>
@@ -1588,7 +1588,7 @@
         <v>20432</v>
       </c>
       <c r="G47">
-        <v>27475</v>
+        <v>27477</v>
       </c>
       <c r="H47">
         <v>31700</v>
@@ -1602,7 +1602,7 @@
         <v>19231</v>
       </c>
       <c r="C48">
-        <v>20665</v>
+        <v>20814</v>
       </c>
       <c r="D48">
         <v>10496</v>
@@ -1614,7 +1614,7 @@
         <v>21419</v>
       </c>
       <c r="G48">
-        <v>25923</v>
+        <v>25924</v>
       </c>
       <c r="H48">
         <v>30346</v>
@@ -1628,7 +1628,7 @@
         <v>10739</v>
       </c>
       <c r="C49">
-        <v>9456</v>
+        <v>9998</v>
       </c>
       <c r="D49">
         <v>5550</v>
@@ -1640,7 +1640,7 @@
         <v>11882</v>
       </c>
       <c r="G49">
-        <v>12285</v>
+        <v>12328</v>
       </c>
       <c r="H49">
         <v>15426</v>
@@ -1654,7 +1654,7 @@
         <v>10589</v>
       </c>
       <c r="C50">
-        <v>10652</v>
+        <v>10981</v>
       </c>
       <c r="D50">
         <v>6257</v>
@@ -1666,7 +1666,7 @@
         <v>12287</v>
       </c>
       <c r="G50">
-        <v>14046</v>
+        <v>14052</v>
       </c>
       <c r="H50">
         <v>16400</v>
@@ -1680,7 +1680,7 @@
         <v>7673</v>
       </c>
       <c r="C51">
-        <v>10072</v>
+        <v>10161</v>
       </c>
       <c r="D51">
         <v>4342</v>
@@ -1692,7 +1692,7 @@
         <v>8716</v>
       </c>
       <c r="G51">
-        <v>12115</v>
+        <v>12116</v>
       </c>
       <c r="H51">
         <v>13935</v>
@@ -1706,7 +1706,7 @@
         <v>7836</v>
       </c>
       <c r="C52">
-        <v>11007</v>
+        <v>11200</v>
       </c>
       <c r="D52">
         <v>3757</v>
@@ -1718,7 +1718,7 @@
         <v>8579</v>
       </c>
       <c r="G52">
-        <v>12776</v>
+        <v>12783</v>
       </c>
       <c r="H52">
         <v>14722</v>
@@ -1732,7 +1732,7 @@
         <v>8889</v>
       </c>
       <c r="C53">
-        <v>7615</v>
+        <v>7994</v>
       </c>
       <c r="D53">
         <v>5087</v>
@@ -1744,7 +1744,7 @@
         <v>10086</v>
       </c>
       <c r="G53">
-        <v>10369</v>
+        <v>10381</v>
       </c>
       <c r="H53">
         <v>13020</v>
@@ -1758,7 +1758,7 @@
         <v>8182</v>
       </c>
       <c r="C54">
-        <v>7457</v>
+        <v>7616</v>
       </c>
       <c r="D54">
         <v>4624</v>
@@ -1770,7 +1770,7 @@
         <v>9185</v>
       </c>
       <c r="G54">
-        <v>9742</v>
+        <v>9751</v>
       </c>
       <c r="H54">
         <v>12202</v>
@@ -1784,7 +1784,7 @@
         <v>10589</v>
       </c>
       <c r="C55">
-        <v>10652</v>
+        <v>10981</v>
       </c>
       <c r="D55">
         <v>6257</v>
@@ -1796,7 +1796,7 @@
         <v>12287</v>
       </c>
       <c r="G55">
-        <v>14046</v>
+        <v>14052</v>
       </c>
       <c r="H55">
         <v>16400</v>
@@ -1810,7 +1810,7 @@
         <v>12306</v>
       </c>
       <c r="C56">
-        <v>13783</v>
+        <v>14015</v>
       </c>
       <c r="D56">
         <v>4421</v>
@@ -1822,7 +1822,7 @@
         <v>13075</v>
       </c>
       <c r="G56">
-        <v>15767</v>
+        <v>15796</v>
       </c>
       <c r="H56">
         <v>18866</v>
@@ -1836,7 +1836,7 @@
         <v>7787</v>
       </c>
       <c r="C57">
-        <v>10658</v>
+        <v>10793</v>
       </c>
       <c r="D57">
         <v>3002</v>
@@ -1848,7 +1848,7 @@
         <v>8412</v>
       </c>
       <c r="G57">
-        <v>12054</v>
+        <v>12060</v>
       </c>
       <c r="H57">
         <v>14145</v>
@@ -1862,7 +1862,7 @@
         <v>13234</v>
       </c>
       <c r="C58">
-        <v>12206</v>
+        <v>12323</v>
       </c>
       <c r="D58">
         <v>3613</v>
@@ -1874,7 +1874,7 @@
         <v>13672</v>
       </c>
       <c r="G58">
-        <v>13820</v>
+        <v>13824</v>
       </c>
       <c r="H58">
         <v>17421</v>
@@ -1888,7 +1888,7 @@
         <v>13234</v>
       </c>
       <c r="C59">
-        <v>12206</v>
+        <v>12323</v>
       </c>
       <c r="D59">
         <v>3613</v>
@@ -1900,7 +1900,7 @@
         <v>13672</v>
       </c>
       <c r="G59">
-        <v>13820</v>
+        <v>13824</v>
       </c>
       <c r="H59">
         <v>17421</v>
@@ -1914,7 +1914,7 @@
         <v>6555</v>
       </c>
       <c r="C60">
-        <v>7883</v>
+        <v>7963</v>
       </c>
       <c r="D60">
         <v>1980</v>
@@ -1926,7 +1926,7 @@
         <v>6848</v>
       </c>
       <c r="G60">
-        <v>8753</v>
+        <v>8756</v>
       </c>
       <c r="H60">
         <v>10597</v>
@@ -1940,7 +1940,7 @@
         <v>6555</v>
       </c>
       <c r="C61">
-        <v>7883</v>
+        <v>7963</v>
       </c>
       <c r="D61">
         <v>1980</v>
@@ -1952,7 +1952,7 @@
         <v>6848</v>
       </c>
       <c r="G61">
-        <v>8753</v>
+        <v>8756</v>
       </c>
       <c r="H61">
         <v>10597</v>
@@ -1966,7 +1966,7 @@
         <v>2388</v>
       </c>
       <c r="C62">
-        <v>4693</v>
+        <v>4737</v>
       </c>
       <c r="D62">
         <v>781</v>
@@ -1978,7 +1978,7 @@
         <v>2538</v>
       </c>
       <c r="G62">
-        <v>5065</v>
+        <v>5080</v>
       </c>
       <c r="H62">
         <v>5846</v>
@@ -1992,7 +1992,7 @@
         <v>2388</v>
       </c>
       <c r="C63">
-        <v>4693</v>
+        <v>4737</v>
       </c>
       <c r="D63">
         <v>781</v>
@@ -2004,7 +2004,7 @@
         <v>2538</v>
       </c>
       <c r="G63">
-        <v>5065</v>
+        <v>5080</v>
       </c>
       <c r="H63">
         <v>5846</v>
@@ -2018,7 +2018,7 @@
         <v>1272</v>
       </c>
       <c r="C64">
-        <v>3829</v>
+        <v>3881</v>
       </c>
       <c r="D64">
         <v>407</v>
@@ -2030,7 +2030,7 @@
         <v>1398</v>
       </c>
       <c r="G64">
-        <v>4044</v>
+        <v>4054</v>
       </c>
       <c r="H64">
         <v>4512</v>
@@ -2044,7 +2044,7 @@
         <v>1272</v>
       </c>
       <c r="C65">
-        <v>3829</v>
+        <v>3881</v>
       </c>
       <c r="D65">
         <v>407</v>
@@ -2056,7 +2056,7 @@
         <v>1398</v>
       </c>
       <c r="G65">
-        <v>4044</v>
+        <v>4054</v>
       </c>
       <c r="H65">
         <v>4512</v>
@@ -2070,7 +2070,7 @@
         <v>11188</v>
       </c>
       <c r="C66">
-        <v>12661</v>
+        <v>13118</v>
       </c>
       <c r="D66">
         <v>6734</v>
@@ -2082,7 +2082,7 @@
         <v>13094</v>
       </c>
       <c r="G66">
-        <v>16277</v>
+        <v>16327</v>
       </c>
       <c r="H66">
         <v>19347</v>
@@ -2096,7 +2096,7 @@
         <v>10507</v>
       </c>
       <c r="C67">
-        <v>17891</v>
+        <v>18189</v>
       </c>
       <c r="D67">
         <v>6257</v>
@@ -2108,7 +2108,7 @@
         <v>12443</v>
       </c>
       <c r="G67">
-        <v>21092</v>
+        <v>21098</v>
       </c>
       <c r="H67">
         <v>23462</v>
@@ -2122,7 +2122,7 @@
         <v>11188</v>
       </c>
       <c r="C68">
-        <v>12661</v>
+        <v>13118</v>
       </c>
       <c r="D68">
         <v>6734</v>
@@ -2134,7 +2134,7 @@
         <v>13094</v>
       </c>
       <c r="G68">
-        <v>16277</v>
+        <v>16327</v>
       </c>
       <c r="H68">
         <v>19347</v>
@@ -2148,7 +2148,7 @@
         <v>10507</v>
       </c>
       <c r="C69">
-        <v>17891</v>
+        <v>18189</v>
       </c>
       <c r="D69">
         <v>6257</v>
@@ -2160,7 +2160,7 @@
         <v>12443</v>
       </c>
       <c r="G69">
-        <v>21092</v>
+        <v>21098</v>
       </c>
       <c r="H69">
         <v>23462</v>
@@ -2174,7 +2174,7 @@
         <v>10507</v>
       </c>
       <c r="C70">
-        <v>17891</v>
+        <v>18189</v>
       </c>
       <c r="D70">
         <v>6257</v>
@@ -2186,7 +2186,7 @@
         <v>12443</v>
       </c>
       <c r="G70">
-        <v>21092</v>
+        <v>21098</v>
       </c>
       <c r="H70">
         <v>23462</v>
@@ -2200,7 +2200,7 @@
         <v>11533</v>
       </c>
       <c r="C71">
-        <v>21805</v>
+        <v>22036</v>
       </c>
       <c r="D71">
         <v>5879</v>
@@ -2212,7 +2212,7 @@
         <v>12865</v>
       </c>
       <c r="G71">
-        <v>24667</v>
+        <v>24672</v>
       </c>
       <c r="H71">
         <v>27329</v>
@@ -2226,7 +2226,7 @@
         <v>10524</v>
       </c>
       <c r="C72">
-        <v>19731</v>
+        <v>19976</v>
       </c>
       <c r="D72">
         <v>5143</v>
@@ -2238,7 +2238,7 @@
         <v>11724</v>
       </c>
       <c r="G72">
-        <v>22265</v>
+        <v>22269</v>
       </c>
       <c r="H72">
         <v>24707</v>
@@ -2252,7 +2252,7 @@
         <v>10524</v>
       </c>
       <c r="C73">
-        <v>19731</v>
+        <v>19976</v>
       </c>
       <c r="D73">
         <v>5143</v>
@@ -2264,7 +2264,7 @@
         <v>11724</v>
       </c>
       <c r="G73">
-        <v>22265</v>
+        <v>22269</v>
       </c>
       <c r="H73">
         <v>24707</v>
@@ -2278,7 +2278,7 @@
         <v>10524</v>
       </c>
       <c r="C74">
-        <v>19731</v>
+        <v>19976</v>
       </c>
       <c r="D74">
         <v>5143</v>
@@ -2290,7 +2290,7 @@
         <v>11724</v>
       </c>
       <c r="G74">
-        <v>22265</v>
+        <v>22269</v>
       </c>
       <c r="H74">
         <v>24707</v>
@@ -2304,7 +2304,7 @@
         <v>8172</v>
       </c>
       <c r="C75">
-        <v>12750</v>
+        <v>12833</v>
       </c>
       <c r="D75">
         <v>3528</v>
@@ -2316,7 +2316,7 @@
         <v>9147</v>
       </c>
       <c r="G75">
-        <v>14556</v>
+        <v>14557</v>
       </c>
       <c r="H75">
         <v>16716</v>
@@ -2330,7 +2330,7 @@
         <v>10507</v>
       </c>
       <c r="C76">
-        <v>17891</v>
+        <v>18189</v>
       </c>
       <c r="D76">
         <v>6257</v>
@@ -2342,7 +2342,7 @@
         <v>12443</v>
       </c>
       <c r="G76">
-        <v>21092</v>
+        <v>21098</v>
       </c>
       <c r="H76">
         <v>23462</v>
@@ -2356,7 +2356,7 @@
         <v>10743</v>
       </c>
       <c r="C77">
-        <v>17723</v>
+        <v>18075</v>
       </c>
       <c r="D77">
         <v>5068</v>
@@ -2368,7 +2368,7 @@
         <v>11759</v>
       </c>
       <c r="G77">
-        <v>20189</v>
+        <v>20196</v>
       </c>
       <c r="H77">
         <v>22791</v>
@@ -2382,7 +2382,7 @@
         <v>10743</v>
       </c>
       <c r="C78">
-        <v>17723</v>
+        <v>18075</v>
       </c>
       <c r="D78">
         <v>5068</v>
@@ -2394,7 +2394,7 @@
         <v>11759</v>
       </c>
       <c r="G78">
-        <v>20189</v>
+        <v>20196</v>
       </c>
       <c r="H78">
         <v>22791</v>
@@ -2408,7 +2408,7 @@
         <v>10743</v>
       </c>
       <c r="C79">
-        <v>17723</v>
+        <v>18075</v>
       </c>
       <c r="D79">
         <v>5068</v>
@@ -2420,7 +2420,7 @@
         <v>11759</v>
       </c>
       <c r="G79">
-        <v>20189</v>
+        <v>20196</v>
       </c>
       <c r="H79">
         <v>22791</v>
@@ -2434,7 +2434,7 @@
         <v>10743</v>
       </c>
       <c r="C80">
-        <v>17723</v>
+        <v>18075</v>
       </c>
       <c r="D80">
         <v>5068</v>
@@ -2446,7 +2446,7 @@
         <v>11759</v>
       </c>
       <c r="G80">
-        <v>20189</v>
+        <v>20196</v>
       </c>
       <c r="H80">
         <v>22791</v>
@@ -2460,7 +2460,7 @@
         <v>17143</v>
       </c>
       <c r="C81">
-        <v>24905</v>
+        <v>24946</v>
       </c>
       <c r="D81">
         <v>6898</v>
@@ -2472,7 +2472,7 @@
         <v>18453</v>
       </c>
       <c r="G81">
-        <v>28268</v>
+        <v>28272</v>
       </c>
       <c r="H81">
         <v>32955</v>
@@ -2486,7 +2486,7 @@
         <v>17143</v>
       </c>
       <c r="C82">
-        <v>24905</v>
+        <v>24946</v>
       </c>
       <c r="D82">
         <v>6898</v>
@@ -2498,7 +2498,7 @@
         <v>18453</v>
       </c>
       <c r="G82">
-        <v>28268</v>
+        <v>28272</v>
       </c>
       <c r="H82">
         <v>32955</v>
@@ -2512,7 +2512,7 @@
         <v>11328</v>
       </c>
       <c r="C83">
-        <v>17476</v>
+        <v>17546</v>
       </c>
       <c r="D83">
         <v>2536</v>
@@ -2524,7 +2524,7 @@
         <v>12054</v>
       </c>
       <c r="G83">
-        <v>18733</v>
+        <v>18736</v>
       </c>
       <c r="H83">
         <v>23183</v>
@@ -2538,7 +2538,7 @@
         <v>11328</v>
       </c>
       <c r="C84">
-        <v>17476</v>
+        <v>17546</v>
       </c>
       <c r="D84">
         <v>2536</v>
@@ -2550,7 +2550,7 @@
         <v>12054</v>
       </c>
       <c r="G84">
-        <v>18733</v>
+        <v>18736</v>
       </c>
       <c r="H84">
         <v>23183</v>
@@ -2564,7 +2564,7 @@
         <v>20595</v>
       </c>
       <c r="C85">
-        <v>27432</v>
+        <v>27525</v>
       </c>
       <c r="D85">
         <v>2888</v>
@@ -2576,7 +2576,7 @@
         <v>21213</v>
       </c>
       <c r="G85">
-        <v>28697</v>
+        <v>28706</v>
       </c>
       <c r="H85">
         <v>36350</v>
@@ -2590,7 +2590,7 @@
         <v>20595</v>
       </c>
       <c r="C86">
-        <v>27432</v>
+        <v>27525</v>
       </c>
       <c r="D86">
         <v>2888</v>
@@ -2602,7 +2602,7 @@
         <v>21213</v>
       </c>
       <c r="G86">
-        <v>28697</v>
+        <v>28706</v>
       </c>
       <c r="H86">
         <v>36350</v>
@@ -2616,7 +2616,7 @@
         <v>18764</v>
       </c>
       <c r="C87">
-        <v>26592</v>
+        <v>26643</v>
       </c>
       <c r="D87">
         <v>3174</v>
@@ -2628,7 +2628,7 @@
         <v>19503</v>
       </c>
       <c r="G87">
-        <v>27930</v>
+        <v>27947</v>
       </c>
       <c r="H87">
         <v>34818</v>
@@ -2642,7 +2642,7 @@
         <v>18764</v>
       </c>
       <c r="C88">
-        <v>26592</v>
+        <v>26643</v>
       </c>
       <c r="D88">
         <v>3174</v>
@@ -2654,7 +2654,7 @@
         <v>19503</v>
       </c>
       <c r="G88">
-        <v>27930</v>
+        <v>27947</v>
       </c>
       <c r="H88">
         <v>34818</v>
@@ -2668,7 +2668,7 @@
         <v>18764</v>
       </c>
       <c r="C89">
-        <v>26592</v>
+        <v>26643</v>
       </c>
       <c r="D89">
         <v>3174</v>
@@ -2680,7 +2680,7 @@
         <v>19503</v>
       </c>
       <c r="G89">
-        <v>27930</v>
+        <v>27947</v>
       </c>
       <c r="H89">
         <v>34818</v>
@@ -2694,22 +2694,22 @@
         <v>43221</v>
       </c>
       <c r="C90">
-        <v>12351</v>
+        <v>21668</v>
       </c>
       <c r="D90">
         <v>43176</v>
       </c>
       <c r="E90">
-        <v>44404</v>
+        <v>44405</v>
       </c>
       <c r="F90">
         <v>50126</v>
       </c>
       <c r="G90">
-        <v>45279</v>
+        <v>45420</v>
       </c>
       <c r="H90">
-        <v>50891</v>
+        <v>50892</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -2720,22 +2720,22 @@
         <v>43236</v>
       </c>
       <c r="C91">
-        <v>11925</v>
+        <v>21384</v>
       </c>
       <c r="D91">
         <v>43243</v>
       </c>
       <c r="E91">
-        <v>44361</v>
+        <v>44362</v>
       </c>
       <c r="F91">
         <v>50157</v>
       </c>
       <c r="G91">
-        <v>45245</v>
+        <v>45388</v>
       </c>
       <c r="H91">
-        <v>50886</v>
+        <v>50887</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -2746,22 +2746,22 @@
         <v>43297</v>
       </c>
       <c r="C92">
-        <v>10105</v>
+        <v>20171</v>
       </c>
       <c r="D92">
         <v>43530</v>
       </c>
       <c r="E92">
-        <v>44179</v>
+        <v>44181</v>
       </c>
       <c r="F92">
         <v>50292</v>
       </c>
       <c r="G92">
-        <v>45099</v>
+        <v>45251</v>
       </c>
       <c r="H92">
-        <v>50863</v>
+        <v>50864</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -2772,22 +2772,22 @@
         <v>43110</v>
       </c>
       <c r="C93">
-        <v>15643</v>
+        <v>23862</v>
       </c>
       <c r="D93">
         <v>42658</v>
       </c>
       <c r="E93">
-        <v>44733</v>
+        <v>44734</v>
       </c>
       <c r="F93">
         <v>49882</v>
       </c>
       <c r="G93">
-        <v>45544</v>
+        <v>45668</v>
       </c>
       <c r="H93">
-        <v>50932</v>
+        <v>50933</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -2798,19 +2798,19 @@
         <v>43452</v>
       </c>
       <c r="C94">
-        <v>7128</v>
+        <v>14207</v>
       </c>
       <c r="D94">
         <v>40220</v>
       </c>
       <c r="E94">
-        <v>43974</v>
+        <v>43982</v>
       </c>
       <c r="F94">
         <v>48625</v>
       </c>
       <c r="G94">
-        <v>41252</v>
+        <v>41444</v>
       </c>
       <c r="H94">
         <v>49021</v>
@@ -2824,19 +2824,19 @@
         <v>43120</v>
       </c>
       <c r="C95">
-        <v>15343</v>
+        <v>23662</v>
       </c>
       <c r="D95">
         <v>42705</v>
       </c>
       <c r="E95">
-        <v>44703</v>
+        <v>44704</v>
       </c>
       <c r="F95">
         <v>49904</v>
       </c>
       <c r="G95">
-        <v>45519</v>
+        <v>45645</v>
       </c>
       <c r="H95">
         <v>50929</v>
@@ -2850,22 +2850,22 @@
         <v>43276</v>
       </c>
       <c r="C96">
-        <v>10722</v>
+        <v>20583</v>
       </c>
       <c r="D96">
         <v>43433</v>
       </c>
       <c r="E96">
-        <v>44241</v>
+        <v>44242</v>
       </c>
       <c r="F96">
         <v>50246</v>
       </c>
       <c r="G96">
-        <v>45148</v>
+        <v>45297</v>
       </c>
       <c r="H96">
-        <v>50871</v>
+        <v>50872</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -2876,22 +2876,22 @@
         <v>43110</v>
       </c>
       <c r="C97">
-        <v>15643</v>
+        <v>23862</v>
       </c>
       <c r="D97">
         <v>42658</v>
       </c>
       <c r="E97">
-        <v>44733</v>
+        <v>44734</v>
       </c>
       <c r="F97">
         <v>49882</v>
       </c>
       <c r="G97">
-        <v>45544</v>
+        <v>45668</v>
       </c>
       <c r="H97">
-        <v>50932</v>
+        <v>50933</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -2902,22 +2902,22 @@
         <v>39869</v>
       </c>
       <c r="C98">
-        <v>14423</v>
+        <v>20277</v>
       </c>
       <c r="D98">
         <v>37757</v>
       </c>
       <c r="E98">
-        <v>41823</v>
+        <v>41825</v>
       </c>
       <c r="F98">
         <v>45928</v>
       </c>
       <c r="G98">
-        <v>40967</v>
+        <v>41110</v>
       </c>
       <c r="H98">
-        <v>47266</v>
+        <v>47268</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -2928,22 +2928,22 @@
         <v>39923</v>
       </c>
       <c r="C99">
-        <v>13115</v>
+        <v>19292</v>
       </c>
       <c r="D99">
         <v>37961</v>
       </c>
       <c r="E99">
-        <v>41656</v>
+        <v>41658</v>
       </c>
       <c r="F99">
         <v>46031</v>
       </c>
       <c r="G99">
-        <v>40808</v>
+        <v>40959</v>
       </c>
       <c r="H99">
-        <v>47218</v>
+        <v>47220</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -2954,7 +2954,7 @@
         <v>42563</v>
       </c>
       <c r="C100">
-        <v>14211</v>
+        <v>19827</v>
       </c>
       <c r="D100">
         <v>37835</v>
@@ -2966,7 +2966,7 @@
         <v>47351</v>
       </c>
       <c r="G100">
-        <v>40759</v>
+        <v>40924</v>
       </c>
       <c r="H100">
         <v>48201</v>
@@ -2980,7 +2980,7 @@
         <v>42595</v>
       </c>
       <c r="C101">
-        <v>13341</v>
+        <v>19167</v>
       </c>
       <c r="D101">
         <v>37979</v>
@@ -2992,7 +2992,7 @@
         <v>47409</v>
       </c>
       <c r="G101">
-        <v>40656</v>
+        <v>40827</v>
       </c>
       <c r="H101">
         <v>48187</v>
@@ -3006,7 +3006,7 @@
         <v>42533</v>
       </c>
       <c r="C102">
-        <v>15020</v>
+        <v>20441</v>
       </c>
       <c r="D102">
         <v>37701</v>
@@ -3018,7 +3018,7 @@
         <v>47297</v>
       </c>
       <c r="G102">
-        <v>40856</v>
+        <v>41015</v>
       </c>
       <c r="H102">
         <v>48213</v>
@@ -3032,7 +3032,7 @@
         <v>37766</v>
       </c>
       <c r="C103">
-        <v>13419</v>
+        <v>18795</v>
       </c>
       <c r="D103">
         <v>32302</v>
@@ -3044,7 +3044,7 @@
         <v>42428</v>
       </c>
       <c r="G103">
-        <v>36090</v>
+        <v>36312</v>
       </c>
       <c r="H103">
         <v>43874</v>
@@ -3058,7 +3058,7 @@
         <v>37766</v>
       </c>
       <c r="C104">
-        <v>13419</v>
+        <v>18795</v>
       </c>
       <c r="D104">
         <v>32302</v>
@@ -3070,7 +3070,7 @@
         <v>42428</v>
       </c>
       <c r="G104">
-        <v>36090</v>
+        <v>36312</v>
       </c>
       <c r="H104">
         <v>43874</v>
@@ -3084,7 +3084,7 @@
         <v>38854</v>
       </c>
       <c r="C105">
-        <v>21648</v>
+        <v>24607</v>
       </c>
       <c r="D105">
         <v>30501</v>
@@ -3096,7 +3096,7 @@
         <v>41975</v>
       </c>
       <c r="G105">
-        <v>38301</v>
+        <v>38390</v>
       </c>
       <c r="H105">
         <v>45158</v>
@@ -3110,7 +3110,7 @@
         <v>37527</v>
       </c>
       <c r="C106">
-        <v>30330</v>
+        <v>32505</v>
       </c>
       <c r="D106">
         <v>26078</v>
@@ -3122,7 +3122,7 @@
         <v>39961</v>
       </c>
       <c r="G106">
-        <v>42407</v>
+        <v>42522</v>
       </c>
       <c r="H106">
         <v>48342</v>
@@ -3136,7 +3136,7 @@
         <v>37527</v>
       </c>
       <c r="C107">
-        <v>30330</v>
+        <v>32505</v>
       </c>
       <c r="D107">
         <v>26078</v>
@@ -3148,7 +3148,7 @@
         <v>39961</v>
       </c>
       <c r="G107">
-        <v>42407</v>
+        <v>42522</v>
       </c>
       <c r="H107">
         <v>48342</v>
@@ -3162,7 +3162,7 @@
         <v>37936</v>
       </c>
       <c r="C108">
-        <v>37137</v>
+        <v>38326</v>
       </c>
       <c r="D108">
         <v>25857</v>
@@ -3174,7 +3174,7 @@
         <v>40455</v>
       </c>
       <c r="G108">
-        <v>48128</v>
+        <v>48147</v>
       </c>
       <c r="H108">
         <v>52387</v>
@@ -3188,22 +3188,22 @@
         <v>35708</v>
       </c>
       <c r="C109">
-        <v>20969</v>
+        <v>24629</v>
       </c>
       <c r="D109">
         <v>25339</v>
       </c>
       <c r="E109">
-        <v>40718</v>
+        <v>40721</v>
       </c>
       <c r="F109">
         <v>38978</v>
       </c>
       <c r="G109">
-        <v>35052</v>
+        <v>35358</v>
       </c>
       <c r="H109">
-        <v>43301</v>
+        <v>43304</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -3214,22 +3214,22 @@
         <v>35708</v>
       </c>
       <c r="C110">
-        <v>20969</v>
+        <v>24629</v>
       </c>
       <c r="D110">
         <v>25339</v>
       </c>
       <c r="E110">
-        <v>40718</v>
+        <v>40721</v>
       </c>
       <c r="F110">
         <v>38978</v>
       </c>
       <c r="G110">
-        <v>35052</v>
+        <v>35358</v>
       </c>
       <c r="H110">
-        <v>43301</v>
+        <v>43304</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -3240,22 +3240,22 @@
         <v>35765</v>
       </c>
       <c r="C111">
-        <v>19597</v>
+        <v>23519</v>
       </c>
       <c r="D111">
         <v>25518</v>
       </c>
       <c r="E111">
-        <v>40402</v>
+        <v>40405</v>
       </c>
       <c r="F111">
         <v>39065</v>
       </c>
       <c r="G111">
-        <v>34512</v>
+        <v>34840</v>
       </c>
       <c r="H111">
-        <v>43066</v>
+        <v>43068</v>
       </c>
     </row>
     <row r="112" spans="1:8">
@@ -3266,22 +3266,22 @@
         <v>37274</v>
       </c>
       <c r="C112">
-        <v>14094</v>
+        <v>19840</v>
       </c>
       <c r="D112">
         <v>30361</v>
       </c>
       <c r="E112">
-        <v>39679</v>
+        <v>39692</v>
       </c>
       <c r="F112">
         <v>41840</v>
       </c>
       <c r="G112">
-        <v>35007</v>
+        <v>35554</v>
       </c>
       <c r="H112">
-        <v>43702</v>
+        <v>43711</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -3292,7 +3292,7 @@
         <v>35107</v>
       </c>
       <c r="C113">
-        <v>21039</v>
+        <v>23154</v>
       </c>
       <c r="D113">
         <v>23058</v>
@@ -3304,7 +3304,7 @@
         <v>37631</v>
       </c>
       <c r="G113">
-        <v>32777</v>
+        <v>33099</v>
       </c>
       <c r="H113">
         <v>41720</v>
@@ -3318,7 +3318,7 @@
         <v>35118</v>
       </c>
       <c r="C114">
-        <v>29079</v>
+        <v>30236</v>
       </c>
       <c r="D114">
         <v>20892</v>
@@ -3330,7 +3330,7 @@
         <v>37108</v>
       </c>
       <c r="G114">
-        <v>38037</v>
+        <v>38226</v>
       </c>
       <c r="H114">
         <v>45460</v>
@@ -3344,22 +3344,22 @@
         <v>37288</v>
       </c>
       <c r="C115">
-        <v>13778</v>
+        <v>19601</v>
       </c>
       <c r="D115">
         <v>30403</v>
       </c>
       <c r="E115">
-        <v>39627</v>
+        <v>39639</v>
       </c>
       <c r="F115">
         <v>41862</v>
       </c>
       <c r="G115">
-        <v>34922</v>
+        <v>35477</v>
       </c>
       <c r="H115">
-        <v>43673</v>
+        <v>43683</v>
       </c>
     </row>
     <row r="116" spans="1:8">
@@ -3370,22 +3370,22 @@
         <v>37274</v>
       </c>
       <c r="C116">
-        <v>14094</v>
+        <v>19840</v>
       </c>
       <c r="D116">
         <v>30361</v>
       </c>
       <c r="E116">
-        <v>39679</v>
+        <v>39692</v>
       </c>
       <c r="F116">
         <v>41840</v>
       </c>
       <c r="G116">
-        <v>35007</v>
+        <v>35554</v>
       </c>
       <c r="H116">
-        <v>43702</v>
+        <v>43711</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -3396,7 +3396,7 @@
         <v>35104</v>
       </c>
       <c r="C117">
-        <v>21111</v>
+        <v>23217</v>
       </c>
       <c r="D117">
         <v>23049</v>
@@ -3408,7 +3408,7 @@
         <v>37627</v>
       </c>
       <c r="G117">
-        <v>32810</v>
+        <v>33130</v>
       </c>
       <c r="H117">
         <v>41733</v>
@@ -3422,7 +3422,7 @@
         <v>33874</v>
       </c>
       <c r="C118">
-        <v>39360</v>
+        <v>39877</v>
       </c>
       <c r="D118">
         <v>16029</v>
@@ -3434,7 +3434,7 @@
         <v>35073</v>
       </c>
       <c r="G118">
-        <v>45520</v>
+        <v>45572</v>
       </c>
       <c r="H118">
         <v>51365</v>
@@ -3448,7 +3448,7 @@
         <v>32437</v>
       </c>
       <c r="C119">
-        <v>33426</v>
+        <v>33965</v>
       </c>
       <c r="D119">
         <v>16658</v>
@@ -3460,7 +3460,7 @@
         <v>34412</v>
       </c>
       <c r="G119">
-        <v>40639</v>
+        <v>40669</v>
       </c>
       <c r="H119">
         <v>47008</v>
@@ -3474,22 +3474,22 @@
         <v>40706</v>
       </c>
       <c r="C120">
-        <v>14416</v>
+        <v>21142</v>
       </c>
       <c r="D120">
         <v>39589</v>
       </c>
       <c r="E120">
-        <v>42545</v>
+        <v>42548</v>
       </c>
       <c r="F120">
         <v>47493</v>
       </c>
       <c r="G120">
-        <v>42587</v>
+        <v>42686</v>
       </c>
       <c r="H120">
-        <v>48691</v>
+        <v>48692</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -3500,22 +3500,22 @@
         <v>40706</v>
       </c>
       <c r="C121">
-        <v>14416</v>
+        <v>21142</v>
       </c>
       <c r="D121">
         <v>39589</v>
       </c>
       <c r="E121">
-        <v>42545</v>
+        <v>42548</v>
       </c>
       <c r="F121">
         <v>47493</v>
       </c>
       <c r="G121">
-        <v>42587</v>
+        <v>42686</v>
       </c>
       <c r="H121">
-        <v>48691</v>
+        <v>48692</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -3526,7 +3526,7 @@
         <v>38281</v>
       </c>
       <c r="C122">
-        <v>22736</v>
+        <v>25111</v>
       </c>
       <c r="D122">
         <v>26463</v>
@@ -3538,7 +3538,7 @@
         <v>41088</v>
       </c>
       <c r="G122">
-        <v>36357</v>
+        <v>36595</v>
       </c>
       <c r="H122">
         <v>45228</v>
@@ -3552,7 +3552,7 @@
         <v>38301</v>
       </c>
       <c r="C123">
-        <v>22237</v>
+        <v>24675</v>
       </c>
       <c r="D123">
         <v>26532</v>
@@ -3564,7 +3564,7 @@
         <v>41117</v>
       </c>
       <c r="G123">
-        <v>36155</v>
+        <v>36399</v>
       </c>
       <c r="H123">
         <v>45143</v>
@@ -3578,7 +3578,7 @@
         <v>38281</v>
       </c>
       <c r="C124">
-        <v>22736</v>
+        <v>25111</v>
       </c>
       <c r="D124">
         <v>26463</v>
@@ -3590,7 +3590,7 @@
         <v>41088</v>
       </c>
       <c r="G124">
-        <v>36357</v>
+        <v>36595</v>
       </c>
       <c r="H124">
         <v>45228</v>
@@ -3604,19 +3604,19 @@
         <v>37469</v>
       </c>
       <c r="C125">
-        <v>22065</v>
+        <v>23916</v>
       </c>
       <c r="D125">
         <v>25294</v>
       </c>
       <c r="E125">
-        <v>42248</v>
+        <v>42251</v>
       </c>
       <c r="F125">
         <v>40309</v>
       </c>
       <c r="G125">
-        <v>35238</v>
+        <v>35335</v>
       </c>
       <c r="H125">
         <v>44457</v>
@@ -3630,19 +3630,19 @@
         <v>37486</v>
       </c>
       <c r="C126">
-        <v>30516</v>
+        <v>31420</v>
       </c>
       <c r="D126">
         <v>22802</v>
       </c>
       <c r="E126">
-        <v>46607</v>
+        <v>46609</v>
       </c>
       <c r="F126">
         <v>39689</v>
       </c>
       <c r="G126">
-        <v>40448</v>
+        <v>40517</v>
       </c>
       <c r="H126">
         <v>48131</v>
@@ -3656,22 +3656,22 @@
         <v>39584</v>
       </c>
       <c r="C127">
-        <v>31972</v>
+        <v>33806</v>
       </c>
       <c r="D127">
         <v>24436</v>
       </c>
       <c r="E127">
-        <v>49085</v>
+        <v>49095</v>
       </c>
       <c r="F127">
         <v>41751</v>
       </c>
       <c r="G127">
-        <v>42938</v>
+        <v>43148</v>
       </c>
       <c r="H127">
-        <v>50552</v>
+        <v>50555</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -3682,7 +3682,7 @@
         <v>40887</v>
       </c>
       <c r="C128">
-        <v>38769</v>
+        <v>39541</v>
       </c>
       <c r="D128">
         <v>23783</v>
@@ -3694,7 +3694,7 @@
         <v>42832</v>
       </c>
       <c r="G128">
-        <v>48414</v>
+        <v>48465</v>
       </c>
       <c r="H128">
         <v>53988</v>
@@ -3708,7 +3708,7 @@
         <v>40887</v>
       </c>
       <c r="C129">
-        <v>38769</v>
+        <v>39541</v>
       </c>
       <c r="D129">
         <v>23783</v>
@@ -3720,7 +3720,7 @@
         <v>42832</v>
       </c>
       <c r="G129">
-        <v>48414</v>
+        <v>48465</v>
       </c>
       <c r="H129">
         <v>53988</v>
@@ -3734,22 +3734,22 @@
         <v>44851</v>
       </c>
       <c r="C130">
-        <v>14468</v>
+        <v>21922</v>
       </c>
       <c r="D130">
         <v>41453</v>
       </c>
       <c r="E130">
-        <v>45897</v>
+        <v>45899</v>
       </c>
       <c r="F130">
         <v>50066</v>
       </c>
       <c r="G130">
-        <v>44375</v>
+        <v>44534</v>
       </c>
       <c r="H130">
-        <v>50768</v>
+        <v>50769</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -3760,22 +3760,22 @@
         <v>44958</v>
       </c>
       <c r="C131">
-        <v>10424</v>
+        <v>19061</v>
       </c>
       <c r="D131">
         <v>42083</v>
       </c>
       <c r="E131">
-        <v>45653</v>
+        <v>45656</v>
       </c>
       <c r="F131">
         <v>50292</v>
       </c>
       <c r="G131">
-        <v>44025</v>
+        <v>44210</v>
       </c>
       <c r="H131">
-        <v>50758</v>
+        <v>50760</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -3786,22 +3786,22 @@
         <v>44950</v>
       </c>
       <c r="C132">
-        <v>10726</v>
+        <v>19275</v>
       </c>
       <c r="D132">
         <v>42036</v>
       </c>
       <c r="E132">
-        <v>45671</v>
+        <v>45674</v>
       </c>
       <c r="F132">
         <v>50275</v>
       </c>
       <c r="G132">
-        <v>44051</v>
+        <v>44234</v>
       </c>
       <c r="H132">
-        <v>50759</v>
+        <v>50761</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -3812,22 +3812,22 @@
         <v>44912</v>
       </c>
       <c r="C133">
-        <v>12162</v>
+        <v>20291</v>
       </c>
       <c r="D133">
         <v>41812</v>
       </c>
       <c r="E133">
-        <v>45757</v>
+        <v>45761</v>
       </c>
       <c r="F133">
         <v>50195</v>
       </c>
       <c r="G133">
-        <v>44176</v>
+        <v>44349</v>
       </c>
       <c r="H133">
-        <v>50763</v>
+        <v>50764</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -3838,19 +3838,19 @@
         <v>43789</v>
       </c>
       <c r="C134">
-        <v>11330</v>
+        <v>18544</v>
       </c>
       <c r="D134">
         <v>42611</v>
       </c>
       <c r="E134">
-        <v>44708</v>
+        <v>44715</v>
       </c>
       <c r="F134">
         <v>50540</v>
       </c>
       <c r="G134">
-        <v>44542</v>
+        <v>44689</v>
       </c>
       <c r="H134">
         <v>51118</v>
@@ -3864,19 +3864,19 @@
         <v>45062</v>
       </c>
       <c r="C135">
-        <v>14683</v>
+        <v>21537</v>
       </c>
       <c r="D135">
         <v>39300</v>
       </c>
       <c r="E135">
-        <v>45996</v>
+        <v>45997</v>
       </c>
       <c r="F135">
         <v>49088</v>
       </c>
       <c r="G135">
-        <v>42452</v>
+        <v>42682</v>
       </c>
       <c r="H135">
         <v>49741</v>
@@ -3890,7 +3890,7 @@
         <v>44490</v>
       </c>
       <c r="C136">
-        <v>16307</v>
+        <v>21629</v>
       </c>
       <c r="D136">
         <v>36558</v>
@@ -3902,7 +3902,7 @@
         <v>47478</v>
       </c>
       <c r="G136">
-        <v>39958</v>
+        <v>40298</v>
       </c>
       <c r="H136">
         <v>48153</v>
@@ -3916,7 +3916,7 @@
         <v>44471</v>
       </c>
       <c r="C137">
-        <v>16949</v>
+        <v>22122</v>
       </c>
       <c r="D137">
         <v>36449</v>
@@ -3928,7 +3928,7 @@
         <v>47448</v>
       </c>
       <c r="G137">
-        <v>40060</v>
+        <v>40391</v>
       </c>
       <c r="H137">
         <v>48165</v>
@@ -3942,7 +3942,7 @@
         <v>44471</v>
       </c>
       <c r="C138">
-        <v>16949</v>
+        <v>22122</v>
       </c>
       <c r="D138">
         <v>36449</v>
@@ -3954,7 +3954,7 @@
         <v>47448</v>
       </c>
       <c r="G138">
-        <v>40060</v>
+        <v>40391</v>
       </c>
       <c r="H138">
         <v>48165</v>
@@ -3968,7 +3968,7 @@
         <v>43586</v>
       </c>
       <c r="C139">
-        <v>15993</v>
+        <v>21376</v>
       </c>
       <c r="D139">
         <v>37701</v>
@@ -3980,7 +3980,7 @@
         <v>47828</v>
       </c>
       <c r="G139">
-        <v>40999</v>
+        <v>41198</v>
       </c>
       <c r="H139">
         <v>48643</v>
@@ -3994,7 +3994,7 @@
         <v>42566</v>
       </c>
       <c r="C140">
-        <v>24744</v>
+        <v>26058</v>
       </c>
       <c r="D140">
         <v>26354</v>
@@ -4006,7 +4006,7 @@
         <v>43813</v>
       </c>
       <c r="G140">
-        <v>39925</v>
+        <v>40065</v>
       </c>
       <c r="H140">
         <v>48695</v>
@@ -4020,7 +4020,7 @@
         <v>43586</v>
       </c>
       <c r="C141">
-        <v>15993</v>
+        <v>21376</v>
       </c>
       <c r="D141">
         <v>37701</v>
@@ -4032,7 +4032,7 @@
         <v>47828</v>
       </c>
       <c r="G141">
-        <v>40999</v>
+        <v>41198</v>
       </c>
       <c r="H141">
         <v>48643</v>
@@ -4046,7 +4046,7 @@
         <v>43596</v>
       </c>
       <c r="C142">
-        <v>15703</v>
+        <v>21156</v>
       </c>
       <c r="D142">
         <v>37750</v>
@@ -4058,7 +4058,7 @@
         <v>47845</v>
       </c>
       <c r="G142">
-        <v>40962</v>
+        <v>41164</v>
       </c>
       <c r="H142">
         <v>48639</v>
@@ -4072,7 +4072,7 @@
         <v>41926</v>
       </c>
       <c r="C143">
-        <v>17908</v>
+        <v>21308</v>
       </c>
       <c r="D143">
         <v>29811</v>
@@ -4084,7 +4084,7 @@
         <v>44377</v>
       </c>
       <c r="G143">
-        <v>36315</v>
+        <v>36674</v>
       </c>
       <c r="H143">
         <v>46513</v>
@@ -4098,7 +4098,7 @@
         <v>41782</v>
       </c>
       <c r="C144">
-        <v>23643</v>
+        <v>26258</v>
       </c>
       <c r="D144">
         <v>28898</v>
@@ -4110,7 +4110,7 @@
         <v>44151</v>
       </c>
       <c r="G144">
-        <v>38351</v>
+        <v>38627</v>
       </c>
       <c r="H144">
         <v>47259</v>
@@ -4124,7 +4124,7 @@
         <v>41782</v>
       </c>
       <c r="C145">
-        <v>23643</v>
+        <v>26258</v>
       </c>
       <c r="D145">
         <v>28898</v>
@@ -4136,7 +4136,7 @@
         <v>44151</v>
       </c>
       <c r="G145">
-        <v>38351</v>
+        <v>38627</v>
       </c>
       <c r="H145">
         <v>47259</v>
@@ -4150,7 +4150,7 @@
         <v>41076</v>
       </c>
       <c r="C146">
-        <v>36817</v>
+        <v>37679</v>
       </c>
       <c r="D146">
         <v>24351</v>
@@ -4162,7 +4162,7 @@
         <v>43076</v>
       </c>
       <c r="G146">
-        <v>47497</v>
+        <v>47553</v>
       </c>
       <c r="H146">
         <v>53551</v>
@@ -4176,7 +4176,7 @@
         <v>43038</v>
       </c>
       <c r="C147">
-        <v>30371</v>
+        <v>31784</v>
       </c>
       <c r="D147">
         <v>25253</v>
@@ -4188,7 +4188,7 @@
         <v>44357</v>
       </c>
       <c r="G147">
-        <v>40936</v>
+        <v>41155</v>
       </c>
       <c r="H147">
         <v>48860</v>
@@ -4202,7 +4202,7 @@
         <v>42725</v>
       </c>
       <c r="C148">
-        <v>23187</v>
+        <v>25859</v>
       </c>
       <c r="D148">
         <v>27814</v>
@@ -4214,7 +4214,7 @@
         <v>44386</v>
       </c>
       <c r="G148">
-        <v>36986</v>
+        <v>37374</v>
       </c>
       <c r="H148">
         <v>46372</v>
@@ -4228,7 +4228,7 @@
         <v>41550</v>
       </c>
       <c r="C149">
-        <v>13832</v>
+        <v>18656</v>
       </c>
       <c r="D149">
         <v>32618</v>
@@ -4240,7 +4240,7 @@
         <v>44886</v>
       </c>
       <c r="G149">
-        <v>36082</v>
+        <v>36447</v>
       </c>
       <c r="H149">
         <v>45492</v>
@@ -4254,7 +4254,7 @@
         <v>41550</v>
       </c>
       <c r="C150">
-        <v>13832</v>
+        <v>18656</v>
       </c>
       <c r="D150">
         <v>32618</v>
@@ -4266,7 +4266,7 @@
         <v>44886</v>
       </c>
       <c r="G150">
-        <v>36082</v>
+        <v>36447</v>
       </c>
       <c r="H150">
         <v>45492</v>
@@ -4280,7 +4280,7 @@
         <v>41586</v>
       </c>
       <c r="C151">
-        <v>12873</v>
+        <v>17921</v>
       </c>
       <c r="D151">
         <v>32782</v>
@@ -4292,7 +4292,7 @@
         <v>44944</v>
       </c>
       <c r="G151">
-        <v>35921</v>
+        <v>36302</v>
       </c>
       <c r="H151">
         <v>45493</v>
@@ -4306,7 +4306,7 @@
         <v>41550</v>
       </c>
       <c r="C152">
-        <v>13832</v>
+        <v>18656</v>
       </c>
       <c r="D152">
         <v>32618</v>
@@ -4318,7 +4318,7 @@
         <v>44886</v>
       </c>
       <c r="G152">
-        <v>36082</v>
+        <v>36447</v>
       </c>
       <c r="H152">
         <v>45492</v>
@@ -4332,7 +4332,7 @@
         <v>37565</v>
       </c>
       <c r="C153">
-        <v>34161</v>
+        <v>34788</v>
       </c>
       <c r="D153">
         <v>23543</v>
@@ -4344,7 +4344,7 @@
         <v>39289</v>
       </c>
       <c r="G153">
-        <v>43377</v>
+        <v>43396</v>
       </c>
       <c r="H153">
         <v>47896</v>
@@ -4358,7 +4358,7 @@
         <v>37565</v>
       </c>
       <c r="C154">
-        <v>34161</v>
+        <v>34788</v>
       </c>
       <c r="D154">
         <v>23543</v>
@@ -4370,7 +4370,7 @@
         <v>39289</v>
       </c>
       <c r="G154">
-        <v>43377</v>
+        <v>43396</v>
       </c>
       <c r="H154">
         <v>47896</v>
@@ -4384,7 +4384,7 @@
         <v>37440</v>
       </c>
       <c r="C155">
-        <v>20188</v>
+        <v>22320</v>
       </c>
       <c r="D155">
         <v>22435</v>
@@ -4396,7 +4396,7 @@
         <v>38969</v>
       </c>
       <c r="G155">
-        <v>31416</v>
+        <v>31745</v>
       </c>
       <c r="H155">
         <v>41187</v>
@@ -4410,7 +4410,7 @@
         <v>37440</v>
       </c>
       <c r="C156">
-        <v>20188</v>
+        <v>22320</v>
       </c>
       <c r="D156">
         <v>22435</v>
@@ -4422,7 +4422,7 @@
         <v>38969</v>
       </c>
       <c r="G156">
-        <v>31416</v>
+        <v>31745</v>
       </c>
       <c r="H156">
         <v>41187</v>
@@ -4436,7 +4436,7 @@
         <v>37610</v>
       </c>
       <c r="C157">
-        <v>26940</v>
+        <v>28069</v>
       </c>
       <c r="D157">
         <v>20314</v>
@@ -4448,7 +4448,7 @@
         <v>38783</v>
       </c>
       <c r="G157">
-        <v>35522</v>
+        <v>35687</v>
       </c>
       <c r="H157">
         <v>43670</v>
@@ -4462,7 +4462,7 @@
         <v>39041</v>
       </c>
       <c r="C158">
-        <v>20408</v>
+        <v>23114</v>
       </c>
       <c r="D158">
         <v>26663</v>
@@ -4474,7 +4474,7 @@
         <v>41139</v>
       </c>
       <c r="G158">
-        <v>34736</v>
+        <v>34983</v>
       </c>
       <c r="H158">
         <v>43322</v>
@@ -4488,7 +4488,7 @@
         <v>39437</v>
       </c>
       <c r="C159">
-        <v>12780</v>
+        <v>17289</v>
       </c>
       <c r="D159">
         <v>30413</v>
@@ -4500,7 +4500,7 @@
         <v>42659</v>
       </c>
       <c r="G159">
-        <v>33850</v>
+        <v>34190</v>
       </c>
       <c r="H159">
         <v>43305</v>
@@ -4514,7 +4514,7 @@
         <v>36533</v>
       </c>
       <c r="C160">
-        <v>18877</v>
+        <v>21286</v>
       </c>
       <c r="D160">
         <v>23661</v>
@@ -4526,7 +4526,7 @@
         <v>38445</v>
       </c>
       <c r="G160">
-        <v>31791</v>
+        <v>32019</v>
       </c>
       <c r="H160">
         <v>40720</v>
@@ -4540,7 +4540,7 @@
         <v>35623</v>
       </c>
       <c r="C161">
-        <v>25883</v>
+        <v>26928</v>
       </c>
       <c r="D161">
         <v>22229</v>
@@ -4552,7 +4552,7 @@
         <v>37232</v>
       </c>
       <c r="G161">
-        <v>35830</v>
+        <v>35888</v>
       </c>
       <c r="H161">
         <v>42880</v>
@@ -4566,7 +4566,7 @@
         <v>35625</v>
       </c>
       <c r="C162">
-        <v>32238</v>
+        <v>33078</v>
       </c>
       <c r="D162">
         <v>19554</v>
@@ -4578,7 +4578,7 @@
         <v>37206</v>
       </c>
       <c r="G162">
-        <v>40678</v>
+        <v>40706</v>
       </c>
       <c r="H162">
         <v>46243</v>
@@ -4592,7 +4592,7 @@
         <v>40045</v>
       </c>
       <c r="C163">
-        <v>12799</v>
+        <v>16579</v>
       </c>
       <c r="D163">
         <v>30376</v>
@@ -4604,7 +4604,7 @@
         <v>43383</v>
       </c>
       <c r="G163">
-        <v>33779</v>
+        <v>33895</v>
       </c>
       <c r="H163">
         <v>44062</v>
@@ -4618,7 +4618,7 @@
         <v>39672</v>
       </c>
       <c r="C164">
-        <v>20508</v>
+        <v>22635</v>
       </c>
       <c r="D164">
         <v>26455</v>
@@ -4630,7 +4630,7 @@
         <v>41879</v>
       </c>
       <c r="G164">
-        <v>34616</v>
+        <v>34712</v>
       </c>
       <c r="H164">
         <v>44208</v>
@@ -4644,7 +4644,7 @@
         <v>36869</v>
       </c>
       <c r="C165">
-        <v>18573</v>
+        <v>20230</v>
       </c>
       <c r="D165">
         <v>22464</v>
@@ -4656,7 +4656,7 @@
         <v>38844</v>
       </c>
       <c r="G165">
-        <v>30607</v>
+        <v>30670</v>
       </c>
       <c r="H165">
         <v>41144</v>
@@ -4670,7 +4670,7 @@
         <v>36869</v>
       </c>
       <c r="C166">
-        <v>18573</v>
+        <v>20230</v>
       </c>
       <c r="D166">
         <v>22464</v>
@@ -4682,7 +4682,7 @@
         <v>38844</v>
       </c>
       <c r="G166">
-        <v>30607</v>
+        <v>30670</v>
       </c>
       <c r="H166">
         <v>41144</v>
@@ -4696,7 +4696,7 @@
         <v>34464</v>
       </c>
       <c r="C167">
-        <v>26415</v>
+        <v>27902</v>
       </c>
       <c r="D167">
         <v>20265</v>
@@ -4708,7 +4708,7 @@
         <v>36458</v>
       </c>
       <c r="G167">
-        <v>35666</v>
+        <v>35772</v>
       </c>
       <c r="H167">
         <v>43384</v>
@@ -4722,7 +4722,7 @@
         <v>33190</v>
       </c>
       <c r="C168">
-        <v>35620</v>
+        <v>36320</v>
       </c>
       <c r="D168">
         <v>15309</v>
@@ -4734,7 +4734,7 @@
         <v>34265</v>
       </c>
       <c r="G168">
-        <v>41931</v>
+        <v>41962</v>
       </c>
       <c r="H168">
         <v>47921</v>
@@ -4748,19 +4748,19 @@
         <v>43840</v>
       </c>
       <c r="C169">
-        <v>15442</v>
+        <v>22515</v>
       </c>
       <c r="D169">
         <v>39402</v>
       </c>
       <c r="E169">
-        <v>45275</v>
+        <v>45276</v>
       </c>
       <c r="F169">
         <v>48503</v>
       </c>
       <c r="G169">
-        <v>42796</v>
+        <v>43035</v>
       </c>
       <c r="H169">
         <v>49533</v>
@@ -4774,7 +4774,7 @@
         <v>44824</v>
       </c>
       <c r="C170">
-        <v>13050</v>
+        <v>20165</v>
       </c>
       <c r="D170">
         <v>39731</v>
@@ -4786,7 +4786,7 @@
         <v>49117</v>
       </c>
       <c r="G170">
-        <v>42274</v>
+        <v>42455</v>
       </c>
       <c r="H170">
         <v>49611</v>
@@ -4800,19 +4800,19 @@
         <v>43833</v>
       </c>
       <c r="C171">
-        <v>15659</v>
+        <v>22672</v>
       </c>
       <c r="D171">
         <v>39370</v>
       </c>
       <c r="E171">
-        <v>45294</v>
+        <v>45296</v>
       </c>
       <c r="F171">
         <v>48491</v>
       </c>
       <c r="G171">
-        <v>42825</v>
+        <v>43062</v>
       </c>
       <c r="H171">
         <v>49540</v>
@@ -4826,7 +4826,7 @@
         <v>44779</v>
       </c>
       <c r="C172">
-        <v>14651</v>
+        <v>21316</v>
       </c>
       <c r="D172">
         <v>39480</v>
@@ -4838,7 +4838,7 @@
         <v>49032</v>
       </c>
       <c r="G172">
-        <v>42429</v>
+        <v>42598</v>
       </c>
       <c r="H172">
         <v>49605</v>
@@ -4852,7 +4852,7 @@
         <v>44860</v>
       </c>
       <c r="C173">
-        <v>11740</v>
+        <v>19224</v>
       </c>
       <c r="D173">
         <v>39936</v>
@@ -4864,7 +4864,7 @@
         <v>49186</v>
       </c>
       <c r="G173">
-        <v>42147</v>
+        <v>42337</v>
       </c>
       <c r="H173">
         <v>49616</v>
@@ -4878,19 +4878,19 @@
         <v>45348</v>
       </c>
       <c r="C174">
-        <v>10996</v>
+        <v>18237</v>
       </c>
       <c r="D174">
         <v>40908</v>
       </c>
       <c r="E174">
-        <v>45895</v>
+        <v>45897</v>
       </c>
       <c r="F174">
         <v>49590</v>
       </c>
       <c r="G174">
-        <v>42765</v>
+        <v>42865</v>
       </c>
       <c r="H174">
         <v>49954</v>
@@ -4904,19 +4904,19 @@
         <v>43480</v>
       </c>
       <c r="C175">
-        <v>31367</v>
+        <v>33929</v>
       </c>
       <c r="D175">
         <v>27586</v>
       </c>
       <c r="E175">
-        <v>49255</v>
+        <v>49256</v>
       </c>
       <c r="F175">
         <v>44789</v>
       </c>
       <c r="G175">
-        <v>43064</v>
+        <v>43271</v>
       </c>
       <c r="H175">
         <v>50220</v>
@@ -4930,19 +4930,19 @@
         <v>43164</v>
       </c>
       <c r="C176">
-        <v>23808</v>
+        <v>27838</v>
       </c>
       <c r="D176">
         <v>29788</v>
       </c>
       <c r="E176">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="F176">
         <v>44764</v>
       </c>
       <c r="G176">
-        <v>38779</v>
+        <v>39106</v>
       </c>
       <c r="H176">
         <v>47281</v>
@@ -4956,19 +4956,19 @@
         <v>43164</v>
       </c>
       <c r="C177">
-        <v>23808</v>
+        <v>27838</v>
       </c>
       <c r="D177">
         <v>29788</v>
       </c>
       <c r="E177">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="F177">
         <v>44764</v>
       </c>
       <c r="G177">
-        <v>38779</v>
+        <v>39106</v>
       </c>
       <c r="H177">
         <v>47281</v>
@@ -4982,7 +4982,7 @@
         <v>44546</v>
       </c>
       <c r="C178">
-        <v>15863</v>
+        <v>21054</v>
       </c>
       <c r="D178">
         <v>34856</v>
@@ -4994,7 +4994,7 @@
         <v>46837</v>
       </c>
       <c r="G178">
-        <v>38572</v>
+        <v>38911</v>
       </c>
       <c r="H178">
         <v>47535</v>
@@ -5008,7 +5008,7 @@
         <v>43716</v>
       </c>
       <c r="C179">
-        <v>23869</v>
+        <v>26847</v>
       </c>
       <c r="D179">
         <v>30880</v>
@@ -5020,7 +5020,7 @@
         <v>45227</v>
       </c>
       <c r="G179">
-        <v>39317</v>
+        <v>39584</v>
       </c>
       <c r="H179">
         <v>47346</v>
@@ -5034,7 +5034,7 @@
         <v>43360</v>
       </c>
       <c r="C180">
-        <v>40669</v>
+        <v>41441</v>
       </c>
       <c r="D180">
         <v>22362</v>
@@ -5046,7 +5046,7 @@
         <v>44117</v>
       </c>
       <c r="G180">
-        <v>49056</v>
+        <v>49097</v>
       </c>
       <c r="H180">
         <v>54212</v>
@@ -5060,7 +5060,7 @@
         <v>43360</v>
       </c>
       <c r="C181">
-        <v>40669</v>
+        <v>41441</v>
       </c>
       <c r="D181">
         <v>22362</v>
@@ -5072,7 +5072,7 @@
         <v>44117</v>
       </c>
       <c r="G181">
-        <v>49056</v>
+        <v>49097</v>
       </c>
       <c r="H181">
         <v>54212</v>
@@ -5086,7 +5086,7 @@
         <v>37871</v>
       </c>
       <c r="C182">
-        <v>35618</v>
+        <v>36350</v>
       </c>
       <c r="D182">
         <v>16802</v>
@@ -5098,7 +5098,7 @@
         <v>38745</v>
       </c>
       <c r="G182">
-        <v>42666</v>
+        <v>42695</v>
       </c>
       <c r="H182">
         <v>48672</v>
@@ -5112,7 +5112,7 @@
         <v>37978</v>
       </c>
       <c r="C183">
-        <v>32118</v>
+        <v>32585</v>
       </c>
       <c r="D183">
         <v>14272</v>
@@ -5124,7 +5124,7 @@
         <v>38497</v>
       </c>
       <c r="G183">
-        <v>38182</v>
+        <v>38201</v>
       </c>
       <c r="H183">
         <v>45692</v>
@@ -5138,7 +5138,7 @@
         <v>41064</v>
       </c>
       <c r="C184">
-        <v>29032</v>
+        <v>30616</v>
       </c>
       <c r="D184">
         <v>23274</v>
@@ -5150,7 +5150,7 @@
         <v>42087</v>
       </c>
       <c r="G184">
-        <v>39282</v>
+        <v>39424</v>
       </c>
       <c r="H184">
         <v>47544</v>
@@ -5164,7 +5164,7 @@
         <v>41064</v>
       </c>
       <c r="C185">
-        <v>29032</v>
+        <v>30616</v>
       </c>
       <c r="D185">
         <v>23274</v>
@@ -5176,7 +5176,7 @@
         <v>42087</v>
       </c>
       <c r="G185">
-        <v>39282</v>
+        <v>39424</v>
       </c>
       <c r="H185">
         <v>47544</v>
@@ -5190,7 +5190,7 @@
         <v>37342</v>
       </c>
       <c r="C186">
-        <v>33483</v>
+        <v>34444</v>
       </c>
       <c r="D186">
         <v>20432</v>
@@ -5202,7 +5202,7 @@
         <v>38653</v>
       </c>
       <c r="G186">
-        <v>42295</v>
+        <v>42310</v>
       </c>
       <c r="H186">
         <v>48116</v>
@@ -5216,7 +5216,7 @@
         <v>38432</v>
       </c>
       <c r="C187">
-        <v>26865</v>
+        <v>28443</v>
       </c>
       <c r="D187">
         <v>22444</v>
@@ -5228,7 +5228,7 @@
         <v>39623</v>
       </c>
       <c r="G187">
-        <v>37269</v>
+        <v>37359</v>
       </c>
       <c r="H187">
         <v>45091</v>
@@ -5242,7 +5242,7 @@
         <v>36259</v>
       </c>
       <c r="C188">
-        <v>33090</v>
+        <v>34043</v>
       </c>
       <c r="D188">
         <v>18460</v>
@@ -5254,7 +5254,7 @@
         <v>37487</v>
       </c>
       <c r="G188">
-        <v>40788</v>
+        <v>40824</v>
       </c>
       <c r="H188">
         <v>46936</v>
@@ -5268,7 +5268,7 @@
         <v>36285</v>
       </c>
       <c r="C189">
-        <v>35618</v>
+        <v>36405</v>
       </c>
       <c r="D189">
         <v>15504</v>
@@ -5280,7 +5280,7 @@
         <v>36925</v>
       </c>
       <c r="G189">
-        <v>41821</v>
+        <v>41854</v>
       </c>
       <c r="H189">
         <v>48116</v>
@@ -5294,7 +5294,7 @@
         <v>36285</v>
       </c>
       <c r="C190">
-        <v>35618</v>
+        <v>36405</v>
       </c>
       <c r="D190">
         <v>15504</v>
@@ -5306,7 +5306,7 @@
         <v>36925</v>
       </c>
       <c r="G190">
-        <v>41821</v>
+        <v>41854</v>
       </c>
       <c r="H190">
         <v>48116</v>
@@ -5320,7 +5320,7 @@
         <v>40656</v>
       </c>
       <c r="C191">
-        <v>29497</v>
+        <v>31400</v>
       </c>
       <c r="D191">
         <v>23568</v>
@@ -5332,10 +5332,10 @@
         <v>41805</v>
       </c>
       <c r="G191">
-        <v>40033</v>
+        <v>40231</v>
       </c>
       <c r="H191">
-        <v>47842</v>
+        <v>47843</v>
       </c>
     </row>
     <row r="192" spans="1:8">
@@ -5346,7 +5346,7 @@
         <v>38432</v>
       </c>
       <c r="C192">
-        <v>26865</v>
+        <v>28443</v>
       </c>
       <c r="D192">
         <v>22444</v>
@@ -5358,7 +5358,7 @@
         <v>39623</v>
       </c>
       <c r="G192">
-        <v>37269</v>
+        <v>37359</v>
       </c>
       <c r="H192">
         <v>45091</v>
@@ -5372,7 +5372,7 @@
         <v>42533</v>
       </c>
       <c r="C193">
-        <v>15020</v>
+        <v>20441</v>
       </c>
       <c r="D193">
         <v>37701</v>
@@ -5384,7 +5384,7 @@
         <v>47297</v>
       </c>
       <c r="G193">
-        <v>40856</v>
+        <v>41015</v>
       </c>
       <c r="H193">
         <v>48213</v>
@@ -5398,7 +5398,7 @@
         <v>42642</v>
       </c>
       <c r="C194">
-        <v>12065</v>
+        <v>18199</v>
       </c>
       <c r="D194">
         <v>38191</v>
@@ -5410,7 +5410,7 @@
         <v>47495</v>
       </c>
       <c r="G194">
-        <v>40505</v>
+        <v>40685</v>
       </c>
       <c r="H194">
         <v>48167</v>
@@ -5424,19 +5424,19 @@
         <v>43849</v>
       </c>
       <c r="C195">
-        <v>15114</v>
+        <v>22279</v>
       </c>
       <c r="D195">
         <v>39451</v>
       </c>
       <c r="E195">
-        <v>45246</v>
+        <v>45247</v>
       </c>
       <c r="F195">
         <v>48521</v>
       </c>
       <c r="G195">
-        <v>42753</v>
+        <v>42995</v>
       </c>
       <c r="H195">
         <v>49523</v>
@@ -5450,7 +5450,7 @@
         <v>41861</v>
       </c>
       <c r="C196">
-        <v>14715</v>
+        <v>19966</v>
       </c>
       <c r="D196">
         <v>32593</v>
@@ -5462,7 +5462,7 @@
         <v>44916</v>
       </c>
       <c r="G196">
-        <v>36494</v>
+        <v>36882</v>
       </c>
       <c r="H196">
         <v>45864</v>
@@ -5476,7 +5476,7 @@
         <v>41043</v>
       </c>
       <c r="C197">
-        <v>15025</v>
+        <v>19206</v>
       </c>
       <c r="D197">
         <v>33405</v>
@@ -5488,7 +5488,7 @@
         <v>44447</v>
       </c>
       <c r="G197">
-        <v>36835</v>
+        <v>37086</v>
       </c>
       <c r="H197">
         <v>45340</v>
@@ -5502,7 +5502,7 @@
         <v>41098</v>
       </c>
       <c r="C198">
-        <v>13644</v>
+        <v>18107</v>
       </c>
       <c r="D198">
         <v>33626</v>
@@ -5514,7 +5514,7 @@
         <v>44533</v>
       </c>
       <c r="G198">
-        <v>36586</v>
+        <v>36855</v>
       </c>
       <c r="H198">
         <v>45304</v>
@@ -5528,7 +5528,7 @@
         <v>40645</v>
       </c>
       <c r="C199">
-        <v>21804</v>
+        <v>24335</v>
       </c>
       <c r="D199">
         <v>29918</v>
@@ -5540,7 +5540,7 @@
         <v>42955</v>
       </c>
       <c r="G199">
-        <v>37498</v>
+        <v>37714</v>
       </c>
       <c r="H199">
         <v>45509</v>
@@ -5554,7 +5554,7 @@
         <v>40621</v>
       </c>
       <c r="C200">
-        <v>22899</v>
+        <v>25284</v>
       </c>
       <c r="D200">
         <v>29756</v>
@@ -5566,7 +5566,7 @@
         <v>42915</v>
       </c>
       <c r="G200">
-        <v>37851</v>
+        <v>38055</v>
       </c>
       <c r="H200">
         <v>45643</v>
@@ -5580,7 +5580,7 @@
         <v>39280</v>
       </c>
       <c r="C201">
-        <v>26194</v>
+        <v>28388</v>
       </c>
       <c r="D201">
         <v>28800</v>
@@ -5592,7 +5592,7 @@
         <v>41784</v>
       </c>
       <c r="G201">
-        <v>41347</v>
+        <v>41415</v>
       </c>
       <c r="H201">
         <v>47769</v>
@@ -5606,7 +5606,7 @@
         <v>37478</v>
       </c>
       <c r="C202">
-        <v>30620</v>
+        <v>31623</v>
       </c>
       <c r="D202">
         <v>24351</v>
@@ -5618,7 +5618,7 @@
         <v>39781</v>
       </c>
       <c r="G202">
-        <v>43066</v>
+        <v>43110</v>
       </c>
       <c r="H202">
         <v>49049</v>
@@ -5632,7 +5632,7 @@
         <v>41421</v>
       </c>
       <c r="C203">
-        <v>22888</v>
+        <v>26040</v>
       </c>
       <c r="D203">
         <v>29018</v>
@@ -5644,7 +5644,7 @@
         <v>43558</v>
       </c>
       <c r="G203">
-        <v>37886</v>
+        <v>38167</v>
       </c>
       <c r="H203">
         <v>46329</v>
@@ -5658,22 +5658,22 @@
         <v>38903</v>
       </c>
       <c r="C204">
-        <v>22350</v>
+        <v>24729</v>
       </c>
       <c r="D204">
         <v>25902</v>
       </c>
       <c r="E204">
-        <v>42487</v>
+        <v>42490</v>
       </c>
       <c r="F204">
         <v>40802</v>
       </c>
       <c r="G204">
-        <v>35295</v>
+        <v>35597</v>
       </c>
       <c r="H204">
-        <v>44029</v>
+        <v>44032</v>
       </c>
     </row>
     <row r="205" spans="1:8">
@@ -5684,22 +5684,22 @@
         <v>39069</v>
       </c>
       <c r="C205">
-        <v>30037</v>
+        <v>31291</v>
       </c>
       <c r="D205">
         <v>23740</v>
       </c>
       <c r="E205">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="F205">
         <v>40590</v>
       </c>
       <c r="G205">
-        <v>40006</v>
+        <v>40175</v>
       </c>
       <c r="H205">
-        <v>47294</v>
+        <v>47296</v>
       </c>
     </row>
     <row r="206" spans="1:8">
@@ -5710,19 +5710,19 @@
         <v>19132</v>
       </c>
       <c r="C206">
-        <v>7494</v>
+        <v>10549</v>
       </c>
       <c r="D206">
         <v>23547</v>
       </c>
       <c r="E206">
-        <v>20882</v>
+        <v>20891</v>
       </c>
       <c r="F206">
         <v>27291</v>
       </c>
       <c r="G206">
-        <v>25329</v>
+        <v>25379</v>
       </c>
       <c r="H206">
         <v>28289</v>
@@ -5736,19 +5736,19 @@
         <v>18686</v>
       </c>
       <c r="C207">
-        <v>6680</v>
+        <v>9865</v>
       </c>
       <c r="D207">
         <v>20162</v>
       </c>
       <c r="E207">
-        <v>19959</v>
+        <v>19960</v>
       </c>
       <c r="F207">
         <v>24566</v>
       </c>
       <c r="G207">
-        <v>21905</v>
+        <v>21979</v>
       </c>
       <c r="H207">
         <v>25347</v>
@@ -5762,19 +5762,19 @@
         <v>18686</v>
       </c>
       <c r="C208">
-        <v>6680</v>
+        <v>9865</v>
       </c>
       <c r="D208">
         <v>20162</v>
       </c>
       <c r="E208">
-        <v>19959</v>
+        <v>19960</v>
       </c>
       <c r="F208">
         <v>24566</v>
       </c>
       <c r="G208">
-        <v>21905</v>
+        <v>21979</v>
       </c>
       <c r="H208">
         <v>25347</v>
@@ -5788,19 +5788,19 @@
         <v>19186</v>
       </c>
       <c r="C209">
-        <v>6344</v>
+        <v>9672</v>
       </c>
       <c r="D209">
         <v>23764</v>
       </c>
       <c r="E209">
-        <v>20619</v>
+        <v>20629</v>
       </c>
       <c r="F209">
         <v>27453</v>
       </c>
       <c r="G209">
-        <v>25225</v>
+        <v>25279</v>
       </c>
       <c r="H209">
         <v>28270</v>
@@ -5814,19 +5814,19 @@
         <v>18686</v>
       </c>
       <c r="C210">
-        <v>6680</v>
+        <v>9865</v>
       </c>
       <c r="D210">
         <v>20162</v>
       </c>
       <c r="E210">
-        <v>19959</v>
+        <v>19960</v>
       </c>
       <c r="F210">
         <v>24566</v>
       </c>
       <c r="G210">
-        <v>21905</v>
+        <v>21979</v>
       </c>
       <c r="H210">
         <v>25347</v>
@@ -5840,7 +5840,7 @@
         <v>18898</v>
       </c>
       <c r="C211">
-        <v>11502</v>
+        <v>13446</v>
       </c>
       <c r="D211">
         <v>17408</v>
@@ -5852,7 +5852,7 @@
         <v>22960</v>
       </c>
       <c r="G211">
-        <v>21906</v>
+        <v>21966</v>
       </c>
       <c r="H211">
         <v>25375</v>
@@ -5866,19 +5866,19 @@
         <v>20101</v>
       </c>
       <c r="C212">
-        <v>12990</v>
+        <v>14974</v>
       </c>
       <c r="D212">
         <v>19116</v>
       </c>
       <c r="E212">
-        <v>24509</v>
+        <v>24511</v>
       </c>
       <c r="F212">
         <v>24631</v>
       </c>
       <c r="G212">
-        <v>24475</v>
+        <v>24515</v>
       </c>
       <c r="H212">
         <v>28035</v>
@@ -5892,19 +5892,19 @@
         <v>18686</v>
       </c>
       <c r="C213">
-        <v>6680</v>
+        <v>9865</v>
       </c>
       <c r="D213">
         <v>20162</v>
       </c>
       <c r="E213">
-        <v>19959</v>
+        <v>19960</v>
       </c>
       <c r="F213">
         <v>24566</v>
       </c>
       <c r="G213">
-        <v>21905</v>
+        <v>21979</v>
       </c>
       <c r="H213">
         <v>25347</v>
@@ -5918,7 +5918,7 @@
         <v>18260</v>
       </c>
       <c r="C214">
-        <v>9814</v>
+        <v>11179</v>
       </c>
       <c r="D214">
         <v>15230</v>
@@ -5930,7 +5930,7 @@
         <v>21246</v>
       </c>
       <c r="G214">
-        <v>18997</v>
+        <v>19037</v>
       </c>
       <c r="H214">
         <v>22770</v>
@@ -5944,7 +5944,7 @@
         <v>18260</v>
       </c>
       <c r="C215">
-        <v>9814</v>
+        <v>11179</v>
       </c>
       <c r="D215">
         <v>15230</v>
@@ -5956,7 +5956,7 @@
         <v>21246</v>
       </c>
       <c r="G215">
-        <v>18997</v>
+        <v>19037</v>
       </c>
       <c r="H215">
         <v>22770</v>
@@ -5970,7 +5970,7 @@
         <v>17930</v>
       </c>
       <c r="C216">
-        <v>10143</v>
+        <v>11134</v>
       </c>
       <c r="D216">
         <v>12435</v>
@@ -5982,7 +5982,7 @@
         <v>19908</v>
       </c>
       <c r="G216">
-        <v>16902</v>
+        <v>17016</v>
       </c>
       <c r="H216">
         <v>21461</v>
@@ -5996,7 +5996,7 @@
         <v>17846</v>
       </c>
       <c r="C217">
-        <v>10508</v>
+        <v>11572</v>
       </c>
       <c r="D217">
         <v>15310</v>
@@ -6008,7 +6008,7 @@
         <v>20734</v>
       </c>
       <c r="G217">
-        <v>19218</v>
+        <v>19261</v>
       </c>
       <c r="H217">
         <v>22575</v>
@@ -6022,7 +6022,7 @@
         <v>17878</v>
       </c>
       <c r="C218">
-        <v>15137</v>
+        <v>15786</v>
       </c>
       <c r="D218">
         <v>13861</v>
@@ -6034,7 +6034,7 @@
         <v>20121</v>
       </c>
       <c r="G218">
-        <v>21791</v>
+        <v>21814</v>
       </c>
       <c r="H218">
         <v>24601</v>
@@ -6048,7 +6048,7 @@
         <v>20954</v>
       </c>
       <c r="C219">
-        <v>12566</v>
+        <v>13688</v>
       </c>
       <c r="D219">
         <v>17541</v>
@@ -6060,7 +6060,7 @@
         <v>25012</v>
       </c>
       <c r="G219">
-        <v>22798</v>
+        <v>22850</v>
       </c>
       <c r="H219">
         <v>27919</v>
@@ -6074,19 +6074,19 @@
         <v>20016</v>
       </c>
       <c r="C220">
-        <v>13745</v>
+        <v>15733</v>
       </c>
       <c r="D220">
         <v>17784</v>
       </c>
       <c r="E220">
-        <v>25217</v>
+        <v>25225</v>
       </c>
       <c r="F220">
         <v>24115</v>
       </c>
       <c r="G220">
-        <v>24260</v>
+        <v>24327</v>
       </c>
       <c r="H220">
         <v>28286</v>
@@ -6100,7 +6100,7 @@
         <v>22021</v>
       </c>
       <c r="C221">
-        <v>19344</v>
+        <v>19826</v>
       </c>
       <c r="D221">
         <v>16274</v>
@@ -6112,7 +6112,7 @@
         <v>25749</v>
       </c>
       <c r="G221">
-        <v>27655</v>
+        <v>27685</v>
       </c>
       <c r="H221">
         <v>32643</v>
@@ -6126,7 +6126,7 @@
         <v>20954</v>
       </c>
       <c r="C222">
-        <v>12566</v>
+        <v>13688</v>
       </c>
       <c r="D222">
         <v>17541</v>
@@ -6138,7 +6138,7 @@
         <v>25012</v>
       </c>
       <c r="G222">
-        <v>22798</v>
+        <v>22850</v>
       </c>
       <c r="H222">
         <v>27919</v>
@@ -6152,7 +6152,7 @@
         <v>20781</v>
       </c>
       <c r="C223">
-        <v>29137</v>
+        <v>29352</v>
       </c>
       <c r="D223">
         <v>12127</v>
@@ -6164,7 +6164,7 @@
         <v>22620</v>
       </c>
       <c r="G223">
-        <v>34601</v>
+        <v>34606</v>
       </c>
       <c r="H223">
         <v>38436</v>
@@ -6178,7 +6178,7 @@
         <v>17068</v>
       </c>
       <c r="C224">
-        <v>17125</v>
+        <v>17443</v>
       </c>
       <c r="D224">
         <v>8785</v>
@@ -6190,7 +6190,7 @@
         <v>19228</v>
       </c>
       <c r="G224">
-        <v>21354</v>
+        <v>21531</v>
       </c>
       <c r="H224">
         <v>24980</v>
@@ -6204,7 +6204,7 @@
         <v>17542</v>
       </c>
       <c r="C225">
-        <v>9174</v>
+        <v>10087</v>
       </c>
       <c r="D225">
         <v>10891</v>
@@ -6216,7 +6216,7 @@
         <v>20257</v>
       </c>
       <c r="G225">
-        <v>15551</v>
+        <v>15935</v>
       </c>
       <c r="H225">
         <v>21385</v>
@@ -6230,7 +6230,7 @@
         <v>17594</v>
       </c>
       <c r="C226">
-        <v>13004</v>
+        <v>13534</v>
       </c>
       <c r="D226">
         <v>9618</v>
@@ -6242,7 +6242,7 @@
         <v>19792</v>
       </c>
       <c r="G226">
-        <v>17834</v>
+        <v>18095</v>
       </c>
       <c r="H226">
         <v>22658</v>
@@ -6256,7 +6256,7 @@
         <v>17686</v>
       </c>
       <c r="C227">
-        <v>8266</v>
+        <v>9152</v>
       </c>
       <c r="D227">
         <v>13734</v>
@@ -6268,7 +6268,7 @@
         <v>21008</v>
       </c>
       <c r="G227">
-        <v>17065</v>
+        <v>17136</v>
       </c>
       <c r="H227">
         <v>21990</v>
@@ -6282,7 +6282,7 @@
         <v>16111</v>
       </c>
       <c r="C228">
-        <v>15600</v>
+        <v>16182</v>
       </c>
       <c r="D228">
         <v>7210</v>
@@ -6294,7 +6294,7 @@
         <v>16833</v>
       </c>
       <c r="G228">
-        <v>18767</v>
+        <v>18804</v>
       </c>
       <c r="H228">
         <v>22132</v>
@@ -6308,19 +6308,19 @@
         <v>20016</v>
       </c>
       <c r="C229">
-        <v>13745</v>
+        <v>15733</v>
       </c>
       <c r="D229">
         <v>17784</v>
       </c>
       <c r="E229">
-        <v>25217</v>
+        <v>25225</v>
       </c>
       <c r="F229">
         <v>24115</v>
       </c>
       <c r="G229">
-        <v>24260</v>
+        <v>24327</v>
       </c>
       <c r="H229">
         <v>28286</v>
@@ -6334,7 +6334,7 @@
         <v>22200</v>
       </c>
       <c r="C230">
-        <v>12771</v>
+        <v>13644</v>
       </c>
       <c r="D230">
         <v>18163</v>
@@ -6346,7 +6346,7 @@
         <v>26988</v>
       </c>
       <c r="G230">
-        <v>23901</v>
+        <v>23963</v>
       </c>
       <c r="H230">
         <v>29865</v>
@@ -6360,19 +6360,19 @@
         <v>20039</v>
       </c>
       <c r="C231">
-        <v>19538</v>
+        <v>20889</v>
       </c>
       <c r="D231">
         <v>17310</v>
       </c>
       <c r="E231">
-        <v>28875</v>
+        <v>28877</v>
       </c>
       <c r="F231">
         <v>23525</v>
       </c>
       <c r="G231">
-        <v>28311</v>
+        <v>28339</v>
       </c>
       <c r="H231">
         <v>31265</v>
@@ -6386,7 +6386,7 @@
         <v>19288</v>
       </c>
       <c r="C232">
-        <v>17000</v>
+        <v>17531</v>
       </c>
       <c r="D232">
         <v>16161</v>
@@ -6398,7 +6398,7 @@
         <v>22263</v>
       </c>
       <c r="G232">
-        <v>24841</v>
+        <v>24848</v>
       </c>
       <c r="H232">
         <v>27915</v>
@@ -6412,7 +6412,7 @@
         <v>18469</v>
       </c>
       <c r="C233">
-        <v>25323</v>
+        <v>25578</v>
       </c>
       <c r="D233">
         <v>12577</v>
@@ -6424,7 +6424,7 @@
         <v>19985</v>
       </c>
       <c r="G233">
-        <v>30584</v>
+        <v>30586</v>
       </c>
       <c r="H233">
         <v>32947</v>
@@ -6438,7 +6438,7 @@
         <v>20476</v>
       </c>
       <c r="C234">
-        <v>25398</v>
+        <v>25855</v>
       </c>
       <c r="D234">
         <v>16921</v>
@@ -6450,7 +6450,7 @@
         <v>24998</v>
       </c>
       <c r="G234">
-        <v>33827</v>
+        <v>33835</v>
       </c>
       <c r="H234">
         <v>36859</v>
@@ -6464,7 +6464,7 @@
         <v>20476</v>
       </c>
       <c r="C235">
-        <v>25398</v>
+        <v>25855</v>
       </c>
       <c r="D235">
         <v>16921</v>
@@ -6476,7 +6476,7 @@
         <v>24998</v>
       </c>
       <c r="G235">
-        <v>33827</v>
+        <v>33835</v>
       </c>
       <c r="H235">
         <v>36859</v>
@@ -6490,7 +6490,7 @@
         <v>20506</v>
       </c>
       <c r="C236">
-        <v>27860</v>
+        <v>28238</v>
       </c>
       <c r="D236">
         <v>13654</v>
@@ -6502,7 +6502,7 @@
         <v>22862</v>
       </c>
       <c r="G236">
-        <v>34260</v>
+        <v>34266</v>
       </c>
       <c r="H236">
         <v>37421</v>
@@ -6516,7 +6516,7 @@
         <v>17707</v>
       </c>
       <c r="C237">
-        <v>13578</v>
+        <v>13941</v>
       </c>
       <c r="D237">
         <v>12043</v>
@@ -6528,7 +6528,7 @@
         <v>20357</v>
       </c>
       <c r="G237">
-        <v>19567</v>
+        <v>19599</v>
       </c>
       <c r="H237">
         <v>23365</v>
@@ -6542,7 +6542,7 @@
         <v>17642</v>
       </c>
       <c r="C238">
-        <v>9688</v>
+        <v>10437</v>
       </c>
       <c r="D238">
         <v>13465</v>
@@ -6554,7 +6554,7 @@
         <v>20888</v>
       </c>
       <c r="G238">
-        <v>17561</v>
+        <v>17621</v>
       </c>
       <c r="H238">
         <v>22100</v>
@@ -6568,7 +6568,7 @@
         <v>17220</v>
       </c>
       <c r="C239">
-        <v>19194</v>
+        <v>19319</v>
       </c>
       <c r="D239">
         <v>8929</v>
@@ -6580,7 +6580,7 @@
         <v>18840</v>
       </c>
       <c r="G239">
-        <v>23094</v>
+        <v>23101</v>
       </c>
       <c r="H239">
         <v>25955</v>
@@ -6594,7 +6594,7 @@
         <v>17092</v>
       </c>
       <c r="C240">
-        <v>17193</v>
+        <v>17334</v>
       </c>
       <c r="D240">
         <v>7724</v>
@@ -6606,7 +6606,7 @@
         <v>18157</v>
       </c>
       <c r="G240">
-        <v>20493</v>
+        <v>20506</v>
       </c>
       <c r="H240">
         <v>23979</v>
@@ -6620,7 +6620,7 @@
         <v>16782</v>
       </c>
       <c r="C241">
-        <v>18570</v>
+        <v>18685</v>
       </c>
       <c r="D241">
         <v>5924</v>
@@ -6632,7 +6632,7 @@
         <v>17425</v>
       </c>
       <c r="G241">
-        <v>21006</v>
+        <v>21020</v>
       </c>
       <c r="H241">
         <v>24500</v>
@@ -6646,7 +6646,7 @@
         <v>22021</v>
       </c>
       <c r="C242">
-        <v>19344</v>
+        <v>19826</v>
       </c>
       <c r="D242">
         <v>16274</v>
@@ -6658,7 +6658,7 @@
         <v>25749</v>
       </c>
       <c r="G242">
-        <v>27655</v>
+        <v>27685</v>
       </c>
       <c r="H242">
         <v>32643</v>
@@ -6672,7 +6672,7 @@
         <v>23999</v>
       </c>
       <c r="C243">
-        <v>21711</v>
+        <v>22214</v>
       </c>
       <c r="D243">
         <v>14714</v>
@@ -6684,7 +6684,7 @@
         <v>27662</v>
       </c>
       <c r="G243">
-        <v>29303</v>
+        <v>29389</v>
       </c>
       <c r="H243">
         <v>35995</v>
@@ -6698,7 +6698,7 @@
         <v>22021</v>
       </c>
       <c r="C244">
-        <v>19344</v>
+        <v>19826</v>
       </c>
       <c r="D244">
         <v>16274</v>
@@ -6710,7 +6710,7 @@
         <v>25749</v>
       </c>
       <c r="G244">
-        <v>27655</v>
+        <v>27685</v>
       </c>
       <c r="H244">
         <v>32643</v>
@@ -6724,7 +6724,7 @@
         <v>22547</v>
       </c>
       <c r="C245">
-        <v>29506</v>
+        <v>29737</v>
       </c>
       <c r="D245">
         <v>13266</v>
@@ -6736,7 +6736,7 @@
         <v>26124</v>
       </c>
       <c r="G245">
-        <v>36144</v>
+        <v>36163</v>
       </c>
       <c r="H245">
         <v>41071</v>
@@ -6750,19 +6750,19 @@
         <v>21043</v>
       </c>
       <c r="C246">
-        <v>29517</v>
+        <v>29703</v>
       </c>
       <c r="D246">
         <v>13044</v>
       </c>
       <c r="E246">
-        <v>37855</v>
+        <v>37856</v>
       </c>
       <c r="F246">
         <v>24645</v>
       </c>
       <c r="G246">
-        <v>35804</v>
+        <v>35823</v>
       </c>
       <c r="H246">
         <v>40152</v>
@@ -6776,19 +6776,19 @@
         <v>21043</v>
       </c>
       <c r="C247">
-        <v>29517</v>
+        <v>29703</v>
       </c>
       <c r="D247">
         <v>13044</v>
       </c>
       <c r="E247">
-        <v>37855</v>
+        <v>37856</v>
       </c>
       <c r="F247">
         <v>24645</v>
       </c>
       <c r="G247">
-        <v>35804</v>
+        <v>35823</v>
       </c>
       <c r="H247">
         <v>40152</v>
@@ -6802,7 +6802,7 @@
         <v>18104</v>
       </c>
       <c r="C248">
-        <v>22676</v>
+        <v>23688</v>
       </c>
       <c r="D248">
         <v>14600</v>
@@ -6814,7 +6814,7 @@
         <v>21269</v>
       </c>
       <c r="G248">
-        <v>29542</v>
+        <v>29557</v>
       </c>
       <c r="H248">
         <v>31662</v>
@@ -6828,7 +6828,7 @@
         <v>16125</v>
       </c>
       <c r="C249">
-        <v>16957</v>
+        <v>17445</v>
       </c>
       <c r="D249">
         <v>5965</v>
@@ -6840,7 +6840,7 @@
         <v>16617</v>
       </c>
       <c r="G249">
-        <v>19486</v>
+        <v>19518</v>
       </c>
       <c r="H249">
         <v>22890</v>
@@ -6854,7 +6854,7 @@
         <v>33840</v>
       </c>
       <c r="C250">
-        <v>25700</v>
+        <v>26386</v>
       </c>
       <c r="D250">
         <v>17427</v>
@@ -6866,7 +6866,7 @@
         <v>36392</v>
       </c>
       <c r="G250">
-        <v>34471</v>
+        <v>34513</v>
       </c>
       <c r="H250">
         <v>44077</v>
@@ -6880,19 +6880,19 @@
         <v>34638</v>
       </c>
       <c r="C251">
-        <v>29383</v>
+        <v>30371</v>
       </c>
       <c r="D251">
         <v>21915</v>
       </c>
       <c r="E251">
-        <v>45042</v>
+        <v>45043</v>
       </c>
       <c r="F251">
         <v>37424</v>
       </c>
       <c r="G251">
-        <v>39665</v>
+        <v>39745</v>
       </c>
       <c r="H251">
         <v>46957</v>
@@ -6906,7 +6906,7 @@
         <v>30697</v>
       </c>
       <c r="C252">
-        <v>23567</v>
+        <v>24074</v>
       </c>
       <c r="D252">
         <v>21740</v>
@@ -6918,7 +6918,7 @@
         <v>34904</v>
       </c>
       <c r="G252">
-        <v>35169</v>
+        <v>35184</v>
       </c>
       <c r="H252">
         <v>42087</v>
@@ -6932,7 +6932,7 @@
         <v>31469</v>
       </c>
       <c r="C253">
-        <v>34939</v>
+        <v>35094</v>
       </c>
       <c r="D253">
         <v>12899</v>
@@ -6944,7 +6944,7 @@
         <v>32787</v>
       </c>
       <c r="G253">
-        <v>41169</v>
+        <v>41177</v>
       </c>
       <c r="H253">
         <v>47973</v>
@@ -6958,7 +6958,7 @@
         <v>35278</v>
       </c>
       <c r="C254">
-        <v>38965</v>
+        <v>39259</v>
       </c>
       <c r="D254">
         <v>16202</v>
@@ -6970,7 +6970,7 @@
         <v>36581</v>
       </c>
       <c r="G254">
-        <v>45902</v>
+        <v>45920</v>
       </c>
       <c r="H254">
         <v>52232</v>
@@ -6984,7 +6984,7 @@
         <v>31469</v>
       </c>
       <c r="C255">
-        <v>34939</v>
+        <v>35094</v>
       </c>
       <c r="D255">
         <v>12899</v>
@@ -6996,7 +6996,7 @@
         <v>32787</v>
       </c>
       <c r="G255">
-        <v>41169</v>
+        <v>41177</v>
       </c>
       <c r="H255">
         <v>47973</v>
@@ -7010,7 +7010,7 @@
         <v>26205</v>
       </c>
       <c r="C256">
-        <v>32219</v>
+        <v>32363</v>
       </c>
       <c r="D256">
         <v>14646</v>
@@ -7022,7 +7022,7 @@
         <v>28343</v>
       </c>
       <c r="G256">
-        <v>39553</v>
+        <v>39555</v>
       </c>
       <c r="H256">
         <v>44463</v>
@@ -7036,7 +7036,7 @@
         <v>23729</v>
       </c>
       <c r="C257">
-        <v>27028</v>
+        <v>27079</v>
       </c>
       <c r="D257">
         <v>7150</v>
@@ -7048,7 +7048,7 @@
         <v>24961</v>
       </c>
       <c r="G257">
-        <v>30750</v>
+        <v>30752</v>
       </c>
       <c r="H257">
         <v>38229</v>
@@ -7062,7 +7062,7 @@
         <v>29717</v>
       </c>
       <c r="C258">
-        <v>25304</v>
+        <v>25339</v>
       </c>
       <c r="D258">
         <v>8105</v>
@@ -7074,7 +7074,7 @@
         <v>30699</v>
       </c>
       <c r="G258">
-        <v>29523</v>
+        <v>29524</v>
       </c>
       <c r="H258">
         <v>39107</v>
@@ -7088,7 +7088,7 @@
         <v>29717</v>
       </c>
       <c r="C259">
-        <v>25304</v>
+        <v>25339</v>
       </c>
       <c r="D259">
         <v>8105</v>
@@ -7100,7 +7100,7 @@
         <v>30699</v>
       </c>
       <c r="G259">
-        <v>29523</v>
+        <v>29524</v>
       </c>
       <c r="H259">
         <v>39107</v>
@@ -7114,7 +7114,7 @@
         <v>12628</v>
       </c>
       <c r="C260">
-        <v>10224</v>
+        <v>10533</v>
       </c>
       <c r="D260">
         <v>3897</v>
@@ -7126,7 +7126,7 @@
         <v>13270</v>
       </c>
       <c r="G260">
-        <v>12174</v>
+        <v>12200</v>
       </c>
       <c r="H260">
         <v>17697</v>
@@ -7140,7 +7140,7 @@
         <v>6719</v>
       </c>
       <c r="C261">
-        <v>8856</v>
+        <v>8948</v>
       </c>
       <c r="D261">
         <v>2169</v>
@@ -7152,7 +7152,7 @@
         <v>7206</v>
       </c>
       <c r="G261">
-        <v>9928</v>
+        <v>9929</v>
       </c>
       <c r="H261">
         <v>12671</v>
@@ -7166,7 +7166,7 @@
         <v>12100</v>
       </c>
       <c r="C262">
-        <v>10122</v>
+        <v>10404</v>
       </c>
       <c r="D262">
         <v>4308</v>
@@ -7178,7 +7178,7 @@
         <v>12875</v>
       </c>
       <c r="G262">
-        <v>12361</v>
+        <v>12375</v>
       </c>
       <c r="H262">
         <v>17387</v>
@@ -7192,7 +7192,7 @@
         <v>11162</v>
       </c>
       <c r="C263">
-        <v>14764</v>
+        <v>14946</v>
       </c>
       <c r="D263">
         <v>4057</v>
@@ -7204,7 +7204,7 @@
         <v>11978</v>
       </c>
       <c r="G263">
-        <v>16717</v>
+        <v>16719</v>
       </c>
       <c r="H263">
         <v>20431</v>
@@ -7218,19 +7218,19 @@
         <v>10183</v>
       </c>
       <c r="C264">
-        <v>13140</v>
+        <v>13230</v>
       </c>
       <c r="D264">
         <v>3299</v>
       </c>
       <c r="E264">
-        <v>17812</v>
+        <v>17813</v>
       </c>
       <c r="F264">
         <v>10904</v>
       </c>
       <c r="G264">
-        <v>14842</v>
+        <v>14845</v>
       </c>
       <c r="H264">
         <v>18374</v>
@@ -7244,19 +7244,19 @@
         <v>10183</v>
       </c>
       <c r="C265">
-        <v>13140</v>
+        <v>13230</v>
       </c>
       <c r="D265">
         <v>3299</v>
       </c>
       <c r="E265">
-        <v>17812</v>
+        <v>17813</v>
       </c>
       <c r="F265">
         <v>10904</v>
       </c>
       <c r="G265">
-        <v>14842</v>
+        <v>14845</v>
       </c>
       <c r="H265">
         <v>18374</v>
@@ -7270,7 +7270,7 @@
         <v>14002</v>
       </c>
       <c r="C266">
-        <v>21116</v>
+        <v>21185</v>
       </c>
       <c r="D266">
         <v>3013</v>
@@ -7282,7 +7282,7 @@
         <v>14481</v>
       </c>
       <c r="G266">
-        <v>22403</v>
+        <v>22406</v>
       </c>
       <c r="H266">
         <v>27399</v>
@@ -7296,19 +7296,19 @@
         <v>10183</v>
       </c>
       <c r="C267">
-        <v>13140</v>
+        <v>13230</v>
       </c>
       <c r="D267">
         <v>3299</v>
       </c>
       <c r="E267">
-        <v>17812</v>
+        <v>17813</v>
       </c>
       <c r="F267">
         <v>10904</v>
       </c>
       <c r="G267">
-        <v>14842</v>
+        <v>14845</v>
       </c>
       <c r="H267">
         <v>18374</v>
@@ -7322,7 +7322,7 @@
         <v>6719</v>
       </c>
       <c r="C268">
-        <v>8856</v>
+        <v>8948</v>
       </c>
       <c r="D268">
         <v>2169</v>
@@ -7334,7 +7334,7 @@
         <v>7206</v>
       </c>
       <c r="G268">
-        <v>9928</v>
+        <v>9929</v>
       </c>
       <c r="H268">
         <v>12671</v>
@@ -7348,7 +7348,7 @@
         <v>6719</v>
       </c>
       <c r="C269">
-        <v>8856</v>
+        <v>8948</v>
       </c>
       <c r="D269">
         <v>2169</v>
@@ -7360,7 +7360,7 @@
         <v>7206</v>
       </c>
       <c r="G269">
-        <v>9928</v>
+        <v>9929</v>
       </c>
       <c r="H269">
         <v>12671</v>
@@ -7374,7 +7374,7 @@
         <v>4841</v>
       </c>
       <c r="C270">
-        <v>12649</v>
+        <v>12693</v>
       </c>
       <c r="D270">
         <v>1428</v>
@@ -7386,7 +7386,7 @@
         <v>5334</v>
       </c>
       <c r="G270">
-        <v>13328</v>
+        <v>13334</v>
       </c>
       <c r="H270">
         <v>15330</v>
@@ -7400,7 +7400,7 @@
         <v>3857</v>
       </c>
       <c r="C271">
-        <v>8283</v>
+        <v>8308</v>
       </c>
       <c r="D271">
         <v>133</v>
@@ -7412,7 +7412,7 @@
         <v>3911</v>
       </c>
       <c r="G271">
-        <v>8342</v>
+        <v>8350</v>
       </c>
       <c r="H271">
         <v>10218</v>
@@ -7426,7 +7426,7 @@
         <v>3857</v>
       </c>
       <c r="C272">
-        <v>8283</v>
+        <v>8308</v>
       </c>
       <c r="D272">
         <v>133</v>
@@ -7438,7 +7438,7 @@
         <v>3911</v>
       </c>
       <c r="G272">
-        <v>8342</v>
+        <v>8350</v>
       </c>
       <c r="H272">
         <v>10218</v>
@@ -7452,7 +7452,7 @@
         <v>5755</v>
       </c>
       <c r="C273">
-        <v>14879</v>
+        <v>14918</v>
       </c>
       <c r="D273">
         <v>1539</v>
@@ -7464,7 +7464,7 @@
         <v>6237</v>
       </c>
       <c r="G273">
-        <v>15587</v>
+        <v>15588</v>
       </c>
       <c r="H273">
         <v>17940</v>
@@ -7478,7 +7478,7 @@
         <v>5755</v>
       </c>
       <c r="C274">
-        <v>14879</v>
+        <v>14918</v>
       </c>
       <c r="D274">
         <v>1539</v>
@@ -7490,7 +7490,7 @@
         <v>6237</v>
       </c>
       <c r="G274">
-        <v>15587</v>
+        <v>15588</v>
       </c>
       <c r="H274">
         <v>17940</v>
@@ -7504,7 +7504,7 @@
         <v>7318</v>
       </c>
       <c r="C275">
-        <v>6035</v>
+        <v>6177</v>
       </c>
       <c r="D275">
         <v>3950</v>
@@ -7516,7 +7516,7 @@
         <v>8637</v>
       </c>
       <c r="G275">
-        <v>8415</v>
+        <v>8427</v>
       </c>
       <c r="H275">
         <v>11196</v>
@@ -7530,7 +7530,7 @@
         <v>4579</v>
       </c>
       <c r="C276">
-        <v>6236</v>
+        <v>6270</v>
       </c>
       <c r="D276">
         <v>1047</v>
@@ -7542,7 +7542,7 @@
         <v>5003</v>
       </c>
       <c r="G276">
-        <v>6867</v>
+        <v>6870</v>
       </c>
       <c r="H276">
         <v>8722</v>
@@ -7556,7 +7556,7 @@
         <v>8942</v>
       </c>
       <c r="C277">
-        <v>12563</v>
+        <v>12624</v>
       </c>
       <c r="D277">
         <v>3459</v>
@@ -7568,7 +7568,7 @@
         <v>10112</v>
       </c>
       <c r="G277">
-        <v>14440</v>
+        <v>14442</v>
       </c>
       <c r="H277">
         <v>17305</v>
@@ -7582,7 +7582,7 @@
         <v>14173</v>
       </c>
       <c r="C278">
-        <v>17978</v>
+        <v>18053</v>
       </c>
       <c r="D278">
         <v>3720</v>
@@ -7594,7 +7594,7 @@
         <v>15745</v>
       </c>
       <c r="G278">
-        <v>20196</v>
+        <v>20222</v>
       </c>
       <c r="H278">
         <v>24657</v>
@@ -7608,7 +7608,7 @@
         <v>16529</v>
       </c>
       <c r="C279">
-        <v>16780</v>
+        <v>16841</v>
       </c>
       <c r="D279">
         <v>5054</v>
@@ -7620,7 +7620,7 @@
         <v>18887</v>
       </c>
       <c r="G279">
-        <v>20113</v>
+        <v>20144</v>
       </c>
       <c r="H279">
         <v>24834</v>
@@ -7634,7 +7634,7 @@
         <v>16529</v>
       </c>
       <c r="C280">
-        <v>16780</v>
+        <v>16841</v>
       </c>
       <c r="D280">
         <v>5054</v>
@@ -7646,7 +7646,7 @@
         <v>18887</v>
       </c>
       <c r="G280">
-        <v>20113</v>
+        <v>20144</v>
       </c>
       <c r="H280">
         <v>24834</v>
@@ -7660,7 +7660,7 @@
         <v>4550</v>
       </c>
       <c r="C281">
-        <v>7633</v>
+        <v>7718</v>
       </c>
       <c r="D281">
         <v>454</v>
@@ -7672,7 +7672,7 @@
         <v>4578</v>
       </c>
       <c r="G281">
-        <v>7815</v>
+        <v>7819</v>
       </c>
       <c r="H281">
         <v>9606</v>
@@ -7686,7 +7686,7 @@
         <v>3675</v>
       </c>
       <c r="C282">
-        <v>6293</v>
+        <v>6366</v>
       </c>
       <c r="D282">
         <v>969</v>
@@ -7698,7 +7698,7 @@
         <v>4057</v>
       </c>
       <c r="G282">
-        <v>6865</v>
+        <v>6883</v>
       </c>
       <c r="H282">
         <v>8199</v>
@@ -7712,7 +7712,7 @@
         <v>3675</v>
       </c>
       <c r="C283">
-        <v>6293</v>
+        <v>6366</v>
       </c>
       <c r="D283">
         <v>969</v>
@@ -7724,7 +7724,7 @@
         <v>4057</v>
       </c>
       <c r="G283">
-        <v>6865</v>
+        <v>6883</v>
       </c>
       <c r="H283">
         <v>8199</v>
@@ -7738,7 +7738,7 @@
         <v>3675</v>
       </c>
       <c r="C284">
-        <v>6293</v>
+        <v>6366</v>
       </c>
       <c r="D284">
         <v>969</v>
@@ -7750,7 +7750,7 @@
         <v>4057</v>
       </c>
       <c r="G284">
-        <v>6865</v>
+        <v>6883</v>
       </c>
       <c r="H284">
         <v>8199</v>
@@ -7764,7 +7764,7 @@
         <v>4579</v>
       </c>
       <c r="C285">
-        <v>6236</v>
+        <v>6270</v>
       </c>
       <c r="D285">
         <v>1047</v>
@@ -7776,7 +7776,7 @@
         <v>5003</v>
       </c>
       <c r="G285">
-        <v>6867</v>
+        <v>6870</v>
       </c>
       <c r="H285">
         <v>8722</v>
@@ -7790,7 +7790,7 @@
         <v>16529</v>
       </c>
       <c r="C286">
-        <v>16780</v>
+        <v>16841</v>
       </c>
       <c r="D286">
         <v>5054</v>
@@ -7802,7 +7802,7 @@
         <v>18887</v>
       </c>
       <c r="G286">
-        <v>20113</v>
+        <v>20144</v>
       </c>
       <c r="H286">
         <v>24834</v>
@@ -7816,7 +7816,7 @@
         <v>24077</v>
       </c>
       <c r="C287">
-        <v>26638</v>
+        <v>27173</v>
       </c>
       <c r="D287">
         <v>12064</v>
@@ -7828,7 +7828,7 @@
         <v>26040</v>
       </c>
       <c r="G287">
-        <v>32474</v>
+        <v>32482</v>
       </c>
       <c r="H287">
         <v>38093</v>
@@ -7842,7 +7842,7 @@
         <v>17082</v>
       </c>
       <c r="C288">
-        <v>23768</v>
+        <v>23918</v>
       </c>
       <c r="D288">
         <v>8164</v>
@@ -7854,7 +7854,7 @@
         <v>18988</v>
       </c>
       <c r="G288">
-        <v>27711</v>
+        <v>27718</v>
       </c>
       <c r="H288">
         <v>32233</v>
@@ -7868,7 +7868,7 @@
         <v>29902</v>
       </c>
       <c r="C289">
-        <v>32243</v>
+        <v>33113</v>
       </c>
       <c r="D289">
         <v>10841</v>
@@ -7880,7 +7880,7 @@
         <v>30835</v>
       </c>
       <c r="G289">
-        <v>36905</v>
+        <v>36952</v>
       </c>
       <c r="H289">
         <v>43731</v>
@@ -7894,7 +7894,7 @@
         <v>24112</v>
       </c>
       <c r="C290">
-        <v>29116</v>
+        <v>29550</v>
       </c>
       <c r="D290">
         <v>9703</v>
@@ -7906,7 +7906,7 @@
         <v>25199</v>
       </c>
       <c r="G290">
-        <v>33646</v>
+        <v>33653</v>
       </c>
       <c r="H290">
         <v>39535</v>
@@ -7920,7 +7920,7 @@
         <v>15442</v>
       </c>
       <c r="C291">
-        <v>21868</v>
+        <v>22022</v>
       </c>
       <c r="D291">
         <v>6902</v>
@@ -7932,7 +7932,7 @@
         <v>17279</v>
       </c>
       <c r="G291">
-        <v>25287</v>
+        <v>25294</v>
       </c>
       <c r="H291">
         <v>29726</v>
@@ -7946,7 +7946,7 @@
         <v>19050</v>
       </c>
       <c r="C292">
-        <v>23860</v>
+        <v>23930</v>
       </c>
       <c r="D292">
         <v>7245</v>
@@ -7958,7 +7958,7 @@
         <v>20848</v>
       </c>
       <c r="G292">
-        <v>27447</v>
+        <v>27453</v>
       </c>
       <c r="H292">
         <v>33401</v>
@@ -7972,7 +7972,7 @@
         <v>19361</v>
       </c>
       <c r="C293">
-        <v>23798</v>
+        <v>23949</v>
       </c>
       <c r="D293">
         <v>8139</v>
@@ -7984,7 +7984,7 @@
         <v>21360</v>
       </c>
       <c r="G293">
-        <v>27939</v>
+        <v>27949</v>
       </c>
       <c r="H293">
         <v>33636</v>
@@ -7998,7 +7998,7 @@
         <v>19086</v>
       </c>
       <c r="C294">
-        <v>26279</v>
+        <v>26335</v>
       </c>
       <c r="D294">
         <v>5505</v>
@@ -8010,7 +8010,7 @@
         <v>20234</v>
       </c>
       <c r="G294">
-        <v>28951</v>
+        <v>28957</v>
       </c>
       <c r="H294">
         <v>35183</v>
@@ -8024,7 +8024,7 @@
         <v>17828</v>
       </c>
       <c r="C295">
-        <v>9155</v>
+        <v>10157</v>
       </c>
       <c r="D295">
         <v>12012</v>
@@ -8036,7 +8036,7 @@
         <v>20709</v>
       </c>
       <c r="G295">
-        <v>16731</v>
+        <v>16762</v>
       </c>
       <c r="H295">
         <v>23157</v>
@@ -8050,7 +8050,7 @@
         <v>19559</v>
       </c>
       <c r="C296">
-        <v>10475</v>
+        <v>11500</v>
       </c>
       <c r="D296">
         <v>15092</v>
@@ -8062,7 +8062,7 @@
         <v>23158</v>
       </c>
       <c r="G296">
-        <v>19925</v>
+        <v>19940</v>
       </c>
       <c r="H296">
         <v>25852</v>
@@ -8076,7 +8076,7 @@
         <v>18117</v>
       </c>
       <c r="C297">
-        <v>16857</v>
+        <v>17407</v>
       </c>
       <c r="D297">
         <v>12115</v>
@@ -8088,7 +8088,7 @@
         <v>20743</v>
       </c>
       <c r="G297">
-        <v>23232</v>
+        <v>23240</v>
       </c>
       <c r="H297">
         <v>28062</v>
@@ -8102,7 +8102,7 @@
         <v>16049</v>
       </c>
       <c r="C298">
-        <v>9223</v>
+        <v>10242</v>
       </c>
       <c r="D298">
         <v>13214</v>
@@ -8114,7 +8114,7 @@
         <v>19866</v>
       </c>
       <c r="G298">
-        <v>17641</v>
+        <v>17655</v>
       </c>
       <c r="H298">
         <v>22603</v>
@@ -8128,7 +8128,7 @@
         <v>15140</v>
       </c>
       <c r="C299">
-        <v>14359</v>
+        <v>14948</v>
       </c>
       <c r="D299">
         <v>10629</v>
@@ -8140,7 +8140,7 @@
         <v>17839</v>
       </c>
       <c r="G299">
-        <v>20125</v>
+        <v>20138</v>
       </c>
       <c r="H299">
         <v>24380</v>
@@ -8154,7 +8154,7 @@
         <v>17828</v>
       </c>
       <c r="C300">
-        <v>9155</v>
+        <v>10157</v>
       </c>
       <c r="D300">
         <v>12012</v>
@@ -8166,7 +8166,7 @@
         <v>20709</v>
       </c>
       <c r="G300">
-        <v>16731</v>
+        <v>16762</v>
       </c>
       <c r="H300">
         <v>23157</v>
@@ -8180,7 +8180,7 @@
         <v>19339</v>
       </c>
       <c r="C301">
-        <v>16317</v>
+        <v>16982</v>
       </c>
       <c r="D301">
         <v>13507</v>
@@ -8192,7 +8192,7 @@
         <v>22166</v>
       </c>
       <c r="G301">
-        <v>23494</v>
+        <v>23503</v>
       </c>
       <c r="H301">
         <v>28505</v>
@@ -8206,7 +8206,7 @@
         <v>14642</v>
       </c>
       <c r="C302">
-        <v>20694</v>
+        <v>21215</v>
       </c>
       <c r="D302">
         <v>10815</v>
@@ -8218,7 +8218,7 @@
         <v>17631</v>
       </c>
       <c r="G302">
-        <v>26316</v>
+        <v>26320</v>
       </c>
       <c r="H302">
         <v>29325</v>
@@ -8232,7 +8232,7 @@
         <v>14671</v>
       </c>
       <c r="C303">
-        <v>22840</v>
+        <v>23272</v>
       </c>
       <c r="D303">
         <v>8710</v>
@@ -8244,7 +8244,7 @@
         <v>16297</v>
       </c>
       <c r="G303">
-        <v>27199</v>
+        <v>27202</v>
       </c>
       <c r="H303">
         <v>30424</v>
@@ -8258,7 +8258,7 @@
         <v>15651</v>
       </c>
       <c r="C304">
-        <v>13038</v>
+        <v>13388</v>
       </c>
       <c r="D304">
         <v>8848</v>
@@ -8270,7 +8270,7 @@
         <v>17522</v>
       </c>
       <c r="G304">
-        <v>17726</v>
+        <v>17741</v>
       </c>
       <c r="H304">
         <v>22903</v>
@@ -8284,7 +8284,7 @@
         <v>15651</v>
       </c>
       <c r="C305">
-        <v>13038</v>
+        <v>13388</v>
       </c>
       <c r="D305">
         <v>8848</v>
@@ -8296,7 +8296,7 @@
         <v>17522</v>
       </c>
       <c r="G305">
-        <v>17726</v>
+        <v>17741</v>
       </c>
       <c r="H305">
         <v>22903</v>
@@ -8310,7 +8310,7 @@
         <v>18590</v>
       </c>
       <c r="C306">
-        <v>11233</v>
+        <v>11374</v>
       </c>
       <c r="D306">
         <v>8201</v>
@@ -8322,7 +8322,7 @@
         <v>19961</v>
       </c>
       <c r="G306">
-        <v>15650</v>
+        <v>15661</v>
       </c>
       <c r="H306">
         <v>23225</v>
@@ -8336,7 +8336,7 @@
         <v>15651</v>
       </c>
       <c r="C307">
-        <v>13038</v>
+        <v>13388</v>
       </c>
       <c r="D307">
         <v>8848</v>
@@ -8348,7 +8348,7 @@
         <v>17522</v>
       </c>
       <c r="G307">
-        <v>17726</v>
+        <v>17741</v>
       </c>
       <c r="H307">
         <v>22903</v>
@@ -8362,7 +8362,7 @@
         <v>17344</v>
       </c>
       <c r="C308">
-        <v>16296</v>
+        <v>16352</v>
       </c>
       <c r="D308">
         <v>7615</v>
@@ -8374,7 +8374,7 @@
         <v>18817</v>
       </c>
       <c r="G308">
-        <v>20202</v>
+        <v>20203</v>
       </c>
       <c r="H308">
         <v>25678</v>
@@ -8388,7 +8388,7 @@
         <v>18590</v>
       </c>
       <c r="C309">
-        <v>11233</v>
+        <v>11374</v>
       </c>
       <c r="D309">
         <v>8201</v>
@@ -8400,7 +8400,7 @@
         <v>19961</v>
       </c>
       <c r="G309">
-        <v>15650</v>
+        <v>15661</v>
       </c>
       <c r="H309">
         <v>23225</v>
@@ -8414,7 +8414,7 @@
         <v>14522</v>
       </c>
       <c r="C310">
-        <v>18639</v>
+        <v>18869</v>
       </c>
       <c r="D310">
         <v>8202</v>
@@ -8426,7 +8426,7 @@
         <v>16490</v>
       </c>
       <c r="G310">
-        <v>22790</v>
+        <v>22793</v>
       </c>
       <c r="H310">
         <v>26549</v>
@@ -8440,7 +8440,7 @@
         <v>6076</v>
       </c>
       <c r="C311">
-        <v>7656</v>
+        <v>7676</v>
       </c>
       <c r="D311">
         <v>2411</v>
@@ -8452,7 +8452,7 @@
         <v>6882</v>
       </c>
       <c r="G311">
-        <v>9131</v>
+        <v>9132</v>
       </c>
       <c r="H311">
         <v>11111</v>
@@ -8466,7 +8466,7 @@
         <v>6792</v>
       </c>
       <c r="C312">
-        <v>5299</v>
+        <v>5333</v>
       </c>
       <c r="D312">
         <v>2758</v>
@@ -8478,7 +8478,7 @@
         <v>7609</v>
       </c>
       <c r="G312">
-        <v>7348</v>
+        <v>7349</v>
       </c>
       <c r="H312">
         <v>10488</v>
@@ -8492,7 +8492,7 @@
         <v>6076</v>
       </c>
       <c r="C313">
-        <v>7656</v>
+        <v>7676</v>
       </c>
       <c r="D313">
         <v>2411</v>
@@ -8504,7 +8504,7 @@
         <v>6882</v>
       </c>
       <c r="G313">
-        <v>9131</v>
+        <v>9132</v>
       </c>
       <c r="H313">
         <v>11111</v>
@@ -8518,7 +8518,7 @@
         <v>6076</v>
       </c>
       <c r="C314">
-        <v>7656</v>
+        <v>7676</v>
       </c>
       <c r="D314">
         <v>2411</v>
@@ -8530,7 +8530,7 @@
         <v>6882</v>
       </c>
       <c r="G314">
-        <v>9131</v>
+        <v>9132</v>
       </c>
       <c r="H314">
         <v>11111</v>
@@ -8544,7 +8544,7 @@
         <v>30656</v>
       </c>
       <c r="C315">
-        <v>24229</v>
+        <v>25070</v>
       </c>
       <c r="D315">
         <v>16146</v>
@@ -8556,7 +8556,7 @@
         <v>32561</v>
       </c>
       <c r="G315">
-        <v>31899</v>
+        <v>31975</v>
       </c>
       <c r="H315">
         <v>40094</v>
@@ -8570,22 +8570,22 @@
         <v>36809</v>
       </c>
       <c r="C316">
-        <v>20602</v>
+        <v>23159</v>
       </c>
       <c r="D316">
         <v>28724</v>
       </c>
       <c r="E316">
-        <v>40608</v>
+        <v>40611</v>
       </c>
       <c r="F316">
         <v>40410</v>
       </c>
       <c r="G316">
-        <v>36638</v>
+        <v>36794</v>
       </c>
       <c r="H316">
-        <v>43566</v>
+        <v>43569</v>
       </c>
     </row>
     <row r="317" spans="1:8">
@@ -8596,7 +8596,7 @@
         <v>38274</v>
       </c>
       <c r="C317">
-        <v>19908</v>
+        <v>22375</v>
       </c>
       <c r="D317">
         <v>26285</v>
@@ -8608,7 +8608,7 @@
         <v>40328</v>
       </c>
       <c r="G317">
-        <v>34454</v>
+        <v>34592</v>
       </c>
       <c r="H317">
         <v>43061</v>
@@ -8622,7 +8622,7 @@
         <v>34939</v>
       </c>
       <c r="C318">
-        <v>18074</v>
+        <v>20429</v>
       </c>
       <c r="D318">
         <v>25210</v>
@@ -8634,7 +8634,7 @@
         <v>37766</v>
       </c>
       <c r="G318">
-        <v>32739</v>
+        <v>32807</v>
       </c>
       <c r="H318">
         <v>40703</v>
@@ -8648,7 +8648,7 @@
         <v>31659</v>
       </c>
       <c r="C319">
-        <v>15739</v>
+        <v>16893</v>
       </c>
       <c r="D319">
         <v>17701</v>
@@ -8660,7 +8660,7 @@
         <v>33633</v>
       </c>
       <c r="G319">
-        <v>25716</v>
+        <v>25778</v>
       </c>
       <c r="H319">
         <v>36384</v>
@@ -8674,7 +8674,7 @@
         <v>32419</v>
       </c>
       <c r="C320">
-        <v>16980</v>
+        <v>19024</v>
       </c>
       <c r="D320">
         <v>22156</v>
@@ -8686,7 +8686,7 @@
         <v>35067</v>
       </c>
       <c r="G320">
-        <v>29904</v>
+        <v>29958</v>
       </c>
       <c r="H320">
         <v>38381</v>
@@ -8700,7 +8700,7 @@
         <v>35180</v>
       </c>
       <c r="C321">
-        <v>18334</v>
+        <v>20573</v>
       </c>
       <c r="D321">
         <v>24711</v>
@@ -8712,7 +8712,7 @@
         <v>37705</v>
       </c>
       <c r="G321">
-        <v>32409</v>
+        <v>32500</v>
       </c>
       <c r="H321">
         <v>40694</v>
@@ -8726,7 +8726,7 @@
         <v>26483</v>
       </c>
       <c r="C322">
-        <v>32934</v>
+        <v>33231</v>
       </c>
       <c r="D322">
         <v>10790</v>
@@ -8738,7 +8738,7 @@
         <v>27699</v>
       </c>
       <c r="G322">
-        <v>37814</v>
+        <v>37820</v>
       </c>
       <c r="H322">
         <v>43802</v>
@@ -8752,7 +8752,7 @@
         <v>33904</v>
       </c>
       <c r="C323">
-        <v>17893</v>
+        <v>19382</v>
       </c>
       <c r="D323">
         <v>23925</v>
@@ -8764,7 +8764,7 @@
         <v>36654</v>
       </c>
       <c r="G323">
-        <v>31251</v>
+        <v>31303</v>
       </c>
       <c r="H323">
         <v>39481</v>
@@ -8778,7 +8778,7 @@
         <v>33904</v>
       </c>
       <c r="C324">
-        <v>17893</v>
+        <v>19382</v>
       </c>
       <c r="D324">
         <v>23925</v>
@@ -8790,7 +8790,7 @@
         <v>36654</v>
       </c>
       <c r="G324">
-        <v>31251</v>
+        <v>31303</v>
       </c>
       <c r="H324">
         <v>39481</v>
@@ -8804,7 +8804,7 @@
         <v>33904</v>
       </c>
       <c r="C325">
-        <v>17893</v>
+        <v>19382</v>
       </c>
       <c r="D325">
         <v>23925</v>
@@ -8816,7 +8816,7 @@
         <v>36654</v>
       </c>
       <c r="G325">
-        <v>31251</v>
+        <v>31303</v>
       </c>
       <c r="H325">
         <v>39481</v>
@@ -8830,7 +8830,7 @@
         <v>37891</v>
       </c>
       <c r="C326">
-        <v>19896</v>
+        <v>22310</v>
       </c>
       <c r="D326">
         <v>27135</v>
@@ -8842,7 +8842,7 @@
         <v>39983</v>
       </c>
       <c r="G326">
-        <v>34800</v>
+        <v>34862</v>
       </c>
       <c r="H326">
         <v>42703</v>
@@ -8856,7 +8856,7 @@
         <v>26842</v>
       </c>
       <c r="C327">
-        <v>28135</v>
+        <v>28381</v>
       </c>
       <c r="D327">
         <v>10028</v>
@@ -8868,7 +8868,7 @@
         <v>28098</v>
       </c>
       <c r="G327">
-        <v>32677</v>
+        <v>32684</v>
       </c>
       <c r="H327">
         <v>40094</v>
@@ -8882,7 +8882,7 @@
         <v>26879</v>
       </c>
       <c r="C328">
-        <v>30739</v>
+        <v>30940</v>
       </c>
       <c r="D328">
         <v>7943</v>
@@ -8894,7 +8894,7 @@
         <v>27743</v>
       </c>
       <c r="G328">
-        <v>34221</v>
+        <v>34228</v>
       </c>
       <c r="H328">
         <v>41904</v>
@@ -8908,7 +8908,7 @@
         <v>24298</v>
       </c>
       <c r="C329">
-        <v>28421</v>
+        <v>28508</v>
       </c>
       <c r="D329">
         <v>6949</v>
@@ -8920,7 +8920,7 @@
         <v>25136</v>
       </c>
       <c r="G329">
-        <v>31565</v>
+        <v>31575</v>
       </c>
       <c r="H329">
         <v>38913</v>
@@ -8934,7 +8934,7 @@
         <v>26879</v>
       </c>
       <c r="C330">
-        <v>30739</v>
+        <v>30940</v>
       </c>
       <c r="D330">
         <v>7943</v>
@@ -8946,7 +8946,7 @@
         <v>27743</v>
       </c>
       <c r="G330">
-        <v>34221</v>
+        <v>34228</v>
       </c>
       <c r="H330">
         <v>41904</v>
@@ -8960,7 +8960,7 @@
         <v>28361</v>
       </c>
       <c r="C331">
-        <v>21025</v>
+        <v>21562</v>
       </c>
       <c r="D331">
         <v>10971</v>
@@ -8972,7 +8972,7 @@
         <v>29528</v>
       </c>
       <c r="G331">
-        <v>26246</v>
+        <v>26286</v>
       </c>
       <c r="H331">
         <v>36252</v>
@@ -8986,7 +8986,7 @@
         <v>29307</v>
       </c>
       <c r="C332">
-        <v>30334</v>
+        <v>30655</v>
       </c>
       <c r="D332">
         <v>12245</v>
@@ -8998,7 +8998,7 @@
         <v>30483</v>
       </c>
       <c r="G332">
-        <v>35717</v>
+        <v>35747</v>
       </c>
       <c r="H332">
         <v>42308</v>
@@ -9012,7 +9012,7 @@
         <v>31813</v>
       </c>
       <c r="C333">
-        <v>24550</v>
+        <v>25320</v>
       </c>
       <c r="D333">
         <v>19301</v>
@@ -9024,7 +9024,7 @@
         <v>33369</v>
       </c>
       <c r="G333">
-        <v>33414</v>
+        <v>33433</v>
       </c>
       <c r="H333">
         <v>40020</v>
@@ -9038,7 +9038,7 @@
         <v>33183</v>
       </c>
       <c r="C334">
-        <v>33740</v>
+        <v>34259</v>
       </c>
       <c r="D334">
         <v>17033</v>
@@ -9050,7 +9050,7 @@
         <v>34583</v>
       </c>
       <c r="G334">
-        <v>40769</v>
+        <v>40817</v>
       </c>
       <c r="H334">
         <v>46547</v>
@@ -9064,7 +9064,7 @@
         <v>30455</v>
       </c>
       <c r="C335">
-        <v>32104</v>
+        <v>32368</v>
       </c>
       <c r="D335">
         <v>15653</v>
@@ -9076,7 +9076,7 @@
         <v>31928</v>
       </c>
       <c r="G335">
-        <v>38615</v>
+        <v>38634</v>
       </c>
       <c r="H335">
         <v>44118</v>
@@ -9090,7 +9090,7 @@
         <v>26958</v>
       </c>
       <c r="C336">
-        <v>31248</v>
+        <v>31430</v>
       </c>
       <c r="D336">
         <v>7795</v>
@@ -9102,7 +9102,7 @@
         <v>27759</v>
       </c>
       <c r="G336">
-        <v>34591</v>
+        <v>34617</v>
       </c>
       <c r="H336">
         <v>41728</v>
@@ -9116,7 +9116,7 @@
         <v>8866</v>
       </c>
       <c r="C337">
-        <v>7197</v>
+        <v>7611</v>
       </c>
       <c r="D337">
         <v>5468</v>
@@ -9128,7 +9128,7 @@
         <v>10258</v>
       </c>
       <c r="G337">
-        <v>10266</v>
+        <v>10276</v>
       </c>
       <c r="H337">
         <v>12973</v>
@@ -9142,7 +9142,7 @@
         <v>7591</v>
       </c>
       <c r="C338">
-        <v>6384</v>
+        <v>6690</v>
       </c>
       <c r="D338">
         <v>6724</v>
@@ -9154,7 +9154,7 @@
         <v>9866</v>
       </c>
       <c r="G338">
-        <v>10445</v>
+        <v>10448</v>
       </c>
       <c r="H338">
         <v>12279</v>
@@ -9168,7 +9168,7 @@
         <v>8866</v>
       </c>
       <c r="C339">
-        <v>7197</v>
+        <v>7611</v>
       </c>
       <c r="D339">
         <v>5468</v>
@@ -9180,7 +9180,7 @@
         <v>10258</v>
       </c>
       <c r="G339">
-        <v>10266</v>
+        <v>10276</v>
       </c>
       <c r="H339">
         <v>12973</v>
@@ -9194,7 +9194,7 @@
         <v>6650</v>
       </c>
       <c r="C340">
-        <v>8516</v>
+        <v>8743</v>
       </c>
       <c r="D340">
         <v>3979</v>
@@ -9206,7 +9206,7 @@
         <v>7775</v>
       </c>
       <c r="G340">
-        <v>10730</v>
+        <v>10733</v>
       </c>
       <c r="H340">
         <v>12386</v>
@@ -9220,7 +9220,7 @@
         <v>6638</v>
       </c>
       <c r="C341">
-        <v>7707</v>
+        <v>7982</v>
       </c>
       <c r="D341">
         <v>4737</v>
@@ -9232,7 +9232,7 @@
         <v>8170</v>
       </c>
       <c r="G341">
-        <v>10428</v>
+        <v>10432</v>
       </c>
       <c r="H341">
         <v>11991</v>
@@ -9246,7 +9246,7 @@
         <v>6922</v>
       </c>
       <c r="C342">
-        <v>10661</v>
+        <v>10756</v>
       </c>
       <c r="D342">
         <v>4135</v>
@@ -9258,7 +9258,7 @@
         <v>8257</v>
       </c>
       <c r="G342">
-        <v>12963</v>
+        <v>12985</v>
       </c>
       <c r="H342">
         <v>14584</v>
@@ -9272,7 +9272,7 @@
         <v>6922</v>
       </c>
       <c r="C343">
-        <v>10661</v>
+        <v>10756</v>
       </c>
       <c r="D343">
         <v>4135</v>
@@ -9284,7 +9284,7 @@
         <v>8257</v>
       </c>
       <c r="G343">
-        <v>12963</v>
+        <v>12985</v>
       </c>
       <c r="H343">
         <v>14584</v>
@@ -9298,7 +9298,7 @@
         <v>6650</v>
       </c>
       <c r="C344">
-        <v>8516</v>
+        <v>8743</v>
       </c>
       <c r="D344">
         <v>3979</v>
@@ -9310,7 +9310,7 @@
         <v>7775</v>
       </c>
       <c r="G344">
-        <v>10730</v>
+        <v>10733</v>
       </c>
       <c r="H344">
         <v>12386</v>
@@ -9324,7 +9324,7 @@
         <v>4395</v>
       </c>
       <c r="C345">
-        <v>6223</v>
+        <v>6315</v>
       </c>
       <c r="D345">
         <v>2683</v>
@@ -9336,7 +9336,7 @@
         <v>5274</v>
       </c>
       <c r="G345">
-        <v>7722</v>
+        <v>7724</v>
       </c>
       <c r="H345">
         <v>8830</v>
@@ -9350,7 +9350,7 @@
         <v>4395</v>
       </c>
       <c r="C346">
-        <v>6223</v>
+        <v>6315</v>
       </c>
       <c r="D346">
         <v>2683</v>
@@ -9362,7 +9362,7 @@
         <v>5274</v>
       </c>
       <c r="G346">
-        <v>7722</v>
+        <v>7724</v>
       </c>
       <c r="H346">
         <v>8830</v>
@@ -9376,7 +9376,7 @@
         <v>4395</v>
       </c>
       <c r="C347">
-        <v>6223</v>
+        <v>6315</v>
       </c>
       <c r="D347">
         <v>2683</v>
@@ -9388,7 +9388,7 @@
         <v>5274</v>
       </c>
       <c r="G347">
-        <v>7722</v>
+        <v>7724</v>
       </c>
       <c r="H347">
         <v>8830</v>
@@ -9402,7 +9402,7 @@
         <v>9393</v>
       </c>
       <c r="C348">
-        <v>10906</v>
+        <v>11008</v>
       </c>
       <c r="D348">
         <v>2499</v>
@@ -9414,7 +9414,7 @@
         <v>9967</v>
       </c>
       <c r="G348">
-        <v>12161</v>
+        <v>12172</v>
       </c>
       <c r="H348">
         <v>15226</v>
@@ -9428,7 +9428,7 @@
         <v>9393</v>
       </c>
       <c r="C349">
-        <v>10906</v>
+        <v>11008</v>
       </c>
       <c r="D349">
         <v>2499</v>
@@ -9440,7 +9440,7 @@
         <v>9967</v>
       </c>
       <c r="G349">
-        <v>12161</v>
+        <v>12172</v>
       </c>
       <c r="H349">
         <v>15226</v>
@@ -9454,7 +9454,7 @@
         <v>9393</v>
       </c>
       <c r="C350">
-        <v>10906</v>
+        <v>11008</v>
       </c>
       <c r="D350">
         <v>2499</v>
@@ -9466,7 +9466,7 @@
         <v>9967</v>
       </c>
       <c r="G350">
-        <v>12161</v>
+        <v>12172</v>
       </c>
       <c r="H350">
         <v>15226</v>
@@ -9480,7 +9480,7 @@
         <v>3045</v>
       </c>
       <c r="C351">
-        <v>5241</v>
+        <v>5304</v>
       </c>
       <c r="D351">
         <v>2095</v>
@@ -9492,7 +9492,7 @@
         <v>3785</v>
       </c>
       <c r="G351">
-        <v>6417</v>
+        <v>6425</v>
       </c>
       <c r="H351">
         <v>7105</v>
@@ -9506,7 +9506,7 @@
         <v>3045</v>
       </c>
       <c r="C352">
-        <v>5241</v>
+        <v>5304</v>
       </c>
       <c r="D352">
         <v>2095</v>
@@ -9518,7 +9518,7 @@
         <v>3785</v>
       </c>
       <c r="G352">
-        <v>6417</v>
+        <v>6425</v>
       </c>
       <c r="H352">
         <v>7105</v>
@@ -9532,7 +9532,7 @@
         <v>14481</v>
       </c>
       <c r="C353">
-        <v>14227</v>
+        <v>14435</v>
       </c>
       <c r="D353">
         <v>5708</v>
@@ -9544,7 +9544,7 @@
         <v>15041</v>
       </c>
       <c r="G353">
-        <v>16759</v>
+        <v>16763</v>
       </c>
       <c r="H353">
         <v>19971</v>
@@ -9558,7 +9558,7 @@
         <v>14394</v>
       </c>
       <c r="C354">
-        <v>12402</v>
+        <v>12526</v>
       </c>
       <c r="D354">
         <v>3996</v>
@@ -9570,7 +9570,7 @@
         <v>14726</v>
       </c>
       <c r="G354">
-        <v>14397</v>
+        <v>14400</v>
       </c>
       <c r="H354">
         <v>18134</v>
@@ -9584,7 +9584,7 @@
         <v>14494</v>
       </c>
       <c r="C355">
-        <v>15405</v>
+        <v>15577</v>
       </c>
       <c r="D355">
         <v>4597</v>
@@ -9596,7 +9596,7 @@
         <v>14894</v>
       </c>
       <c r="G355">
-        <v>17403</v>
+        <v>17407</v>
       </c>
       <c r="H355">
         <v>20684</v>
@@ -9610,7 +9610,7 @@
         <v>9030</v>
       </c>
       <c r="C356">
-        <v>10884</v>
+        <v>10979</v>
       </c>
       <c r="D356">
         <v>4177</v>
@@ -9622,7 +9622,7 @@
         <v>9562</v>
       </c>
       <c r="G356">
-        <v>12902</v>
+        <v>12903</v>
       </c>
       <c r="H356">
         <v>15074</v>
@@ -9636,7 +9636,7 @@
         <v>9030</v>
       </c>
       <c r="C357">
-        <v>10884</v>
+        <v>10979</v>
       </c>
       <c r="D357">
         <v>4177</v>
@@ -9648,7 +9648,7 @@
         <v>9562</v>
       </c>
       <c r="G357">
-        <v>12902</v>
+        <v>12903</v>
       </c>
       <c r="H357">
         <v>15074</v>
@@ -9662,7 +9662,7 @@
         <v>9030</v>
       </c>
       <c r="C358">
-        <v>10884</v>
+        <v>10979</v>
       </c>
       <c r="D358">
         <v>4177</v>
@@ -9674,7 +9674,7 @@
         <v>9562</v>
       </c>
       <c r="G358">
-        <v>12902</v>
+        <v>12903</v>
       </c>
       <c r="H358">
         <v>15074</v>
@@ -9688,7 +9688,7 @@
         <v>3081</v>
       </c>
       <c r="C359">
-        <v>5761</v>
+        <v>5804</v>
       </c>
       <c r="D359">
         <v>1111</v>
@@ -9700,7 +9700,7 @@
         <v>3536</v>
       </c>
       <c r="G359">
-        <v>6421</v>
+        <v>6437</v>
       </c>
       <c r="H359">
         <v>7551</v>
@@ -9714,7 +9714,7 @@
         <v>3081</v>
       </c>
       <c r="C360">
-        <v>5761</v>
+        <v>5804</v>
       </c>
       <c r="D360">
         <v>1111</v>
@@ -9726,7 +9726,7 @@
         <v>3536</v>
       </c>
       <c r="G360">
-        <v>6421</v>
+        <v>6437</v>
       </c>
       <c r="H360">
         <v>7551</v>
@@ -9740,7 +9740,7 @@
         <v>13959</v>
       </c>
       <c r="C361">
-        <v>17142</v>
+        <v>17359</v>
       </c>
       <c r="D361">
         <v>8116</v>
@@ -9752,7 +9752,7 @@
         <v>16889</v>
       </c>
       <c r="G361">
-        <v>21985</v>
+        <v>21989</v>
       </c>
       <c r="H361">
         <v>26539</v>
@@ -9766,7 +9766,7 @@
         <v>9973</v>
       </c>
       <c r="C362">
-        <v>18222</v>
+        <v>18424</v>
       </c>
       <c r="D362">
         <v>4054</v>
@@ -9778,7 +9778,7 @@
         <v>11056</v>
       </c>
       <c r="G362">
-        <v>20375</v>
+        <v>20377</v>
       </c>
       <c r="H362">
         <v>23975</v>
@@ -9792,7 +9792,7 @@
         <v>14064</v>
       </c>
       <c r="C363">
-        <v>13989</v>
+        <v>14055</v>
       </c>
       <c r="D363">
         <v>3551</v>
@@ -9804,7 +9804,7 @@
         <v>14892</v>
       </c>
       <c r="G363">
-        <v>15966</v>
+        <v>15967</v>
       </c>
       <c r="H363">
         <v>21714</v>
@@ -9818,7 +9818,7 @@
         <v>10374</v>
       </c>
       <c r="C364">
-        <v>19426</v>
+        <v>19506</v>
       </c>
       <c r="D364">
         <v>10484</v>
@@ -9844,7 +9844,7 @@
         <v>10374</v>
       </c>
       <c r="C365">
-        <v>19426</v>
+        <v>19506</v>
       </c>
       <c r="D365">
         <v>10484</v>
@@ -9870,7 +9870,7 @@
         <v>6447</v>
       </c>
       <c r="C366">
-        <v>15606</v>
+        <v>15644</v>
       </c>
       <c r="D366">
         <v>4079</v>
@@ -9882,7 +9882,7 @@
         <v>7989</v>
       </c>
       <c r="G366">
-        <v>17892</v>
+        <v>17894</v>
       </c>
       <c r="H366">
         <v>19505</v>
@@ -9896,7 +9896,7 @@
         <v>6447</v>
       </c>
       <c r="C367">
-        <v>15606</v>
+        <v>15644</v>
       </c>
       <c r="D367">
         <v>4079</v>
@@ -9908,7 +9908,7 @@
         <v>7989</v>
       </c>
       <c r="G367">
-        <v>17892</v>
+        <v>17894</v>
       </c>
       <c r="H367">
         <v>19505</v>
@@ -9922,7 +9922,7 @@
         <v>7830</v>
       </c>
       <c r="C368">
-        <v>15919</v>
+        <v>15953</v>
       </c>
       <c r="D368">
         <v>7351</v>
@@ -9948,7 +9948,7 @@
         <v>6447</v>
       </c>
       <c r="C369">
-        <v>15606</v>
+        <v>15644</v>
       </c>
       <c r="D369">
         <v>4079</v>
@@ -9960,7 +9960,7 @@
         <v>7989</v>
       </c>
       <c r="G369">
-        <v>17892</v>
+        <v>17894</v>
       </c>
       <c r="H369">
         <v>19505</v>
@@ -9974,7 +9974,7 @@
         <v>6195</v>
       </c>
       <c r="C370">
-        <v>11246</v>
+        <v>11320</v>
       </c>
       <c r="D370">
         <v>1440</v>
@@ -9986,7 +9986,7 @@
         <v>6645</v>
       </c>
       <c r="G370">
-        <v>11956</v>
+        <v>11963</v>
       </c>
       <c r="H370">
         <v>14543</v>
@@ -10000,7 +10000,7 @@
         <v>6195</v>
       </c>
       <c r="C371">
-        <v>11246</v>
+        <v>11320</v>
       </c>
       <c r="D371">
         <v>1440</v>
@@ -10012,7 +10012,7 @@
         <v>6645</v>
       </c>
       <c r="G371">
-        <v>11956</v>
+        <v>11963</v>
       </c>
       <c r="H371">
         <v>14543</v>
@@ -10026,7 +10026,7 @@
         <v>6195</v>
       </c>
       <c r="C372">
-        <v>11246</v>
+        <v>11320</v>
       </c>
       <c r="D372">
         <v>1440</v>
@@ -10038,7 +10038,7 @@
         <v>6645</v>
       </c>
       <c r="G372">
-        <v>11956</v>
+        <v>11963</v>
       </c>
       <c r="H372">
         <v>14543</v>
@@ -10052,7 +10052,7 @@
         <v>14444</v>
       </c>
       <c r="C373">
-        <v>15003</v>
+        <v>15255</v>
       </c>
       <c r="D373">
         <v>8015</v>
@@ -10064,7 +10064,7 @@
         <v>16819</v>
       </c>
       <c r="G373">
-        <v>19418</v>
+        <v>19423</v>
       </c>
       <c r="H373">
         <v>22998</v>
@@ -10078,7 +10078,7 @@
         <v>11873</v>
       </c>
       <c r="C374">
-        <v>11300</v>
+        <v>11493</v>
       </c>
       <c r="D374">
         <v>6093</v>
@@ -10090,7 +10090,7 @@
         <v>13622</v>
       </c>
       <c r="G374">
-        <v>14736</v>
+        <v>14737</v>
       </c>
       <c r="H374">
         <v>18276</v>
@@ -10104,7 +10104,7 @@
         <v>14463</v>
       </c>
       <c r="C375">
-        <v>16489</v>
+        <v>16696</v>
       </c>
       <c r="D375">
         <v>6312</v>
@@ -10116,7 +10116,7 @@
         <v>15976</v>
       </c>
       <c r="G375">
-        <v>19813</v>
+        <v>19818</v>
       </c>
       <c r="H375">
         <v>23464</v>
@@ -10130,7 +10130,7 @@
         <v>11472</v>
       </c>
       <c r="C376">
-        <v>12958</v>
+        <v>13116</v>
       </c>
       <c r="D376">
         <v>4946</v>
@@ -10142,7 +10142,7 @@
         <v>12686</v>
       </c>
       <c r="G376">
-        <v>15570</v>
+        <v>15572</v>
       </c>
       <c r="H376">
         <v>18733</v>
@@ -10156,7 +10156,7 @@
         <v>11472</v>
       </c>
       <c r="C377">
-        <v>12958</v>
+        <v>13116</v>
       </c>
       <c r="D377">
         <v>4946</v>
@@ -10168,7 +10168,7 @@
         <v>12686</v>
       </c>
       <c r="G377">
-        <v>15570</v>
+        <v>15572</v>
       </c>
       <c r="H377">
         <v>18733</v>
@@ -10182,7 +10182,7 @@
         <v>17234</v>
       </c>
       <c r="C378">
-        <v>18448</v>
+        <v>18628</v>
       </c>
       <c r="D378">
         <v>12849</v>
@@ -10194,7 +10194,7 @@
         <v>20840</v>
       </c>
       <c r="G378">
-        <v>25028</v>
+        <v>25031</v>
       </c>
       <c r="H378">
         <v>27878</v>
@@ -10208,7 +10208,7 @@
         <v>17234</v>
       </c>
       <c r="C379">
-        <v>18448</v>
+        <v>18628</v>
       </c>
       <c r="D379">
         <v>12849</v>
@@ -10220,7 +10220,7 @@
         <v>20840</v>
       </c>
       <c r="G379">
-        <v>25028</v>
+        <v>25031</v>
       </c>
       <c r="H379">
         <v>27878</v>
@@ -10234,7 +10234,7 @@
         <v>17253</v>
       </c>
       <c r="C380">
-        <v>20177</v>
+        <v>20326</v>
       </c>
       <c r="D380">
         <v>10290</v>
@@ -10246,7 +10246,7 @@
         <v>19288</v>
       </c>
       <c r="G380">
-        <v>25022</v>
+        <v>25025</v>
       </c>
       <c r="H380">
         <v>27929</v>
@@ -10260,7 +10260,7 @@
         <v>17253</v>
       </c>
       <c r="C381">
-        <v>20177</v>
+        <v>20326</v>
       </c>
       <c r="D381">
         <v>10290</v>
@@ -10272,7 +10272,7 @@
         <v>19288</v>
       </c>
       <c r="G381">
-        <v>25022</v>
+        <v>25025</v>
       </c>
       <c r="H381">
         <v>27929</v>
@@ -10286,7 +10286,7 @@
         <v>15867</v>
       </c>
       <c r="C382">
-        <v>17132</v>
+        <v>17211</v>
       </c>
       <c r="D382">
         <v>6490</v>
@@ -10298,7 +10298,7 @@
         <v>16751</v>
       </c>
       <c r="G382">
-        <v>20123</v>
+        <v>20124</v>
       </c>
       <c r="H382">
         <v>23438</v>
@@ -10312,7 +10312,7 @@
         <v>16513</v>
       </c>
       <c r="C383">
-        <v>21432</v>
+        <v>21552</v>
       </c>
       <c r="D383">
         <v>6370</v>
@@ -10324,7 +10324,7 @@
         <v>17752</v>
       </c>
       <c r="G383">
-        <v>24685</v>
+        <v>24686</v>
       </c>
       <c r="H383">
         <v>29611</v>
@@ -10338,7 +10338,7 @@
         <v>14225</v>
       </c>
       <c r="C384">
-        <v>16281</v>
+        <v>16477</v>
       </c>
       <c r="D384">
         <v>6407</v>
@@ -10350,7 +10350,7 @@
         <v>15618</v>
       </c>
       <c r="G384">
-        <v>19818</v>
+        <v>19822</v>
       </c>
       <c r="H384">
         <v>23896</v>
@@ -10364,7 +10364,7 @@
         <v>20415</v>
       </c>
       <c r="C385">
-        <v>26637</v>
+        <v>26684</v>
       </c>
       <c r="D385">
         <v>10325</v>
@@ -10376,7 +10376,7 @@
         <v>22679</v>
       </c>
       <c r="G385">
-        <v>32044</v>
+        <v>32046</v>
       </c>
       <c r="H385">
         <v>36971</v>
@@ -10390,7 +10390,7 @@
         <v>10363</v>
       </c>
       <c r="C386">
-        <v>13310</v>
+        <v>13391</v>
       </c>
       <c r="D386">
         <v>4460</v>
@@ -10402,7 +10402,7 @@
         <v>11512</v>
       </c>
       <c r="G386">
-        <v>15802</v>
+        <v>15803</v>
       </c>
       <c r="H386">
         <v>19365</v>
@@ -10416,7 +10416,7 @@
         <v>10363</v>
       </c>
       <c r="C387">
-        <v>13310</v>
+        <v>13391</v>
       </c>
       <c r="D387">
         <v>4460</v>
@@ -10428,7 +10428,7 @@
         <v>11512</v>
       </c>
       <c r="G387">
-        <v>15802</v>
+        <v>15803</v>
       </c>
       <c r="H387">
         <v>19365</v>
@@ -10442,7 +10442,7 @@
         <v>5116</v>
       </c>
       <c r="C388">
-        <v>4992</v>
+        <v>5217</v>
       </c>
       <c r="D388">
         <v>5001</v>
@@ -10454,7 +10454,7 @@
         <v>6365</v>
       </c>
       <c r="G388">
-        <v>7517</v>
+        <v>7529</v>
       </c>
       <c r="H388">
         <v>7918</v>
@@ -10468,7 +10468,7 @@
         <v>4261</v>
       </c>
       <c r="C389">
-        <v>4576</v>
+        <v>4653</v>
       </c>
       <c r="D389">
         <v>2222</v>
@@ -10480,7 +10480,7 @@
         <v>4788</v>
       </c>
       <c r="G389">
-        <v>5732</v>
+        <v>5786</v>
       </c>
       <c r="H389">
         <v>6505</v>
@@ -10494,7 +10494,7 @@
         <v>4261</v>
       </c>
       <c r="C390">
-        <v>4576</v>
+        <v>4653</v>
       </c>
       <c r="D390">
         <v>2222</v>
@@ -10506,7 +10506,7 @@
         <v>4788</v>
       </c>
       <c r="G390">
-        <v>5732</v>
+        <v>5786</v>
       </c>
       <c r="H390">
         <v>6505</v>
@@ -10520,7 +10520,7 @@
         <v>5116</v>
       </c>
       <c r="C391">
-        <v>4992</v>
+        <v>5217</v>
       </c>
       <c r="D391">
         <v>5001</v>
@@ -10532,7 +10532,7 @@
         <v>6365</v>
       </c>
       <c r="G391">
-        <v>7517</v>
+        <v>7529</v>
       </c>
       <c r="H391">
         <v>7918</v>
@@ -10546,7 +10546,7 @@
         <v>4261</v>
       </c>
       <c r="C392">
-        <v>4576</v>
+        <v>4653</v>
       </c>
       <c r="D392">
         <v>2222</v>
@@ -10558,7 +10558,7 @@
         <v>4788</v>
       </c>
       <c r="G392">
-        <v>5732</v>
+        <v>5786</v>
       </c>
       <c r="H392">
         <v>6505</v>
@@ -10572,7 +10572,7 @@
         <v>3285</v>
       </c>
       <c r="C393">
-        <v>3877</v>
+        <v>3910</v>
       </c>
       <c r="D393">
         <v>1792</v>
@@ -10598,7 +10598,7 @@
         <v>3285</v>
       </c>
       <c r="C394">
-        <v>3877</v>
+        <v>3910</v>
       </c>
       <c r="D394">
         <v>1792</v>
@@ -10624,7 +10624,7 @@
         <v>3564</v>
       </c>
       <c r="C395">
-        <v>4225</v>
+        <v>4254</v>
       </c>
       <c r="D395">
         <v>1094</v>
@@ -10636,7 +10636,7 @@
         <v>3852</v>
       </c>
       <c r="G395">
-        <v>4769</v>
+        <v>4770</v>
       </c>
       <c r="H395">
         <v>5812</v>
@@ -10650,7 +10650,7 @@
         <v>3564</v>
       </c>
       <c r="C396">
-        <v>4225</v>
+        <v>4254</v>
       </c>
       <c r="D396">
         <v>1094</v>
@@ -10662,7 +10662,7 @@
         <v>3852</v>
       </c>
       <c r="G396">
-        <v>4769</v>
+        <v>4770</v>
       </c>
       <c r="H396">
         <v>5812</v>
@@ -10676,7 +10676,7 @@
         <v>5507</v>
       </c>
       <c r="C397">
-        <v>4883</v>
+        <v>4896</v>
       </c>
       <c r="D397">
         <v>2273</v>
@@ -10702,7 +10702,7 @@
         <v>5507</v>
       </c>
       <c r="C398">
-        <v>4883</v>
+        <v>4896</v>
       </c>
       <c r="D398">
         <v>2273</v>
@@ -10728,7 +10728,7 @@
         <v>3162</v>
       </c>
       <c r="C399">
-        <v>2800</v>
+        <v>3026</v>
       </c>
       <c r="D399">
         <v>2151</v>
@@ -10740,7 +10740,7 @@
         <v>3636</v>
       </c>
       <c r="G399">
-        <v>3927</v>
+        <v>3930</v>
       </c>
       <c r="H399">
         <v>4638</v>
@@ -10754,7 +10754,7 @@
         <v>2914</v>
       </c>
       <c r="C400">
-        <v>2952</v>
+        <v>3103</v>
       </c>
       <c r="D400">
         <v>1701</v>
@@ -10766,7 +10766,7 @@
         <v>3224</v>
       </c>
       <c r="G400">
-        <v>3770</v>
+        <v>3773</v>
       </c>
       <c r="H400">
         <v>4369</v>
@@ -10780,7 +10780,7 @@
         <v>3166</v>
       </c>
       <c r="C401">
-        <v>3092</v>
+        <v>3279</v>
       </c>
       <c r="D401">
         <v>1934</v>
@@ -10792,7 +10792,7 @@
         <v>3557</v>
       </c>
       <c r="G401">
-        <v>4054</v>
+        <v>4056</v>
       </c>
       <c r="H401">
         <v>4768</v>
@@ -10806,7 +10806,7 @@
         <v>3378</v>
       </c>
       <c r="C402">
-        <v>2673</v>
+        <v>2729</v>
       </c>
       <c r="D402">
         <v>1343</v>
@@ -10818,7 +10818,7 @@
         <v>3537</v>
       </c>
       <c r="G402">
-        <v>3252</v>
+        <v>3254</v>
       </c>
       <c r="H402">
         <v>4315</v>
@@ -10832,7 +10832,7 @@
         <v>2914</v>
       </c>
       <c r="C403">
-        <v>2952</v>
+        <v>3103</v>
       </c>
       <c r="D403">
         <v>1701</v>
@@ -10844,7 +10844,7 @@
         <v>3224</v>
       </c>
       <c r="G403">
-        <v>3770</v>
+        <v>3773</v>
       </c>
       <c r="H403">
         <v>4369</v>
@@ -10858,7 +10858,7 @@
         <v>2424</v>
       </c>
       <c r="C404">
-        <v>2437</v>
+        <v>2542</v>
       </c>
       <c r="D404">
         <v>1541</v>
@@ -10870,7 +10870,7 @@
         <v>2707</v>
       </c>
       <c r="G404">
-        <v>3153</v>
+        <v>3154</v>
       </c>
       <c r="H404">
         <v>3614</v>
@@ -10884,7 +10884,7 @@
         <v>2424</v>
       </c>
       <c r="C405">
-        <v>2437</v>
+        <v>2542</v>
       </c>
       <c r="D405">
         <v>1541</v>
@@ -10896,7 +10896,7 @@
         <v>2707</v>
       </c>
       <c r="G405">
-        <v>3153</v>
+        <v>3154</v>
       </c>
       <c r="H405">
         <v>3614</v>
@@ -10910,7 +10910,7 @@
         <v>2424</v>
       </c>
       <c r="C406">
-        <v>2437</v>
+        <v>2542</v>
       </c>
       <c r="D406">
         <v>1541</v>
@@ -10922,7 +10922,7 @@
         <v>2707</v>
       </c>
       <c r="G406">
-        <v>3153</v>
+        <v>3154</v>
       </c>
       <c r="H406">
         <v>3614</v>
@@ -10936,7 +10936,7 @@
         <v>2014</v>
       </c>
       <c r="C407">
-        <v>2108</v>
+        <v>2165</v>
       </c>
       <c r="D407">
         <v>1353</v>
@@ -10962,7 +10962,7 @@
         <v>2014</v>
       </c>
       <c r="C408">
-        <v>2108</v>
+        <v>2165</v>
       </c>
       <c r="D408">
         <v>1353</v>
@@ -10988,7 +10988,7 @@
         <v>2014</v>
       </c>
       <c r="C409">
-        <v>2108</v>
+        <v>2165</v>
       </c>
       <c r="D409">
         <v>1353</v>
@@ -11014,7 +11014,7 @@
         <v>4313</v>
       </c>
       <c r="C410">
-        <v>9857</v>
+        <v>9978</v>
       </c>
       <c r="D410">
         <v>4334</v>
@@ -11026,7 +11026,7 @@
         <v>6270</v>
       </c>
       <c r="G410">
-        <v>12358</v>
+        <v>12360</v>
       </c>
       <c r="H410">
         <v>13045</v>
@@ -11040,7 +11040,7 @@
         <v>3671</v>
       </c>
       <c r="C411">
-        <v>7642</v>
+        <v>7715</v>
       </c>
       <c r="D411">
         <v>2672</v>
@@ -11052,7 +11052,7 @@
         <v>4773</v>
       </c>
       <c r="G411">
-        <v>9321</v>
+        <v>9328</v>
       </c>
       <c r="H411">
         <v>10045</v>
@@ -11066,7 +11066,7 @@
         <v>3671</v>
       </c>
       <c r="C412">
-        <v>7642</v>
+        <v>7715</v>
       </c>
       <c r="D412">
         <v>2672</v>
@@ -11078,7 +11078,7 @@
         <v>4773</v>
       </c>
       <c r="G412">
-        <v>9321</v>
+        <v>9328</v>
       </c>
       <c r="H412">
         <v>10045</v>
@@ -11092,7 +11092,7 @@
         <v>3498</v>
       </c>
       <c r="C413">
-        <v>7434</v>
+        <v>7508</v>
       </c>
       <c r="D413">
         <v>1435</v>
@@ -11104,7 +11104,7 @@
         <v>4089</v>
       </c>
       <c r="G413">
-        <v>8308</v>
+        <v>8312</v>
       </c>
       <c r="H413">
         <v>9387</v>
@@ -11118,7 +11118,7 @@
         <v>4319</v>
       </c>
       <c r="C414">
-        <v>10984</v>
+        <v>11085</v>
       </c>
       <c r="D414">
         <v>3428</v>
@@ -11130,7 +11130,7 @@
         <v>5630</v>
       </c>
       <c r="G414">
-        <v>12953</v>
+        <v>12955</v>
       </c>
       <c r="H414">
         <v>13683</v>
@@ -11144,7 +11144,7 @@
         <v>4440</v>
       </c>
       <c r="C415">
-        <v>8236</v>
+        <v>8267</v>
       </c>
       <c r="D415">
         <v>2886</v>
@@ -11170,7 +11170,7 @@
         <v>4440</v>
       </c>
       <c r="C416">
-        <v>8236</v>
+        <v>8267</v>
       </c>
       <c r="D416">
         <v>2886</v>
@@ -11196,7 +11196,7 @@
         <v>4019</v>
       </c>
       <c r="C417">
-        <v>5105</v>
+        <v>5162</v>
       </c>
       <c r="D417">
         <v>2057</v>
@@ -11222,7 +11222,7 @@
         <v>4019</v>
       </c>
       <c r="C418">
-        <v>5105</v>
+        <v>5162</v>
       </c>
       <c r="D418">
         <v>2057</v>
@@ -11248,7 +11248,7 @@
         <v>7569</v>
       </c>
       <c r="C419">
-        <v>8034</v>
+        <v>8289</v>
       </c>
       <c r="D419">
         <v>5245</v>
@@ -11260,7 +11260,7 @@
         <v>9008</v>
       </c>
       <c r="G419">
-        <v>10930</v>
+        <v>10932</v>
       </c>
       <c r="H419">
         <v>12614</v>
@@ -11274,7 +11274,7 @@
         <v>7569</v>
       </c>
       <c r="C420">
-        <v>8034</v>
+        <v>8289</v>
       </c>
       <c r="D420">
         <v>5245</v>
@@ -11286,7 +11286,7 @@
         <v>9008</v>
       </c>
       <c r="G420">
-        <v>10930</v>
+        <v>10932</v>
       </c>
       <c r="H420">
         <v>12614</v>
@@ -11300,7 +11300,7 @@
         <v>8076</v>
       </c>
       <c r="C421">
-        <v>5723</v>
+        <v>6074</v>
       </c>
       <c r="D421">
         <v>5646</v>
@@ -11312,7 +11312,7 @@
         <v>9457</v>
       </c>
       <c r="G421">
-        <v>8955</v>
+        <v>8962</v>
       </c>
       <c r="H421">
         <v>11263</v>
@@ -11326,7 +11326,7 @@
         <v>8076</v>
       </c>
       <c r="C422">
-        <v>5723</v>
+        <v>6074</v>
       </c>
       <c r="D422">
         <v>5646</v>
@@ -11338,7 +11338,7 @@
         <v>9457</v>
       </c>
       <c r="G422">
-        <v>8955</v>
+        <v>8962</v>
       </c>
       <c r="H422">
         <v>11263</v>
@@ -11352,7 +11352,7 @@
         <v>7569</v>
       </c>
       <c r="C423">
-        <v>8034</v>
+        <v>8289</v>
       </c>
       <c r="D423">
         <v>5245</v>
@@ -11364,7 +11364,7 @@
         <v>9008</v>
       </c>
       <c r="G423">
-        <v>10930</v>
+        <v>10932</v>
       </c>
       <c r="H423">
         <v>12614</v>
@@ -11378,7 +11378,7 @@
         <v>7569</v>
       </c>
       <c r="C424">
-        <v>8034</v>
+        <v>8289</v>
       </c>
       <c r="D424">
         <v>5245</v>
@@ -11390,7 +11390,7 @@
         <v>9008</v>
       </c>
       <c r="G424">
-        <v>10930</v>
+        <v>10932</v>
       </c>
       <c r="H424">
         <v>12614</v>
@@ -11404,7 +11404,7 @@
         <v>8076</v>
       </c>
       <c r="C425">
-        <v>5723</v>
+        <v>6074</v>
       </c>
       <c r="D425">
         <v>5646</v>
@@ -11416,7 +11416,7 @@
         <v>9457</v>
       </c>
       <c r="G425">
-        <v>8955</v>
+        <v>8962</v>
       </c>
       <c r="H425">
         <v>11263</v>
@@ -11430,7 +11430,7 @@
         <v>7569</v>
       </c>
       <c r="C426">
-        <v>8034</v>
+        <v>8289</v>
       </c>
       <c r="D426">
         <v>5245</v>
@@ -11442,7 +11442,7 @@
         <v>9008</v>
       </c>
       <c r="G426">
-        <v>10930</v>
+        <v>10932</v>
       </c>
       <c r="H426">
         <v>12614</v>
@@ -11456,7 +11456,7 @@
         <v>7582</v>
       </c>
       <c r="C427">
-        <v>8853</v>
+        <v>9066</v>
       </c>
       <c r="D427">
         <v>4393</v>
@@ -11468,7 +11468,7 @@
         <v>8589</v>
       </c>
       <c r="G427">
-        <v>11208</v>
+        <v>11210</v>
       </c>
       <c r="H427">
         <v>12957</v>
@@ -11482,7 +11482,7 @@
         <v>7582</v>
       </c>
       <c r="C428">
-        <v>8853</v>
+        <v>9066</v>
       </c>
       <c r="D428">
         <v>4393</v>
@@ -11494,7 +11494,7 @@
         <v>8589</v>
       </c>
       <c r="G428">
-        <v>11208</v>
+        <v>11210</v>
       </c>
       <c r="H428">
         <v>12957</v>
@@ -11508,7 +11508,7 @@
         <v>7569</v>
       </c>
       <c r="C429">
-        <v>8034</v>
+        <v>8289</v>
       </c>
       <c r="D429">
         <v>5245</v>
@@ -11520,7 +11520,7 @@
         <v>9008</v>
       </c>
       <c r="G429">
-        <v>10930</v>
+        <v>10932</v>
       </c>
       <c r="H429">
         <v>12614</v>
@@ -11534,7 +11534,7 @@
         <v>7569</v>
       </c>
       <c r="C430">
-        <v>8034</v>
+        <v>8289</v>
       </c>
       <c r="D430">
         <v>5245</v>
@@ -11546,7 +11546,7 @@
         <v>9008</v>
       </c>
       <c r="G430">
-        <v>10930</v>
+        <v>10932</v>
       </c>
       <c r="H430">
         <v>12614</v>
@@ -11560,7 +11560,7 @@
         <v>8076</v>
       </c>
       <c r="C431">
-        <v>5723</v>
+        <v>6074</v>
       </c>
       <c r="D431">
         <v>5646</v>
@@ -11572,7 +11572,7 @@
         <v>9457</v>
       </c>
       <c r="G431">
-        <v>8955</v>
+        <v>8962</v>
       </c>
       <c r="H431">
         <v>11263</v>
@@ -11586,7 +11586,7 @@
         <v>7569</v>
       </c>
       <c r="C432">
-        <v>8034</v>
+        <v>8289</v>
       </c>
       <c r="D432">
         <v>5245</v>
@@ -11598,7 +11598,7 @@
         <v>9008</v>
       </c>
       <c r="G432">
-        <v>10930</v>
+        <v>10932</v>
       </c>
       <c r="H432">
         <v>12614</v>
@@ -11612,7 +11612,7 @@
         <v>7569</v>
       </c>
       <c r="C433">
-        <v>8034</v>
+        <v>8289</v>
       </c>
       <c r="D433">
         <v>5245</v>
@@ -11624,7 +11624,7 @@
         <v>9008</v>
       </c>
       <c r="G433">
-        <v>10930</v>
+        <v>10932</v>
       </c>
       <c r="H433">
         <v>12614</v>
@@ -11638,7 +11638,7 @@
         <v>6386</v>
       </c>
       <c r="C434">
-        <v>5196</v>
+        <v>5367</v>
       </c>
       <c r="D434">
         <v>3387</v>
@@ -11650,7 +11650,7 @@
         <v>7436</v>
       </c>
       <c r="G434">
-        <v>7240</v>
+        <v>7245</v>
       </c>
       <c r="H434">
         <v>9222</v>
@@ -11664,7 +11664,7 @@
         <v>7569</v>
       </c>
       <c r="C435">
-        <v>8034</v>
+        <v>8289</v>
       </c>
       <c r="D435">
         <v>5245</v>
@@ -11676,7 +11676,7 @@
         <v>9008</v>
       </c>
       <c r="G435">
-        <v>10930</v>
+        <v>10932</v>
       </c>
       <c r="H435">
         <v>12614</v>
@@ -11690,7 +11690,7 @@
         <v>5439</v>
       </c>
       <c r="C436">
-        <v>6098</v>
+        <v>6111</v>
       </c>
       <c r="D436">
         <v>1408</v>
@@ -11716,7 +11716,7 @@
         <v>4203</v>
       </c>
       <c r="C437">
-        <v>4179</v>
+        <v>4234</v>
       </c>
       <c r="D437">
         <v>2221</v>
@@ -11742,7 +11742,7 @@
         <v>4203</v>
       </c>
       <c r="C438">
-        <v>4179</v>
+        <v>4234</v>
       </c>
       <c r="D438">
         <v>2221</v>
@@ -11768,7 +11768,7 @@
         <v>4203</v>
       </c>
       <c r="C439">
-        <v>4179</v>
+        <v>4234</v>
       </c>
       <c r="D439">
         <v>2221</v>
@@ -11794,7 +11794,7 @@
         <v>4203</v>
       </c>
       <c r="C440">
-        <v>4179</v>
+        <v>4234</v>
       </c>
       <c r="D440">
         <v>2221</v>
@@ -11820,7 +11820,7 @@
         <v>4203</v>
       </c>
       <c r="C441">
-        <v>4179</v>
+        <v>4234</v>
       </c>
       <c r="D441">
         <v>2221</v>
@@ -11846,7 +11846,7 @@
         <v>4325</v>
       </c>
       <c r="C442">
-        <v>3859</v>
+        <v>3924</v>
       </c>
       <c r="D442">
         <v>2275</v>
@@ -11872,7 +11872,7 @@
         <v>4203</v>
       </c>
       <c r="C443">
-        <v>4179</v>
+        <v>4234</v>
       </c>
       <c r="D443">
         <v>2221</v>
@@ -11898,7 +11898,7 @@
         <v>4203</v>
       </c>
       <c r="C444">
-        <v>4179</v>
+        <v>4234</v>
       </c>
       <c r="D444">
         <v>2221</v>
@@ -11924,7 +11924,7 @@
         <v>4203</v>
       </c>
       <c r="C445">
-        <v>4179</v>
+        <v>4234</v>
       </c>
       <c r="D445">
         <v>2221</v>
@@ -11950,7 +11950,7 @@
         <v>4203</v>
       </c>
       <c r="C446">
-        <v>4179</v>
+        <v>4234</v>
       </c>
       <c r="D446">
         <v>2221</v>
@@ -11976,7 +11976,7 @@
         <v>4203</v>
       </c>
       <c r="C447">
-        <v>4179</v>
+        <v>4234</v>
       </c>
       <c r="D447">
         <v>2221</v>
@@ -12002,7 +12002,7 @@
         <v>14690</v>
       </c>
       <c r="C448">
-        <v>12588</v>
+        <v>12630</v>
       </c>
       <c r="D448">
         <v>3522</v>
@@ -12014,7 +12014,7 @@
         <v>15599</v>
       </c>
       <c r="G448">
-        <v>14586</v>
+        <v>14594</v>
       </c>
       <c r="H448">
         <v>20080</v>
@@ -12028,7 +12028,7 @@
         <v>14690</v>
       </c>
       <c r="C449">
-        <v>12588</v>
+        <v>12630</v>
       </c>
       <c r="D449">
         <v>3522</v>
@@ -12040,7 +12040,7 @@
         <v>15599</v>
       </c>
       <c r="G449">
-        <v>14586</v>
+        <v>14594</v>
       </c>
       <c r="H449">
         <v>20080</v>
@@ -12054,7 +12054,7 @@
         <v>14690</v>
       </c>
       <c r="C450">
-        <v>12588</v>
+        <v>12630</v>
       </c>
       <c r="D450">
         <v>3522</v>
@@ -12066,7 +12066,7 @@
         <v>15599</v>
       </c>
       <c r="G450">
-        <v>14586</v>
+        <v>14594</v>
       </c>
       <c r="H450">
         <v>20080</v>
@@ -12080,7 +12080,7 @@
         <v>14690</v>
       </c>
       <c r="C451">
-        <v>12588</v>
+        <v>12630</v>
       </c>
       <c r="D451">
         <v>3522</v>
@@ -12092,7 +12092,7 @@
         <v>15599</v>
       </c>
       <c r="G451">
-        <v>14586</v>
+        <v>14594</v>
       </c>
       <c r="H451">
         <v>20080</v>
@@ -12106,7 +12106,7 @@
         <v>14690</v>
       </c>
       <c r="C452">
-        <v>12588</v>
+        <v>12630</v>
       </c>
       <c r="D452">
         <v>3522</v>
@@ -12118,7 +12118,7 @@
         <v>15599</v>
       </c>
       <c r="G452">
-        <v>14586</v>
+        <v>14594</v>
       </c>
       <c r="H452">
         <v>20080</v>
@@ -12132,7 +12132,7 @@
         <v>14690</v>
       </c>
       <c r="C453">
-        <v>12588</v>
+        <v>12630</v>
       </c>
       <c r="D453">
         <v>3522</v>
@@ -12144,7 +12144,7 @@
         <v>15599</v>
       </c>
       <c r="G453">
-        <v>14586</v>
+        <v>14594</v>
       </c>
       <c r="H453">
         <v>20080</v>
@@ -12158,7 +12158,7 @@
         <v>9259</v>
       </c>
       <c r="C454">
-        <v>10131</v>
+        <v>10230</v>
       </c>
       <c r="D454">
         <v>4782</v>
@@ -12170,7 +12170,7 @@
         <v>10389</v>
       </c>
       <c r="G454">
-        <v>12692</v>
+        <v>12694</v>
       </c>
       <c r="H454">
         <v>15097</v>
@@ -12184,7 +12184,7 @@
         <v>9259</v>
       </c>
       <c r="C455">
-        <v>10131</v>
+        <v>10230</v>
       </c>
       <c r="D455">
         <v>4782</v>
@@ -12196,7 +12196,7 @@
         <v>10389</v>
       </c>
       <c r="G455">
-        <v>12692</v>
+        <v>12694</v>
       </c>
       <c r="H455">
         <v>15097</v>
@@ -12210,7 +12210,7 @@
         <v>9259</v>
       </c>
       <c r="C456">
-        <v>10131</v>
+        <v>10230</v>
       </c>
       <c r="D456">
         <v>4782</v>
@@ -12222,7 +12222,7 @@
         <v>10389</v>
       </c>
       <c r="G456">
-        <v>12692</v>
+        <v>12694</v>
       </c>
       <c r="H456">
         <v>15097</v>
@@ -12236,7 +12236,7 @@
         <v>9259</v>
       </c>
       <c r="C457">
-        <v>10131</v>
+        <v>10230</v>
       </c>
       <c r="D457">
         <v>4782</v>
@@ -12248,7 +12248,7 @@
         <v>10389</v>
       </c>
       <c r="G457">
-        <v>12692</v>
+        <v>12694</v>
       </c>
       <c r="H457">
         <v>15097</v>
@@ -12262,7 +12262,7 @@
         <v>9259</v>
       </c>
       <c r="C458">
-        <v>10131</v>
+        <v>10230</v>
       </c>
       <c r="D458">
         <v>4782</v>
@@ -12274,7 +12274,7 @@
         <v>10389</v>
       </c>
       <c r="G458">
-        <v>12692</v>
+        <v>12694</v>
       </c>
       <c r="H458">
         <v>15097</v>
@@ -12288,7 +12288,7 @@
         <v>9259</v>
       </c>
       <c r="C459">
-        <v>10131</v>
+        <v>10230</v>
       </c>
       <c r="D459">
         <v>4782</v>
@@ -12300,7 +12300,7 @@
         <v>10389</v>
       </c>
       <c r="G459">
-        <v>12692</v>
+        <v>12694</v>
       </c>
       <c r="H459">
         <v>15097</v>
@@ -12314,7 +12314,7 @@
         <v>9259</v>
       </c>
       <c r="C460">
-        <v>10131</v>
+        <v>10230</v>
       </c>
       <c r="D460">
         <v>4782</v>
@@ -12326,7 +12326,7 @@
         <v>10389</v>
       </c>
       <c r="G460">
-        <v>12692</v>
+        <v>12694</v>
       </c>
       <c r="H460">
         <v>15097</v>
@@ -12340,7 +12340,7 @@
         <v>9259</v>
       </c>
       <c r="C461">
-        <v>10131</v>
+        <v>10230</v>
       </c>
       <c r="D461">
         <v>4782</v>
@@ -12352,7 +12352,7 @@
         <v>10389</v>
       </c>
       <c r="G461">
-        <v>12692</v>
+        <v>12694</v>
       </c>
       <c r="H461">
         <v>15097</v>
@@ -12366,7 +12366,7 @@
         <v>9259</v>
       </c>
       <c r="C462">
-        <v>10131</v>
+        <v>10230</v>
       </c>
       <c r="D462">
         <v>4782</v>
@@ -12378,7 +12378,7 @@
         <v>10389</v>
       </c>
       <c r="G462">
-        <v>12692</v>
+        <v>12694</v>
       </c>
       <c r="H462">
         <v>15097</v>
@@ -12392,7 +12392,7 @@
         <v>7582</v>
       </c>
       <c r="C463">
-        <v>8853</v>
+        <v>9066</v>
       </c>
       <c r="D463">
         <v>4393</v>
@@ -12404,7 +12404,7 @@
         <v>8589</v>
       </c>
       <c r="G463">
-        <v>11208</v>
+        <v>11210</v>
       </c>
       <c r="H463">
         <v>12957</v>
@@ -12418,7 +12418,7 @@
         <v>7582</v>
       </c>
       <c r="C464">
-        <v>8853</v>
+        <v>9066</v>
       </c>
       <c r="D464">
         <v>4393</v>
@@ -12430,7 +12430,7 @@
         <v>8589</v>
       </c>
       <c r="G464">
-        <v>11208</v>
+        <v>11210</v>
       </c>
       <c r="H464">
         <v>12957</v>
@@ -12444,7 +12444,7 @@
         <v>6386</v>
       </c>
       <c r="C465">
-        <v>5196</v>
+        <v>5367</v>
       </c>
       <c r="D465">
         <v>3387</v>
@@ -12456,7 +12456,7 @@
         <v>7436</v>
       </c>
       <c r="G465">
-        <v>7240</v>
+        <v>7245</v>
       </c>
       <c r="H465">
         <v>9222</v>
@@ -12470,7 +12470,7 @@
         <v>6396</v>
       </c>
       <c r="C466">
-        <v>5758</v>
+        <v>5898</v>
       </c>
       <c r="D466">
         <v>2799</v>
@@ -12482,7 +12482,7 @@
         <v>7197</v>
       </c>
       <c r="G466">
-        <v>7427</v>
+        <v>7430</v>
       </c>
       <c r="H466">
         <v>9394</v>
@@ -12496,7 +12496,7 @@
         <v>7582</v>
       </c>
       <c r="C467">
-        <v>8853</v>
+        <v>9066</v>
       </c>
       <c r="D467">
         <v>4393</v>
@@ -12508,7 +12508,7 @@
         <v>8589</v>
       </c>
       <c r="G467">
-        <v>11208</v>
+        <v>11210</v>
       </c>
       <c r="H467">
         <v>12957</v>
@@ -12522,7 +12522,7 @@
         <v>14690</v>
       </c>
       <c r="C468">
-        <v>12588</v>
+        <v>12630</v>
       </c>
       <c r="D468">
         <v>3522</v>
@@ -12534,7 +12534,7 @@
         <v>15599</v>
       </c>
       <c r="G468">
-        <v>14586</v>
+        <v>14594</v>
       </c>
       <c r="H468">
         <v>20080</v>
@@ -12548,7 +12548,7 @@
         <v>14690</v>
       </c>
       <c r="C469">
-        <v>12588</v>
+        <v>12630</v>
       </c>
       <c r="D469">
         <v>3522</v>
@@ -12560,7 +12560,7 @@
         <v>15599</v>
       </c>
       <c r="G469">
-        <v>14586</v>
+        <v>14594</v>
       </c>
       <c r="H469">
         <v>20080</v>
@@ -12574,7 +12574,7 @@
         <v>14690</v>
       </c>
       <c r="C470">
-        <v>12588</v>
+        <v>12630</v>
       </c>
       <c r="D470">
         <v>3522</v>
@@ -12586,7 +12586,7 @@
         <v>15599</v>
       </c>
       <c r="G470">
-        <v>14586</v>
+        <v>14594</v>
       </c>
       <c r="H470">
         <v>20080</v>
@@ -12600,7 +12600,7 @@
         <v>7582</v>
       </c>
       <c r="C471">
-        <v>8853</v>
+        <v>9066</v>
       </c>
       <c r="D471">
         <v>4393</v>
@@ -12612,7 +12612,7 @@
         <v>8589</v>
       </c>
       <c r="G471">
-        <v>11208</v>
+        <v>11210</v>
       </c>
       <c r="H471">
         <v>12957</v>
@@ -12626,7 +12626,7 @@
         <v>9259</v>
       </c>
       <c r="C472">
-        <v>10131</v>
+        <v>10230</v>
       </c>
       <c r="D472">
         <v>4782</v>
@@ -12638,7 +12638,7 @@
         <v>10389</v>
       </c>
       <c r="G472">
-        <v>12692</v>
+        <v>12694</v>
       </c>
       <c r="H472">
         <v>15097</v>
@@ -12652,7 +12652,7 @@
         <v>6396</v>
       </c>
       <c r="C473">
-        <v>5758</v>
+        <v>5898</v>
       </c>
       <c r="D473">
         <v>2799</v>
@@ -12664,7 +12664,7 @@
         <v>7197</v>
       </c>
       <c r="G473">
-        <v>7427</v>
+        <v>7430</v>
       </c>
       <c r="H473">
         <v>9394</v>
@@ -12678,7 +12678,7 @@
         <v>6396</v>
       </c>
       <c r="C474">
-        <v>5758</v>
+        <v>5898</v>
       </c>
       <c r="D474">
         <v>2799</v>
@@ -12690,7 +12690,7 @@
         <v>7197</v>
       </c>
       <c r="G474">
-        <v>7427</v>
+        <v>7430</v>
       </c>
       <c r="H474">
         <v>9394</v>
@@ -12704,7 +12704,7 @@
         <v>5439</v>
       </c>
       <c r="C475">
-        <v>6098</v>
+        <v>6111</v>
       </c>
       <c r="D475">
         <v>1408</v>
@@ -12730,7 +12730,7 @@
         <v>4931</v>
       </c>
       <c r="C476">
-        <v>5251</v>
+        <v>5272</v>
       </c>
       <c r="D476">
         <v>2329</v>
@@ -12742,7 +12742,7 @@
         <v>5623</v>
       </c>
       <c r="G476">
-        <v>6603</v>
+        <v>6606</v>
       </c>
       <c r="H476">
         <v>8097</v>
@@ -12756,7 +12756,7 @@
         <v>4931</v>
       </c>
       <c r="C477">
-        <v>5251</v>
+        <v>5272</v>
       </c>
       <c r="D477">
         <v>2329</v>
@@ -12768,7 +12768,7 @@
         <v>5623</v>
       </c>
       <c r="G477">
-        <v>6603</v>
+        <v>6606</v>
       </c>
       <c r="H477">
         <v>8097</v>
@@ -12782,7 +12782,7 @@
         <v>7308</v>
       </c>
       <c r="C478">
-        <v>5280</v>
+        <v>5842</v>
       </c>
       <c r="D478">
         <v>5205</v>
@@ -12794,7 +12794,7 @@
         <v>8151</v>
       </c>
       <c r="G478">
-        <v>7888</v>
+        <v>7912</v>
       </c>
       <c r="H478">
         <v>9269</v>
@@ -12808,7 +12808,7 @@
         <v>6222</v>
       </c>
       <c r="C479">
-        <v>6424</v>
+        <v>6750</v>
       </c>
       <c r="D479">
         <v>4568</v>
@@ -12820,7 +12820,7 @@
         <v>7063</v>
       </c>
       <c r="G479">
-        <v>8613</v>
+        <v>8617</v>
       </c>
       <c r="H479">
         <v>9331</v>
@@ -12834,7 +12834,7 @@
         <v>7097</v>
       </c>
       <c r="C480">
-        <v>6832</v>
+        <v>7252</v>
       </c>
       <c r="D480">
         <v>4864</v>
@@ -12846,7 +12846,7 @@
         <v>7956</v>
       </c>
       <c r="G480">
-        <v>9133</v>
+        <v>9141</v>
       </c>
       <c r="H480">
         <v>10167</v>
@@ -12860,7 +12860,7 @@
         <v>7308</v>
       </c>
       <c r="C481">
-        <v>5280</v>
+        <v>5842</v>
       </c>
       <c r="D481">
         <v>5205</v>
@@ -12872,7 +12872,7 @@
         <v>8151</v>
       </c>
       <c r="G481">
-        <v>7888</v>
+        <v>7912</v>
       </c>
       <c r="H481">
         <v>9269</v>
@@ -12886,7 +12886,7 @@
         <v>7308</v>
       </c>
       <c r="C482">
-        <v>5280</v>
+        <v>5842</v>
       </c>
       <c r="D482">
         <v>5205</v>
@@ -12898,7 +12898,7 @@
         <v>8151</v>
       </c>
       <c r="G482">
-        <v>7888</v>
+        <v>7912</v>
       </c>
       <c r="H482">
         <v>9269</v>
@@ -12912,7 +12912,7 @@
         <v>7308</v>
       </c>
       <c r="C483">
-        <v>5280</v>
+        <v>5842</v>
       </c>
       <c r="D483">
         <v>5205</v>
@@ -12924,7 +12924,7 @@
         <v>8151</v>
       </c>
       <c r="G483">
-        <v>7888</v>
+        <v>7912</v>
       </c>
       <c r="H483">
         <v>9269</v>
@@ -12938,7 +12938,7 @@
         <v>7308</v>
       </c>
       <c r="C484">
-        <v>5280</v>
+        <v>5842</v>
       </c>
       <c r="D484">
         <v>5205</v>
@@ -12950,7 +12950,7 @@
         <v>8151</v>
       </c>
       <c r="G484">
-        <v>7888</v>
+        <v>7912</v>
       </c>
       <c r="H484">
         <v>9269</v>
@@ -12964,7 +12964,7 @@
         <v>7097</v>
       </c>
       <c r="C485">
-        <v>6832</v>
+        <v>7252</v>
       </c>
       <c r="D485">
         <v>4864</v>
@@ -12976,7 +12976,7 @@
         <v>7956</v>
       </c>
       <c r="G485">
-        <v>9133</v>
+        <v>9141</v>
       </c>
       <c r="H485">
         <v>10167</v>
@@ -12990,7 +12990,7 @@
         <v>6761</v>
       </c>
       <c r="C486">
-        <v>6587</v>
+        <v>6819</v>
       </c>
       <c r="D486">
         <v>5124</v>
@@ -13002,7 +13002,7 @@
         <v>7737</v>
       </c>
       <c r="G486">
-        <v>9040</v>
+        <v>9043</v>
       </c>
       <c r="H486">
         <v>9899</v>
@@ -13016,7 +13016,7 @@
         <v>6796</v>
       </c>
       <c r="C487">
-        <v>6472</v>
+        <v>6585</v>
       </c>
       <c r="D487">
         <v>3887</v>
@@ -13028,7 +13028,7 @@
         <v>7376</v>
       </c>
       <c r="G487">
-        <v>8242</v>
+        <v>8247</v>
       </c>
       <c r="H487">
         <v>9327</v>
@@ -13042,7 +13042,7 @@
         <v>6474</v>
       </c>
       <c r="C488">
-        <v>6909</v>
+        <v>6932</v>
       </c>
       <c r="D488">
         <v>2542</v>
@@ -13068,7 +13068,7 @@
         <v>6474</v>
       </c>
       <c r="C489">
-        <v>6909</v>
+        <v>6932</v>
       </c>
       <c r="D489">
         <v>2542</v>
@@ -13094,7 +13094,7 @@
         <v>8579</v>
       </c>
       <c r="C490">
-        <v>9972</v>
+        <v>10351</v>
       </c>
       <c r="D490">
         <v>6015</v>
@@ -13106,7 +13106,7 @@
         <v>9931</v>
       </c>
       <c r="G490">
-        <v>12892</v>
+        <v>12901</v>
       </c>
       <c r="H490">
         <v>14354</v>
@@ -13120,7 +13120,7 @@
         <v>8588</v>
       </c>
       <c r="C491">
-        <v>10944</v>
+        <v>11258</v>
       </c>
       <c r="D491">
         <v>5309</v>
@@ -13132,7 +13132,7 @@
         <v>9582</v>
       </c>
       <c r="G491">
-        <v>13393</v>
+        <v>13401</v>
       </c>
       <c r="H491">
         <v>14866</v>
@@ -13146,7 +13146,7 @@
         <v>8579</v>
       </c>
       <c r="C492">
-        <v>9972</v>
+        <v>10351</v>
       </c>
       <c r="D492">
         <v>6015</v>
@@ -13158,7 +13158,7 @@
         <v>9931</v>
       </c>
       <c r="G492">
-        <v>12892</v>
+        <v>12901</v>
       </c>
       <c r="H492">
         <v>14354</v>
@@ -13172,7 +13172,7 @@
         <v>8579</v>
       </c>
       <c r="C493">
-        <v>9972</v>
+        <v>10351</v>
       </c>
       <c r="D493">
         <v>6015</v>
@@ -13184,7 +13184,7 @@
         <v>9931</v>
       </c>
       <c r="G493">
-        <v>12892</v>
+        <v>12901</v>
       </c>
       <c r="H493">
         <v>14354</v>
@@ -13198,7 +13198,7 @@
         <v>8579</v>
       </c>
       <c r="C494">
-        <v>9972</v>
+        <v>10351</v>
       </c>
       <c r="D494">
         <v>6015</v>
@@ -13210,7 +13210,7 @@
         <v>9931</v>
       </c>
       <c r="G494">
-        <v>12892</v>
+        <v>12901</v>
       </c>
       <c r="H494">
         <v>14354</v>
@@ -13224,7 +13224,7 @@
         <v>7417</v>
       </c>
       <c r="C495">
-        <v>11480</v>
+        <v>11605</v>
       </c>
       <c r="D495">
         <v>2375</v>
@@ -13236,7 +13236,7 @@
         <v>7954</v>
       </c>
       <c r="G495">
-        <v>12631</v>
+        <v>12637</v>
       </c>
       <c r="H495">
         <v>14543</v>
@@ -13250,7 +13250,7 @@
         <v>8345</v>
       </c>
       <c r="C496">
-        <v>13019</v>
+        <v>13239</v>
       </c>
       <c r="D496">
         <v>4070</v>
@@ -13262,7 +13262,7 @@
         <v>9121</v>
       </c>
       <c r="G496">
-        <v>14954</v>
+        <v>14967</v>
       </c>
       <c r="H496">
         <v>16754</v>
@@ -13276,7 +13276,7 @@
         <v>7417</v>
       </c>
       <c r="C497">
-        <v>11480</v>
+        <v>11605</v>
       </c>
       <c r="D497">
         <v>2375</v>
@@ -13288,7 +13288,7 @@
         <v>7954</v>
       </c>
       <c r="G497">
-        <v>12631</v>
+        <v>12637</v>
       </c>
       <c r="H497">
         <v>14543</v>
@@ -13302,7 +13302,7 @@
         <v>9949</v>
       </c>
       <c r="C498">
-        <v>12700</v>
+        <v>12751</v>
       </c>
       <c r="D498">
         <v>2535</v>
@@ -13314,7 +13314,7 @@
         <v>10520</v>
       </c>
       <c r="G498">
-        <v>13885</v>
+        <v>13888</v>
       </c>
       <c r="H498">
         <v>17299</v>
@@ -13328,7 +13328,7 @@
         <v>9949</v>
       </c>
       <c r="C499">
-        <v>12700</v>
+        <v>12751</v>
       </c>
       <c r="D499">
         <v>2535</v>
@@ -13340,7 +13340,7 @@
         <v>10520</v>
       </c>
       <c r="G499">
-        <v>13885</v>
+        <v>13888</v>
       </c>
       <c r="H499">
         <v>17299</v>
@@ -13354,7 +13354,7 @@
         <v>9949</v>
       </c>
       <c r="C500">
-        <v>12700</v>
+        <v>12751</v>
       </c>
       <c r="D500">
         <v>2535</v>
@@ -13366,7 +13366,7 @@
         <v>10520</v>
       </c>
       <c r="G500">
-        <v>13885</v>
+        <v>13888</v>
       </c>
       <c r="H500">
         <v>17299</v>
@@ -13380,7 +13380,7 @@
         <v>7988</v>
       </c>
       <c r="C501">
-        <v>7546</v>
+        <v>7560</v>
       </c>
       <c r="D501">
         <v>2312</v>
@@ -13392,7 +13392,7 @@
         <v>8438</v>
       </c>
       <c r="G501">
-        <v>8685</v>
+        <v>8686</v>
       </c>
       <c r="H501">
         <v>11083</v>
